--- a/Dados/ativos_mapeados_com_taxa_efetiva.xlsx
+++ b/Dados/ativos_mapeados_com_taxa_efetiva.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J85"/>
+  <dimension ref="A1:J91"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -513,7 +513,7 @@
         </is>
       </c>
       <c r="H2" t="n">
-        <v>1.01626291113667</v>
+        <v>1.01553505875782</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
@@ -557,7 +557,7 @@
         </is>
       </c>
       <c r="H3" t="n">
-        <v>1.01626291113667</v>
+        <v>1.01553505875782</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
@@ -601,7 +601,7 @@
         </is>
       </c>
       <c r="H4" t="n">
-        <v>1.04914803198956</v>
+        <v>1.04831805749317</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
@@ -645,7 +645,7 @@
         </is>
       </c>
       <c r="H5" t="n">
-        <v>1.063267934349178</v>
+        <v>1.062938081797936</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
@@ -689,7 +689,7 @@
         </is>
       </c>
       <c r="H6" t="n">
-        <v>1.04914803198956</v>
+        <v>1.04831805749317</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
@@ -733,7 +733,7 @@
         </is>
       </c>
       <c r="H7" t="n">
-        <v>1.04914803198956</v>
+        <v>1.04831805749317</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
@@ -777,7 +777,7 @@
         </is>
       </c>
       <c r="H8" t="n">
-        <v>1.04914803198956</v>
+        <v>1.04831805749317</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
@@ -957,7 +957,7 @@
         </is>
       </c>
       <c r="H12" t="n">
-        <v>1.031768685873833</v>
+        <v>1.031649836844364</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
@@ -1049,7 +1049,7 @@
         </is>
       </c>
       <c r="H14" t="n">
-        <v>1.031768685873833</v>
+        <v>1.031649836844364</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
@@ -1185,7 +1185,7 @@
         </is>
       </c>
       <c r="H17" t="n">
-        <v>1.026805369518718</v>
+        <v>1.026691004408933</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
@@ -1321,7 +1321,7 @@
         </is>
       </c>
       <c r="H20" t="n">
-        <v>1.026805369518718</v>
+        <v>1.026691004408933</v>
       </c>
       <c r="I20" t="inlineStr">
         <is>
@@ -1493,7 +1493,7 @@
         </is>
       </c>
       <c r="H24" t="n">
-        <v>1.031932</v>
+        <v>1.030755</v>
       </c>
       <c r="I24" t="inlineStr">
         <is>
@@ -1537,7 +1537,7 @@
         </is>
       </c>
       <c r="H25" t="n">
-        <v>1.031932</v>
+        <v>1.030755</v>
       </c>
       <c r="I25" t="inlineStr">
         <is>
@@ -1581,7 +1581,7 @@
         </is>
       </c>
       <c r="H26" t="n">
-        <v>1.031932</v>
+        <v>1.030755</v>
       </c>
       <c r="I26" t="inlineStr">
         <is>
@@ -1625,7 +1625,7 @@
         </is>
       </c>
       <c r="H27" t="n">
-        <v>1.031932</v>
+        <v>1.030755</v>
       </c>
       <c r="I27" t="inlineStr">
         <is>
@@ -1673,7 +1673,7 @@
         </is>
       </c>
       <c r="H28" t="n">
-        <v>1.031932</v>
+        <v>1.030755</v>
       </c>
       <c r="I28" t="inlineStr">
         <is>
@@ -1761,7 +1761,7 @@
         </is>
       </c>
       <c r="H30" t="n">
-        <v>1.0214880754061</v>
+        <v>1.02110484018471</v>
       </c>
       <c r="I30" t="inlineStr">
         <is>
@@ -1809,7 +1809,7 @@
         </is>
       </c>
       <c r="H31" t="n">
-        <v>1.02370957634504</v>
+        <v>1.023681210689404</v>
       </c>
       <c r="I31" t="inlineStr">
         <is>
@@ -1853,7 +1853,7 @@
         </is>
       </c>
       <c r="H32" t="n">
-        <v>1.0214880754061</v>
+        <v>1.02110484018471</v>
       </c>
       <c r="I32" t="inlineStr">
         <is>
@@ -2097,7 +2097,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>JERA2026</t>
+          <t>BMG SEG</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -2105,23 +2105,15 @@
           <t>LF002400KC0</t>
         </is>
       </c>
-      <c r="E38" t="inlineStr">
-        <is>
-          <t>BRBMEBLFI8V4</t>
-        </is>
-      </c>
-      <c r="F38" t="inlineStr">
-        <is>
-          <t>567797-LF0</t>
-        </is>
-      </c>
+      <c r="E38" t="inlineStr"/>
+      <c r="F38" t="inlineStr"/>
       <c r="G38" t="inlineStr">
         <is>
           <t>2026-07-31 00:00:00</t>
         </is>
       </c>
       <c r="H38" t="n">
-        <v>1.052494240533592</v>
+        <v>1.052488639161389</v>
       </c>
       <c r="I38" t="inlineStr">
         <is>
@@ -2145,12 +2137,12 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>REAL FIM</t>
+          <t>JERA2026</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>LF002400KC1</t>
+          <t>LF002400KC0</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
@@ -2160,7 +2152,7 @@
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>567798-LF0</t>
+          <t>567797-LF0</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
@@ -2169,7 +2161,7 @@
         </is>
       </c>
       <c r="H39" t="n">
-        <v>1.052494240533592</v>
+        <v>1.052488639161389</v>
       </c>
       <c r="I39" t="inlineStr">
         <is>
@@ -2193,12 +2185,12 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>TOPAZIO INFRA</t>
+          <t>REAL FIM</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>LF002400KC2</t>
+          <t>LF002400KC1</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
@@ -2206,18 +2198,22 @@
           <t>BRBMEBLFI8V4</t>
         </is>
       </c>
-      <c r="F40" t="inlineStr"/>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>567798-LF0</t>
+        </is>
+      </c>
       <c r="G40" t="inlineStr">
         <is>
           <t>2026-07-31 00:00:00</t>
         </is>
       </c>
       <c r="H40" t="n">
-        <v>1.03646883318903</v>
+        <v>1.052488639161389</v>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>ISIN</t>
+          <t>MATRIZ</t>
         </is>
       </c>
       <c r="J40" t="b">
@@ -2227,37 +2223,37 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>LFSC</t>
+          <t>Letra Financeira</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>BANCO ABC BRASIL S.A.</t>
+          <t>BANCO MERCANTIL DO BRASIL S.A.</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>FIRF GERAES</t>
+          <t>TOPAZIO INFRA</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>LFSC19003FD</t>
+          <t>LF002400KC2</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>BRABCBLFN7I2</t>
+          <t>BRBMEBLFI8V4</t>
         </is>
       </c>
       <c r="F41" t="inlineStr"/>
       <c r="G41" t="inlineStr">
         <is>
-          <t>2024-10-17 00:00:00</t>
+          <t>2026-07-31 00:00:00</t>
         </is>
       </c>
       <c r="H41" t="n">
-        <v>0.0108</v>
+        <v>1.03646883318903</v>
       </c>
       <c r="I41" t="inlineStr">
         <is>
@@ -2281,12 +2277,12 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>HORIZONTE FIM</t>
+          <t>FIRF GERAES</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>LFSC19003W3</t>
+          <t>LFSC19003FD</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
@@ -2325,12 +2321,12 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>FIRF GERAES 30</t>
+          <t>HORIZONTE FIM</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>LFSC19003W4</t>
+          <t>LFSC19003W3</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
@@ -2364,32 +2360,32 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>BANCO DO NORDESTE DO BRASIL S.A.</t>
+          <t>BANCO ABC BRASIL S.A.</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>HORIZONTE FIM</t>
+          <t>FIRF GERAES 30</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>LFSC190054C</t>
+          <t>LFSC19003W4</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>BRBNBRLFI013</t>
+          <t>BRABCBLFN7I2</t>
         </is>
       </c>
       <c r="F44" t="inlineStr"/>
       <c r="G44" t="inlineStr">
         <is>
-          <t>2024-06-11 00:00:00</t>
+          <t>2024-10-17 00:00:00</t>
         </is>
       </c>
       <c r="H44" t="n">
-        <v>1.65</v>
+        <v>0.0108</v>
       </c>
       <c r="I44" t="inlineStr">
         <is>
@@ -2413,17 +2409,17 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>BH INFRA</t>
+          <t>HORIZONTE FIM</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>LFSC190054D</t>
+          <t>LFSC190054C</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>BRBNBRLFI021</t>
+          <t>BRBNBRLFI013</t>
         </is>
       </c>
       <c r="F45" t="inlineStr"/>
@@ -2457,7 +2453,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>FIRF GERAES</t>
+          <t>BH INFRA</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -2501,7 +2497,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>HORIZONTE FIM</t>
+          <t>FIRF GERAES</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -2545,7 +2541,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>MANACA INFRA</t>
+          <t>HORIZONTE FIM</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -2589,23 +2585,23 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>FIRF GERAES 30</t>
+          <t>MANACA INFRA</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>LFSC190054I</t>
+          <t>LFSC190054D</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>BRBNBRLFI039</t>
+          <t>BRBNBRLFI021</t>
         </is>
       </c>
       <c r="F49" t="inlineStr"/>
       <c r="G49" t="inlineStr">
         <is>
-          <t>2024-06-12 00:00:00</t>
+          <t>2024-06-11 00:00:00</t>
         </is>
       </c>
       <c r="H49" t="n">
@@ -2633,7 +2629,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>HORIZONTE FIM</t>
+          <t>FIRF GERAES 30</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -2682,12 +2678,12 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>LFSC190059S</t>
+          <t>LFSC190054I</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>BRBNBRLFI062</t>
+          <t>BRBNBRLFI039</t>
         </is>
       </c>
       <c r="F51" t="inlineStr"/>
@@ -2721,23 +2717,23 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>FIRF GERAES 30</t>
+          <t>HORIZONTE FIM</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>LFSC19005FF</t>
+          <t>LFSC190059S</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>BRBNBRLFI0C5</t>
+          <t>BRBNBRLFI062</t>
         </is>
       </c>
       <c r="F52" t="inlineStr"/>
       <c r="G52" t="inlineStr">
         <is>
-          <t>2024-06-18 00:00:00</t>
+          <t>2024-06-12 00:00:00</t>
         </is>
       </c>
       <c r="H52" t="n">
@@ -2765,7 +2761,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>HORIZONTE FIM</t>
+          <t>FIRF GERAES 30</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -2814,18 +2810,18 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>LFSC19005L1</t>
+          <t>LFSC19005FF</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>BRBNBRLFI0F8</t>
+          <t>BRBNBRLFI0C5</t>
         </is>
       </c>
       <c r="F54" t="inlineStr"/>
       <c r="G54" t="inlineStr">
         <is>
-          <t>2024-06-19 00:00:00</t>
+          <t>2024-06-18 00:00:00</t>
         </is>
       </c>
       <c r="H54" t="n">
@@ -2853,23 +2849,23 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>BH INFRA</t>
+          <t>HORIZONTE FIM</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>LFSC19005L3</t>
+          <t>LFSC19005L1</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>BRBNBRLFI0G6</t>
+          <t>BRBNBRLFI0F8</t>
         </is>
       </c>
       <c r="F55" t="inlineStr"/>
       <c r="G55" t="inlineStr">
         <is>
-          <t>2024-06-21 00:00:00</t>
+          <t>2024-06-19 00:00:00</t>
         </is>
       </c>
       <c r="H55" t="n">
@@ -2897,7 +2893,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>FIRF GERAES 30</t>
+          <t>BH INFRA</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -2936,7 +2932,7 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>BANCO ABC BRASIL S.A.</t>
+          <t>BANCO DO NORDESTE DO BRASIL S.A.</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -2946,22 +2942,22 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>LFSC19007G2</t>
+          <t>LFSC19005L3</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>BRABCBLFIM30</t>
+          <t>BRBNBRLFI0G6</t>
         </is>
       </c>
       <c r="F57" t="inlineStr"/>
       <c r="G57" t="inlineStr">
         <is>
-          <t>2024-10-17 00:00:00</t>
+          <t>2024-06-21 00:00:00</t>
         </is>
       </c>
       <c r="H57" t="n">
-        <v>0.004631489999999999</v>
+        <v>1.65</v>
       </c>
       <c r="I57" t="inlineStr">
         <is>
@@ -2975,45 +2971,41 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>LFSN</t>
+          <t>LFSC</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>BANCO BRADESCO S.A.</t>
+          <t>BANCO ABC BRASIL S.A.</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>JERA2026</t>
+          <t>FIRF GERAES 30</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>LFSN1800DG1</t>
+          <t>LFSC19007G2</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>BRBBDCLTR2X9</t>
-        </is>
-      </c>
-      <c r="F58" t="inlineStr">
-        <is>
-          <t>407137-LFS</t>
-        </is>
-      </c>
+          <t>BRABCBLFIM30</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr"/>
       <c r="G58" t="inlineStr">
         <is>
-          <t>2026-08-03 00:00:00</t>
+          <t>2024-10-17 00:00:00</t>
         </is>
       </c>
       <c r="H58" t="n">
-        <v>1.015163025666136</v>
+        <v>0.004631489999999999</v>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>MATRIZ</t>
+          <t>ISIN</t>
         </is>
       </c>
       <c r="J58" t="b">
@@ -3028,36 +3020,32 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>BANCO BRADESCO S.A.</t>
+          <t>BANCO SAFRA S.A.</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>FIRF GERAES</t>
+          <t>BH INFRA</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>LFSN1800DIG</t>
-        </is>
-      </c>
-      <c r="E59" t="inlineStr">
-        <is>
-          <t>BRBBDCLTROH4</t>
-        </is>
-      </c>
+          <t>LFSN1800D4W</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr"/>
       <c r="F59" t="inlineStr"/>
       <c r="G59" t="inlineStr">
         <is>
-          <t>2026-08-03 00:00:00</t>
+          <t>2026-06-08 00:00:00</t>
         </is>
       </c>
       <c r="H59" t="n">
-        <v>1.02361</v>
+        <v>1.015984776187372</v>
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>ISIN</t>
+          <t>MATRIZ</t>
         </is>
       </c>
       <c r="J59" t="b">
@@ -3072,36 +3060,28 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>BANCO SAFRA S.A.</t>
+          <t>BANCO BRADESCO S.A.</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>JERA2026</t>
+          <t>CARMEL INFRA</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>LFSN1800DS5</t>
-        </is>
-      </c>
-      <c r="E60" t="inlineStr">
-        <is>
-          <t>BRBSAFLNN8B3</t>
-        </is>
-      </c>
-      <c r="F60" t="inlineStr">
-        <is>
-          <t>335769-LFS</t>
-        </is>
-      </c>
+          <t>LFSN1800DG1</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr"/>
+      <c r="F60" t="inlineStr"/>
       <c r="G60" t="inlineStr">
         <is>
-          <t>2026-08-17 00:00:00</t>
+          <t>2026-08-03 00:00:00</t>
         </is>
       </c>
       <c r="H60" t="n">
-        <v>1.016</v>
+        <v>1.013470243265679</v>
       </c>
       <c r="I60" t="inlineStr">
         <is>
@@ -3120,36 +3100,40 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>BANCO ABC BRASIL S.A.</t>
+          <t>BANCO BRADESCO S.A.</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>FIRF GERAES</t>
+          <t>JERA2026</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>LFSN1800E2G</t>
+          <t>LFSN1800DG1</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>BRABCBLFIM22</t>
-        </is>
-      </c>
-      <c r="F61" t="inlineStr"/>
+          <t>BRBBDCLTR2X9</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>407137-LFS</t>
+        </is>
+      </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>2025-09-29 00:00:00</t>
+          <t>2026-08-03 00:00:00</t>
         </is>
       </c>
       <c r="H61" t="n">
-        <v>0.004631489999999999</v>
+        <v>1.013470243265679</v>
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>ISIN</t>
+          <t>MATRIZ</t>
         </is>
       </c>
       <c r="J61" t="b">
@@ -3164,7 +3148,7 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>BANCO SAFRA S.A.</t>
+          <t>BANCO BRADESCO S.A.</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -3174,22 +3158,22 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>LFSN1800HXO</t>
+          <t>LFSN1800DIG</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>BRBSAFLNN7R1</t>
+          <t>BRBBDCLTROH4</t>
         </is>
       </c>
       <c r="F62" t="inlineStr"/>
       <c r="G62" t="inlineStr">
         <is>
-          <t>2026-11-06 00:00:00</t>
+          <t>2026-08-03 00:00:00</t>
         </is>
       </c>
       <c r="H62" t="n">
-        <v>1.032666</v>
+        <v>1.02361</v>
       </c>
       <c r="I62" t="inlineStr">
         <is>
@@ -3213,31 +3197,27 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>FIRF GERAES</t>
+          <t>BORDEAUX INFRA</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>LFSN1900008</t>
-        </is>
-      </c>
-      <c r="E63" t="inlineStr">
-        <is>
-          <t>BRBSAFLFNBB5</t>
-        </is>
-      </c>
+          <t>LFSN1800DS5</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr"/>
       <c r="F63" t="inlineStr"/>
       <c r="G63" t="inlineStr">
         <is>
-          <t>2027-01-08 00:00:00</t>
+          <t>2026-08-17 00:00:00</t>
         </is>
       </c>
       <c r="H63" t="n">
-        <v>1.040176</v>
+        <v>1.015991948917102</v>
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>ISIN</t>
+          <t>MATRIZ</t>
         </is>
       </c>
       <c r="J63" t="b">
@@ -3252,36 +3232,28 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>BANCO BTG PACTUAL S.A.</t>
+          <t>BANCO SAFRA S.A.</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>JERA2026</t>
+          <t>CARMEL INFRA</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>LFSN19001BC</t>
-        </is>
-      </c>
-      <c r="E64" t="inlineStr">
-        <is>
-          <t>BRBPACLFIVQ4</t>
-        </is>
-      </c>
-      <c r="F64" t="inlineStr">
-        <is>
-          <t>353997-N L</t>
-        </is>
-      </c>
+          <t>LFSN1800DS5</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr"/>
+      <c r="F64" t="inlineStr"/>
       <c r="G64" t="inlineStr">
         <is>
-          <t>2027-04-09 00:00:00</t>
+          <t>2026-08-17 00:00:00</t>
         </is>
       </c>
       <c r="H64" t="n">
-        <v>1.051724082046834</v>
+        <v>1.015991948917102</v>
       </c>
       <c r="I64" t="inlineStr">
         <is>
@@ -3300,36 +3272,40 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>BANCO BTG PACTUAL S.A.</t>
+          <t>BANCO SAFRA S.A.</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>BH INFRA</t>
+          <t>JERA2026</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>LFSN19001BH</t>
+          <t>LFSN1800DS5</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>BRBPACLFIVQ4</t>
-        </is>
-      </c>
-      <c r="F65" t="inlineStr"/>
+          <t>BRBSAFLNN8B3</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>335769-LFS</t>
+        </is>
+      </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>2027-04-09 00:00:00</t>
+          <t>2026-08-17 00:00:00</t>
         </is>
       </c>
       <c r="H65" t="n">
-        <v>1.040961</v>
+        <v>1.015991948917102</v>
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>ISIN</t>
+          <t>MATRIZ</t>
         </is>
       </c>
       <c r="J65" t="b">
@@ -3344,32 +3320,32 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>BANCO BTG PACTUAL S.A.</t>
+          <t>BANCO ABC BRASIL S.A.</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>FIRF GERAES 30</t>
+          <t>FIRF GERAES</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>LFSN19006KM</t>
+          <t>LFSN1800E2G</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>BRBPACLFIWC2</t>
+          <t>BRABCBLFIM22</t>
         </is>
       </c>
       <c r="F66" t="inlineStr"/>
       <c r="G66" t="inlineStr">
         <is>
-          <t>2028-05-31 00:00:00</t>
+          <t>2025-09-29 00:00:00</t>
         </is>
       </c>
       <c r="H66" t="n">
-        <v>1.054204</v>
+        <v>0.004631489999999999</v>
       </c>
       <c r="I66" t="inlineStr">
         <is>
@@ -3388,32 +3364,32 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>BANCO BTG PACTUAL S.A.</t>
+          <t>BANCO SAFRA S.A.</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>HORIZONTE FIM</t>
+          <t>FIRF GERAES</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>LFSN19006KM</t>
+          <t>LFSN1800HXO</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>BRBPACLFIWC2</t>
+          <t>BRBSAFLNN7R1</t>
         </is>
       </c>
       <c r="F67" t="inlineStr"/>
       <c r="G67" t="inlineStr">
         <is>
-          <t>2028-05-31 00:00:00</t>
+          <t>2026-11-06 00:00:00</t>
         </is>
       </c>
       <c r="H67" t="n">
-        <v>1.054204</v>
+        <v>1.032666</v>
       </c>
       <c r="I67" t="inlineStr">
         <is>
@@ -3432,32 +3408,32 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>BANCO BTG PACTUAL S.A.</t>
+          <t>BANCO SAFRA S.A.</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>MANACA INFRA</t>
+          <t>FIRF GERAES</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>LFSN19006KM</t>
+          <t>LFSN1900008</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>BRBPACLFIWC2</t>
+          <t>BRBSAFLFNBB5</t>
         </is>
       </c>
       <c r="F68" t="inlineStr"/>
       <c r="G68" t="inlineStr">
         <is>
-          <t>2028-05-31 00:00:00</t>
+          <t>2027-01-08 00:00:00</t>
         </is>
       </c>
       <c r="H68" t="n">
-        <v>1.054204</v>
+        <v>1.03773</v>
       </c>
       <c r="I68" t="inlineStr">
         <is>
@@ -3481,31 +3457,23 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>REAL FIM</t>
+          <t>CARMEL INFRA</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>LFSN19006KM</t>
-        </is>
-      </c>
-      <c r="E69" t="inlineStr">
-        <is>
-          <t>BRBPACLFIWC2</t>
-        </is>
-      </c>
-      <c r="F69" t="inlineStr">
-        <is>
-          <t>513453-LFS</t>
-        </is>
-      </c>
+          <t>LFSN19001BC</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr"/>
+      <c r="F69" t="inlineStr"/>
       <c r="G69" t="inlineStr">
         <is>
-          <t>2028-05-31 00:00:00</t>
+          <t>2027-04-09 00:00:00</t>
         </is>
       </c>
       <c r="H69" t="n">
-        <v>1.065353039136789</v>
+        <v>1.050625</v>
       </c>
       <c r="I69" t="inlineStr">
         <is>
@@ -3529,31 +3497,35 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>FIRF GERAES</t>
+          <t>JERA2026</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>LFSN19006KN</t>
+          <t>LFSN19001BC</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>BRBPACLFIWC2</t>
-        </is>
-      </c>
-      <c r="F70" t="inlineStr"/>
+          <t>BRBPACLFIVQ4</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>353997-N L</t>
+        </is>
+      </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>2028-05-31 00:00:00</t>
+          <t>2027-04-09 00:00:00</t>
         </is>
       </c>
       <c r="H70" t="n">
-        <v>1.054204</v>
+        <v>1.050625</v>
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>ISIN</t>
+          <t>MATRIZ</t>
         </is>
       </c>
       <c r="J70" t="b">
@@ -3568,7 +3540,7 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>BANCO BMG S.A.</t>
+          <t>BANCO BTG PACTUAL S.A.</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
@@ -3578,22 +3550,22 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>LFSN1900971</t>
+          <t>LFSN19001BH</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>BRBMGBLFI489</t>
+          <t>BRBPACLFIVQ4</t>
         </is>
       </c>
       <c r="F71" t="inlineStr"/>
       <c r="G71" t="inlineStr">
         <is>
-          <t>2026-06-22 00:00:00</t>
+          <t>2027-04-09 00:00:00</t>
         </is>
       </c>
       <c r="H71" t="n">
-        <v>1.204881</v>
+        <v>1.039847</v>
       </c>
       <c r="I71" t="inlineStr">
         <is>
@@ -3612,32 +3584,32 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>BANCO BMG S.A.</t>
+          <t>BANCO BTG PACTUAL S.A.</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>BORDEAUX INFRA</t>
+          <t>FIRF GERAES 30</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>LFSN1900971</t>
+          <t>LFSN19006KM</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>BRBMGBLFI489</t>
+          <t>BRBPACLFIWC2</t>
         </is>
       </c>
       <c r="F72" t="inlineStr"/>
       <c r="G72" t="inlineStr">
         <is>
-          <t>2026-06-22 00:00:00</t>
+          <t>2028-05-31 00:00:00</t>
         </is>
       </c>
       <c r="H72" t="n">
-        <v>1.204881</v>
+        <v>1.053379</v>
       </c>
       <c r="I72" t="inlineStr">
         <is>
@@ -3656,32 +3628,32 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>BANCO BMG S.A.</t>
+          <t>BANCO BTG PACTUAL S.A.</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>FIRF GERAES 30</t>
+          <t>HORIZONTE FIM</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>LFSN1900971</t>
+          <t>LFSN19006KM</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>BRBMGBLFI489</t>
+          <t>BRBPACLFIWC2</t>
         </is>
       </c>
       <c r="F73" t="inlineStr"/>
       <c r="G73" t="inlineStr">
         <is>
-          <t>2026-06-22 00:00:00</t>
+          <t>2028-05-31 00:00:00</t>
         </is>
       </c>
       <c r="H73" t="n">
-        <v>1.204881</v>
+        <v>1.053379</v>
       </c>
       <c r="I73" t="inlineStr">
         <is>
@@ -3700,32 +3672,32 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>BANCO BMG S.A.</t>
+          <t>BANCO BTG PACTUAL S.A.</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>FIRF GERAES</t>
+          <t>MANACA INFRA</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>LFSN1900971</t>
+          <t>LFSN19006KM</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>BRBMGBLFI489</t>
+          <t>BRBPACLFIWC2</t>
         </is>
       </c>
       <c r="F74" t="inlineStr"/>
       <c r="G74" t="inlineStr">
         <is>
-          <t>2026-06-22 00:00:00</t>
+          <t>2028-05-31 00:00:00</t>
         </is>
       </c>
       <c r="H74" t="n">
-        <v>1.204881</v>
+        <v>1.053379</v>
       </c>
       <c r="I74" t="inlineStr">
         <is>
@@ -3744,36 +3716,40 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>BANCO BMG S.A.</t>
+          <t>BANCO BTG PACTUAL S.A.</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>BH INFRA</t>
+          <t>REAL FIM</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>LFSN19009YU</t>
+          <t>LFSN19006KM</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>BRBMGBLFI6I3</t>
-        </is>
-      </c>
-      <c r="F75" t="inlineStr"/>
+          <t>BRBPACLFIWC2</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>513453-LFS</t>
+        </is>
+      </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>2026-06-26 00:00:00</t>
+          <t>2028-05-31 00:00:00</t>
         </is>
       </c>
       <c r="H75" t="n">
-        <v>1.204881</v>
+        <v>1.064997093019325</v>
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>ISIN</t>
+          <t>MATRIZ</t>
         </is>
       </c>
       <c r="J75" t="b">
@@ -3788,7 +3764,7 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>BANCO BMG S.A.</t>
+          <t>BANCO BTG PACTUAL S.A.</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
@@ -3798,22 +3774,22 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>LFSN19009YU</t>
+          <t>LFSN19006KN</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>BRBMGBLFI6I3</t>
+          <t>BRBPACLFIWC2</t>
         </is>
       </c>
       <c r="F76" t="inlineStr"/>
       <c r="G76" t="inlineStr">
         <is>
-          <t>2026-06-26 00:00:00</t>
+          <t>2028-05-31 00:00:00</t>
         </is>
       </c>
       <c r="H76" t="n">
-        <v>1.204881</v>
+        <v>1.053379</v>
       </c>
       <c r="I76" t="inlineStr">
         <is>
@@ -3832,32 +3808,32 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>BANCO SAFRA S.A.</t>
+          <t>BANCO BMG S.A.</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>FIRF GERAES 30</t>
+          <t>BH INFRA</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>LFSN1900CR5</t>
+          <t>LFSN1900971</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>BRBSAFLFNG47</t>
+          <t>BRBMGBLFI489</t>
         </is>
       </c>
       <c r="F77" t="inlineStr"/>
       <c r="G77" t="inlineStr">
         <is>
-          <t>2029-08-13 00:00:00</t>
+          <t>2026-06-22 00:00:00</t>
         </is>
       </c>
       <c r="H77" t="n">
-        <v>1.093356</v>
+        <v>1.200691</v>
       </c>
       <c r="I77" t="inlineStr">
         <is>
@@ -3871,45 +3847,41 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>CDB</t>
+          <t>LFSN</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>AGIBANK</t>
+          <t>BANCO BMG S.A.</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>BMG SEG</t>
+          <t>BORDEAUX INFRA</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>CDB3251WXH0</t>
+          <t>LFSN1900971</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>BRAGBKC00M66</t>
-        </is>
-      </c>
-      <c r="F78" t="inlineStr">
-        <is>
-          <t>614522-CDB</t>
-        </is>
-      </c>
+          <t>BRBMGBLFI489</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr"/>
       <c r="G78" t="inlineStr">
         <is>
-          <t>2027-03-08 00:00:00</t>
+          <t>2026-06-22 00:00:00</t>
         </is>
       </c>
       <c r="H78" t="n">
-        <v>1.063267934349178</v>
+        <v>1.200691</v>
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>MATRIZ</t>
+          <t>ISIN</t>
         </is>
       </c>
       <c r="J78" t="b">
@@ -3919,45 +3891,41 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>CDB</t>
+          <t>LFSN</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>AGIBANK</t>
+          <t>BANCO BMG S.A.</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>JERA2026</t>
+          <t>FIRF GERAES 30</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>CDB3251WXH0</t>
+          <t>LFSN1900971</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>BRAGBKC00M66</t>
-        </is>
-      </c>
-      <c r="F79" t="inlineStr">
-        <is>
-          <t>353997-N L</t>
-        </is>
-      </c>
+          <t>BRBMGBLFI489</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr"/>
       <c r="G79" t="inlineStr">
         <is>
-          <t>2027-03-08 00:00:00</t>
+          <t>2026-06-22 00:00:00</t>
         </is>
       </c>
       <c r="H79" t="n">
-        <v>1.063267934349178</v>
+        <v>1.200691</v>
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>MATRIZ</t>
+          <t>ISIN</t>
         </is>
       </c>
       <c r="J79" t="b">
@@ -3967,45 +3935,41 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>CDB</t>
+          <t>LFSN</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>AGIBANK</t>
+          <t>BANCO BMG S.A.</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>REAL FIM</t>
+          <t>FIRF GERAES</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>CDB3251WXH0</t>
+          <t>LFSN1900971</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>BRAGBKC00M66</t>
-        </is>
-      </c>
-      <c r="F80" t="inlineStr">
-        <is>
-          <t>353997-N L</t>
-        </is>
-      </c>
+          <t>BRBMGBLFI489</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr"/>
       <c r="G80" t="inlineStr">
         <is>
-          <t>2027-03-08 00:00:00</t>
+          <t>2026-06-22 00:00:00</t>
         </is>
       </c>
       <c r="H80" t="n">
-        <v>1.063267934349178</v>
+        <v>1.200691</v>
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>MATRIZ</t>
+          <t>ISIN</t>
         </is>
       </c>
       <c r="J80" t="b">
@@ -4015,45 +3979,41 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>CDB</t>
+          <t>LFSN</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>BANCO XP</t>
+          <t>BANCO BMG S.A.</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>BMG SEG</t>
+          <t>BH INFRA</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>LF00240072E</t>
+          <t>LFSN19009YU</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>BRBCXPLFIKS5</t>
-        </is>
-      </c>
-      <c r="F81" t="inlineStr">
-        <is>
-          <t>614522-CDB</t>
-        </is>
-      </c>
+          <t>BRBMGBLFI6I3</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr"/>
       <c r="G81" t="inlineStr">
         <is>
-          <t>2026-03-02 00:00:00</t>
+          <t>2026-06-26 00:00:00</t>
         </is>
       </c>
       <c r="H81" t="n">
-        <v>1.0225</v>
+        <v>1.204881</v>
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>MATRIZ</t>
+          <t>ISIN</t>
         </is>
       </c>
       <c r="J81" t="b">
@@ -4063,45 +4023,41 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>CDB</t>
+          <t>LFSN</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>BANCO XP</t>
+          <t>BANCO BMG S.A.</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>JERA2026</t>
+          <t>FIRF GERAES</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>LF00240072E</t>
+          <t>LFSN19009YU</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>BRBCXPLFIKS5</t>
-        </is>
-      </c>
-      <c r="F82" t="inlineStr">
-        <is>
-          <t>353997-N L</t>
-        </is>
-      </c>
+          <t>BRBMGBLFI6I3</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr"/>
       <c r="G82" t="inlineStr">
         <is>
-          <t>2026-03-02 00:00:00</t>
+          <t>2026-06-26 00:00:00</t>
         </is>
       </c>
       <c r="H82" t="n">
-        <v>1.0225</v>
+        <v>1.204881</v>
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>MATRIZ</t>
+          <t>ISIN</t>
         </is>
       </c>
       <c r="J82" t="b">
@@ -4111,45 +4067,41 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>CDB</t>
+          <t>LFSN</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>BANCO BMG S.A.</t>
+          <t>BANCO SAFRA S.A.</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>JERA2026</t>
+          <t>FIRF GERAES 30</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>LFSC19002CD</t>
+          <t>LFSN1900CR5</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>BRBMGBLFI7Q4</t>
-        </is>
-      </c>
-      <c r="F83" t="inlineStr">
-        <is>
-          <t>609712-LFS</t>
-        </is>
-      </c>
+          <t>BRBSAFLFNG47</t>
+        </is>
+      </c>
+      <c r="F83" t="inlineStr"/>
       <c r="G83" t="inlineStr">
         <is>
-          <t>2029-04-09 00:00:00</t>
+          <t>2029-08-13 00:00:00</t>
         </is>
       </c>
       <c r="H83" t="n">
-        <v>1.145180230498749</v>
+        <v>1.093356</v>
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t>MATRIZ</t>
+          <t>ISIN</t>
         </is>
       </c>
       <c r="J83" t="b">
@@ -4164,36 +4116,36 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>BANCO BMG S.A.</t>
+          <t>AGIBANK</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>JERA2026</t>
+          <t>BMG SEG</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>LFSC19002CE</t>
+          <t>CDB3251WXH0</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>BRBMGBLFI7P6</t>
+          <t>BRAGBKC00M66</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>609711-LFS</t>
+          <t>614522-CDB</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>2029-04-09 00:00:00</t>
+          <t>2027-03-08 00:00:00</t>
         </is>
       </c>
       <c r="H84" t="n">
-        <v>1.145180230498749</v>
+        <v>1.062938081797936</v>
       </c>
       <c r="I84" t="inlineStr">
         <is>
@@ -4212,43 +4164,331 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
+          <t>AGIBANK</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>JERA2026</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>CDB3251WXH0</t>
+        </is>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>BRAGBKC00M66</t>
+        </is>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>353997-N L</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>2027-03-08 00:00:00</t>
+        </is>
+      </c>
+      <c r="H85" t="n">
+        <v>1.062938081797936</v>
+      </c>
+      <c r="I85" t="inlineStr">
+        <is>
+          <t>MATRIZ</t>
+        </is>
+      </c>
+      <c r="J85" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>CDB</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>AGIBANK</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>REAL FIM</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>CDB3251WXH0</t>
+        </is>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>BRAGBKC00M66</t>
+        </is>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>353997-N L</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>2027-03-08 00:00:00</t>
+        </is>
+      </c>
+      <c r="H86" t="n">
+        <v>1.062938081797936</v>
+      </c>
+      <c r="I86" t="inlineStr">
+        <is>
+          <t>MATRIZ</t>
+        </is>
+      </c>
+      <c r="J86" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>CDB</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>BANCO XP</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>BMG SEG</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>LF00240072E</t>
+        </is>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>BRBCXPLFIKS5</t>
+        </is>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>614522-CDB</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>2026-03-02 00:00:00</t>
+        </is>
+      </c>
+      <c r="H87" t="n">
+        <v>1.0225</v>
+      </c>
+      <c r="I87" t="inlineStr">
+        <is>
+          <t>MATRIZ</t>
+        </is>
+      </c>
+      <c r="J87" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>CDB</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>BANCO XP</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>JERA2026</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>LF00240072E</t>
+        </is>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>BRBCXPLFIKS5</t>
+        </is>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>353997-N L</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>2026-03-02 00:00:00</t>
+        </is>
+      </c>
+      <c r="H88" t="n">
+        <v>1.0225</v>
+      </c>
+      <c r="I88" t="inlineStr">
+        <is>
+          <t>MATRIZ</t>
+        </is>
+      </c>
+      <c r="J88" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>CDB</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
           <t>BANCO BMG S.A.</t>
         </is>
       </c>
-      <c r="C85" t="inlineStr">
+      <c r="C89" t="inlineStr">
         <is>
           <t>JERA2026</t>
         </is>
       </c>
-      <c r="D85" t="inlineStr">
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>LFSC19002CD</t>
+        </is>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>BRBMGBLFI7Q4</t>
+        </is>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>609712-LFS</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>2029-04-09 00:00:00</t>
+        </is>
+      </c>
+      <c r="H89" t="n">
+        <v>1.144518010602442</v>
+      </c>
+      <c r="I89" t="inlineStr">
+        <is>
+          <t>MATRIZ</t>
+        </is>
+      </c>
+      <c r="J89" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>CDB</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>BANCO BMG S.A.</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>JERA2026</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>LFSC19002CE</t>
+        </is>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>BRBMGBLFI7P6</t>
+        </is>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>609711-LFS</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>2029-04-09 00:00:00</t>
+        </is>
+      </c>
+      <c r="H90" t="n">
+        <v>1.144518010602442</v>
+      </c>
+      <c r="I90" t="inlineStr">
+        <is>
+          <t>MATRIZ</t>
+        </is>
+      </c>
+      <c r="J90" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>CDB</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>BANCO BMG S.A.</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>JERA2026</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
         <is>
           <t>LFSC19002HS</t>
         </is>
       </c>
-      <c r="E85" t="inlineStr">
+      <c r="E91" t="inlineStr">
         <is>
           <t>BRBMGBLFI7R2</t>
         </is>
       </c>
-      <c r="F85" t="inlineStr">
+      <c r="F91" t="inlineStr">
         <is>
           <t>609713-LFS</t>
         </is>
       </c>
-      <c r="G85" t="inlineStr">
+      <c r="G91" t="inlineStr">
         <is>
           <t>2029-04-09 00:00:00</t>
         </is>
       </c>
-      <c r="H85" t="n">
-        <v>1.145180230498749</v>
-      </c>
-      <c r="I85" t="inlineStr">
+      <c r="H91" t="n">
+        <v>1.144518010602442</v>
+      </c>
+      <c r="I91" t="inlineStr">
         <is>
           <t>MATRIZ</t>
         </is>
       </c>
-      <c r="J85" t="b">
+      <c r="J91" t="b">
         <v>0</v>
       </c>
     </row>

--- a/Dados/ativos_mapeados_com_taxa_efetiva.xlsx
+++ b/Dados/ativos_mapeados_com_taxa_efetiva.xlsx
@@ -1397,17 +1397,23 @@
           <t>HAPV21</t>
         </is>
       </c>
-      <c r="E22" t="inlineStr"/>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>BRHAPVDBS014</t>
+        </is>
+      </c>
       <c r="F22" t="inlineStr"/>
       <c r="G22" t="inlineStr">
         <is>
           <t>2026-07-10 00:00:00</t>
         </is>
       </c>
-      <c r="H22" t="inlineStr"/>
+      <c r="H22" t="n">
+        <v>1.212386</v>
+      </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>ISIN</t>
         </is>
       </c>
       <c r="J22" t="b">
@@ -1450,14 +1456,16 @@
           <t>2026-07-10 00:00:00</t>
         </is>
       </c>
-      <c r="H23" t="inlineStr"/>
+      <c r="H23" t="n">
+        <v>1.212386</v>
+      </c>
       <c r="I23" t="inlineStr">
         <is>
           <t>NA</t>
         </is>
       </c>
       <c r="J23" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="24">
@@ -2105,7 +2113,11 @@
           <t>LF002400KC0</t>
         </is>
       </c>
-      <c r="E38" t="inlineStr"/>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>BRBMEBLFI8V4</t>
+        </is>
+      </c>
       <c r="F38" t="inlineStr"/>
       <c r="G38" t="inlineStr">
         <is>
@@ -3073,7 +3085,11 @@
           <t>LFSN1800DG1</t>
         </is>
       </c>
-      <c r="E60" t="inlineStr"/>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>BRBBDCLTR2X9</t>
+        </is>
+      </c>
       <c r="F60" t="inlineStr"/>
       <c r="G60" t="inlineStr">
         <is>
@@ -3205,7 +3221,11 @@
           <t>LFSN1800DS5</t>
         </is>
       </c>
-      <c r="E63" t="inlineStr"/>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>BRBSAFLNN8B3</t>
+        </is>
+      </c>
       <c r="F63" t="inlineStr"/>
       <c r="G63" t="inlineStr">
         <is>
@@ -3213,11 +3233,11 @@
         </is>
       </c>
       <c r="H63" t="n">
-        <v>1.015991948917102</v>
+        <v>1.02462</v>
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>MATRIZ</t>
+          <t>ISIN</t>
         </is>
       </c>
       <c r="J63" t="b">
@@ -3245,7 +3265,11 @@
           <t>LFSN1800DS5</t>
         </is>
       </c>
-      <c r="E64" t="inlineStr"/>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>BRBSAFLNN8B3</t>
+        </is>
+      </c>
       <c r="F64" t="inlineStr"/>
       <c r="G64" t="inlineStr">
         <is>
@@ -3465,7 +3489,11 @@
           <t>LFSN19001BC</t>
         </is>
       </c>
-      <c r="E69" t="inlineStr"/>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>BRBPACLFIVQ4</t>
+        </is>
+      </c>
       <c r="F69" t="inlineStr"/>
       <c r="G69" t="inlineStr">
         <is>

--- a/Dados/ativos_mapeados_com_taxa_efetiva.xlsx
+++ b/Dados/ativos_mapeados_com_taxa_efetiva.xlsx
@@ -645,7 +645,7 @@
         </is>
       </c>
       <c r="H5" t="n">
-        <v>1.062938081797936</v>
+        <v>1.062862511354904</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
@@ -957,7 +957,7 @@
         </is>
       </c>
       <c r="H12" t="n">
-        <v>1.031649836844364</v>
+        <v>1.031621464981925</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
@@ -1049,7 +1049,7 @@
         </is>
       </c>
       <c r="H14" t="n">
-        <v>1.031649836844364</v>
+        <v>1.031621464981925</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
@@ -1185,7 +1185,7 @@
         </is>
       </c>
       <c r="H17" t="n">
-        <v>1.026691004408933</v>
+        <v>1.0266637404173</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
@@ -1321,7 +1321,7 @@
         </is>
       </c>
       <c r="H20" t="n">
-        <v>1.026691004408933</v>
+        <v>1.0266637404173</v>
       </c>
       <c r="I20" t="inlineStr">
         <is>
@@ -1817,7 +1817,7 @@
         </is>
       </c>
       <c r="H31" t="n">
-        <v>1.023681210689404</v>
+        <v>1.023669954692576</v>
       </c>
       <c r="I31" t="inlineStr">
         <is>
@@ -2125,7 +2125,7 @@
         </is>
       </c>
       <c r="H38" t="n">
-        <v>1.052488639161389</v>
+        <v>1.052487262760346</v>
       </c>
       <c r="I38" t="inlineStr">
         <is>
@@ -2173,7 +2173,7 @@
         </is>
       </c>
       <c r="H39" t="n">
-        <v>1.052488639161389</v>
+        <v>1.052487262760346</v>
       </c>
       <c r="I39" t="inlineStr">
         <is>
@@ -2221,7 +2221,7 @@
         </is>
       </c>
       <c r="H40" t="n">
-        <v>1.052488639161389</v>
+        <v>1.052487262760346</v>
       </c>
       <c r="I40" t="inlineStr">
         <is>
@@ -3053,7 +3053,7 @@
         </is>
       </c>
       <c r="H59" t="n">
-        <v>1.015984776187372</v>
+        <v>1.015982556066905</v>
       </c>
       <c r="I59" t="inlineStr">
         <is>
@@ -3097,7 +3097,7 @@
         </is>
       </c>
       <c r="H60" t="n">
-        <v>1.013470243265679</v>
+        <v>1.011717717542436</v>
       </c>
       <c r="I60" t="inlineStr">
         <is>
@@ -3145,7 +3145,7 @@
         </is>
       </c>
       <c r="H61" t="n">
-        <v>1.013470243265679</v>
+        <v>1.011717717542436</v>
       </c>
       <c r="I61" t="inlineStr">
         <is>
@@ -3277,7 +3277,7 @@
         </is>
       </c>
       <c r="H64" t="n">
-        <v>1.015991948917102</v>
+        <v>1.015989988663004</v>
       </c>
       <c r="I64" t="inlineStr">
         <is>
@@ -3325,7 +3325,7 @@
         </is>
       </c>
       <c r="H65" t="n">
-        <v>1.015991948917102</v>
+        <v>1.015989988663004</v>
       </c>
       <c r="I65" t="inlineStr">
         <is>
@@ -3501,7 +3501,7 @@
         </is>
       </c>
       <c r="H69" t="n">
-        <v>1.050625</v>
+        <v>1.050497965289035</v>
       </c>
       <c r="I69" t="inlineStr">
         <is>
@@ -3549,7 +3549,7 @@
         </is>
       </c>
       <c r="H70" t="n">
-        <v>1.050625</v>
+        <v>1.050497965289035</v>
       </c>
       <c r="I70" t="inlineStr">
         <is>
@@ -3773,7 +3773,7 @@
         </is>
       </c>
       <c r="H75" t="n">
-        <v>1.064997093019325</v>
+        <v>1.064916450955605</v>
       </c>
       <c r="I75" t="inlineStr">
         <is>
@@ -4173,7 +4173,7 @@
         </is>
       </c>
       <c r="H84" t="n">
-        <v>1.062938081797936</v>
+        <v>1.062862511354904</v>
       </c>
       <c r="I84" t="inlineStr">
         <is>
@@ -4221,7 +4221,7 @@
         </is>
       </c>
       <c r="H85" t="n">
-        <v>1.062938081797936</v>
+        <v>1.062862511354904</v>
       </c>
       <c r="I85" t="inlineStr">
         <is>
@@ -4269,7 +4269,7 @@
         </is>
       </c>
       <c r="H86" t="n">
-        <v>1.062938081797936</v>
+        <v>1.062862511354904</v>
       </c>
       <c r="I86" t="inlineStr">
         <is>
@@ -4413,7 +4413,7 @@
         </is>
       </c>
       <c r="H89" t="n">
-        <v>1.144518010602442</v>
+        <v>1.144378917056012</v>
       </c>
       <c r="I89" t="inlineStr">
         <is>
@@ -4461,7 +4461,7 @@
         </is>
       </c>
       <c r="H90" t="n">
-        <v>1.144518010602442</v>
+        <v>1.144378917056012</v>
       </c>
       <c r="I90" t="inlineStr">
         <is>
@@ -4509,7 +4509,7 @@
         </is>
       </c>
       <c r="H91" t="n">
-        <v>1.144518010602442</v>
+        <v>1.144378917056012</v>
       </c>
       <c r="I91" t="inlineStr">
         <is>

--- a/Dados/ativos_mapeados_com_taxa_efetiva.xlsx
+++ b/Dados/ativos_mapeados_com_taxa_efetiva.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J91"/>
+  <dimension ref="A1:J93"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -601,7 +601,7 @@
         </is>
       </c>
       <c r="H4" t="n">
-        <v>1.04831805749317</v>
+        <v>1.04807792075738</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
@@ -645,7 +645,7 @@
         </is>
       </c>
       <c r="H5" t="n">
-        <v>1.062862511354904</v>
+        <v>1.062308713517584</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
@@ -669,7 +669,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>FIRF GERAES 30</t>
+          <t>CARMEL INFRA</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -689,11 +689,11 @@
         </is>
       </c>
       <c r="H6" t="n">
-        <v>1.04831805749317</v>
+        <v>1.062308713517584</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>ISIN</t>
+          <t>MATRIZ</t>
         </is>
       </c>
       <c r="J6" t="b">
@@ -713,7 +713,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>FIRF GERAES</t>
+          <t>FIRF GERAES 30</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -733,7 +733,7 @@
         </is>
       </c>
       <c r="H7" t="n">
-        <v>1.04831805749317</v>
+        <v>1.04807792075738</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
@@ -757,7 +757,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>TOPAZIO INFRA</t>
+          <t>FIRF GERAES</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -777,7 +777,7 @@
         </is>
       </c>
       <c r="H8" t="n">
-        <v>1.04831805749317</v>
+        <v>1.04807792075738</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
@@ -796,32 +796,32 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>PARANA BANCO S.A.</t>
+          <t>AGIBANK</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>BH INFRA</t>
+          <t>TOPAZIO INFRA</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>CDB3253PPYA</t>
+          <t>CDB3251WXH0</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>BRPRBCC059P8</t>
+          <t>BRAGBKC00M66</t>
         </is>
       </c>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
-          <t>2026-03-10 00:00:00</t>
+          <t>2027-03-08 00:00:00</t>
         </is>
       </c>
       <c r="H9" t="n">
-        <v>1.09</v>
+        <v>1.04807792075738</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
@@ -845,7 +845,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>FIRF GERAES 30</t>
+          <t>BH INFRA</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -865,11 +865,11 @@
         </is>
       </c>
       <c r="H10" t="n">
-        <v>1.09</v>
+        <v>1.03139917489967</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>ISIN</t>
+          <t>MATRIZ</t>
         </is>
       </c>
       <c r="J10" t="b">
@@ -889,7 +889,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>FIRF GERAES</t>
+          <t>FIRF GERAES 30</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -909,11 +909,11 @@
         </is>
       </c>
       <c r="H11" t="n">
-        <v>1.09</v>
+        <v>1.03139917489967</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>ISIN</t>
+          <t>MATRIZ</t>
         </is>
       </c>
       <c r="J11" t="b">
@@ -933,7 +933,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>JERA2026</t>
+          <t>FIRF GERAES</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -946,18 +946,14 @@
           <t>BRPRBCC059P8</t>
         </is>
       </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>606488-CDB</t>
-        </is>
-      </c>
+      <c r="F12" t="inlineStr"/>
       <c r="G12" t="inlineStr">
         <is>
           <t>2026-03-10 00:00:00</t>
         </is>
       </c>
       <c r="H12" t="n">
-        <v>1.031621464981925</v>
+        <v>1.03139917489967</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
@@ -981,7 +977,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>MANACA INFRA</t>
+          <t>JERA2026</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -994,18 +990,22 @@
           <t>BRPRBCC059P8</t>
         </is>
       </c>
-      <c r="F13" t="inlineStr"/>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>606488-CDB</t>
+        </is>
+      </c>
       <c r="G13" t="inlineStr">
         <is>
           <t>2026-03-10 00:00:00</t>
         </is>
       </c>
       <c r="H13" t="n">
-        <v>1.09</v>
+        <v>1.03139917489967</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>ISIN</t>
+          <t>MATRIZ</t>
         </is>
       </c>
       <c r="J13" t="b">
@@ -1025,7 +1025,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>REAL FIM</t>
+          <t>MANACA INFRA</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -1038,18 +1038,14 @@
           <t>BRPRBCC059P8</t>
         </is>
       </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>606488-CDB</t>
-        </is>
-      </c>
+      <c r="F14" t="inlineStr"/>
       <c r="G14" t="inlineStr">
         <is>
           <t>2026-03-10 00:00:00</t>
         </is>
       </c>
       <c r="H14" t="n">
-        <v>1.031621464981925</v>
+        <v>1.03139917489967</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
@@ -1068,36 +1064,40 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>BANCO VOLKSWAGEN S/A</t>
+          <t>PARANA BANCO S.A.</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>BBRASIL FIM CP RESP</t>
+          <t>REAL FIM</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>CDB424EERW3</t>
+          <t>CDB3253PPYA</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>BRBVKWC00WA0</t>
-        </is>
-      </c>
-      <c r="F15" t="inlineStr"/>
+          <t>BRPRBCC059P8</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>606488-CDB</t>
+        </is>
+      </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>2026-05-04 00:00:00</t>
+          <t>2026-03-10 00:00:00</t>
         </is>
       </c>
       <c r="H15" t="n">
-        <v>1.0125</v>
+        <v>1.03139917489967</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>ISIN</t>
+          <t>MATRIZ</t>
         </is>
       </c>
       <c r="J15" t="b">
@@ -1117,7 +1117,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>BBRASIL FIM</t>
+          <t>BBRASIL FIM CP RESP</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -1156,40 +1156,36 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>BANCO INTER SA</t>
+          <t>BANCO VOLKSWAGEN S/A</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>REAL FIM</t>
+          <t>BBRASIL FIM</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>CDB7257QUDF</t>
+          <t>CDB424EERW3</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>BRBIDIC002H4</t>
-        </is>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>613312-CDB</t>
-        </is>
-      </c>
+          <t>BRBVKWC00WA0</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr"/>
       <c r="G17" t="inlineStr">
         <is>
-          <t>2026-07-10 00:00:00</t>
+          <t>2026-05-04 00:00:00</t>
         </is>
       </c>
       <c r="H17" t="n">
-        <v>1.0266637404173</v>
+        <v>1.0125</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>MATRIZ</t>
+          <t>ISIN</t>
         </is>
       </c>
       <c r="J17" t="b">
@@ -1209,12 +1205,12 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>FIRF GERAES</t>
+          <t>REAL FIM</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>CDB7257QUDG</t>
+          <t>CDB7257QUDF</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -1222,18 +1218,22 @@
           <t>BRBIDIC002H4</t>
         </is>
       </c>
-      <c r="F18" t="inlineStr"/>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>613312-CDB</t>
+        </is>
+      </c>
       <c r="G18" t="inlineStr">
         <is>
           <t>2026-07-10 00:00:00</t>
         </is>
       </c>
       <c r="H18" t="n">
-        <v>1.022399</v>
+        <v>1.026450628376097</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>ISIN</t>
+          <t>MATRIZ</t>
         </is>
       </c>
       <c r="J18" t="b">
@@ -1253,12 +1253,12 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>FIRF GERAES 30</t>
+          <t>FIRF GERAES</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>CDB7257QUDH</t>
+          <t>CDB7257QUDG</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -1273,7 +1273,7 @@
         </is>
       </c>
       <c r="H19" t="n">
-        <v>1.022399</v>
+        <v>1.02131</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
@@ -1297,12 +1297,12 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>BMG SEG</t>
+          <t>FIRF GERAES 30</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>CDB7257QUDI</t>
+          <t>CDB7257QUDH</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -1310,22 +1310,18 @@
           <t>BRBIDIC002H4</t>
         </is>
       </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>613315-CDB</t>
-        </is>
-      </c>
+      <c r="F20" t="inlineStr"/>
       <c r="G20" t="inlineStr">
         <is>
           <t>2026-07-10 00:00:00</t>
         </is>
       </c>
       <c r="H20" t="n">
-        <v>1.0266637404173</v>
+        <v>1.02131</v>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>MATRIZ</t>
+          <t>ISIN</t>
         </is>
       </c>
       <c r="J20" t="b">
@@ -1340,32 +1336,36 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>BANCO VOLKSWAGEN S/A</t>
+          <t>BANCO INTER SA</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>BBRASIL FIM CP RESP</t>
+          <t>BMG SEG</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>CDB925CDN0L</t>
+          <t>CDB7257QUDI</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>BRBVKWC01543</t>
-        </is>
-      </c>
-      <c r="F21" t="inlineStr"/>
+          <t>BRBIDIC002H4</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>613315-CDB</t>
+        </is>
+      </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>2025-12-22 00:00:00</t>
+          <t>2026-07-10 00:00:00</t>
         </is>
       </c>
       <c r="H21" t="n">
-        <v>1.015</v>
+        <v>1.026450628376097</v>
       </c>
       <c r="I21" t="inlineStr">
         <is>
@@ -1379,41 +1379,41 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Debêntures</t>
+          <t>CDB</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>HAPVIDA PARTICIPACOES E INVESTIMENTOS S/A</t>
+          <t>BANCO VOLKSWAGEN S/A</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>FIRF GERAES</t>
+          <t>BBRASIL FIM CP RESP</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>HAPV21</t>
+          <t>CDB925CDN0L</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>BRHAPVDBS014</t>
+          <t>BRBVKWC01543</t>
         </is>
       </c>
       <c r="F22" t="inlineStr"/>
       <c r="G22" t="inlineStr">
         <is>
-          <t>2026-07-10 00:00:00</t>
+          <t>2025-12-22 00:00:00</t>
         </is>
       </c>
       <c r="H22" t="n">
-        <v>1.212386</v>
+        <v>1.015</v>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>ISIN</t>
+          <t>MATRIZ</t>
         </is>
       </c>
       <c r="J22" t="b">
@@ -1433,7 +1433,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>JERA2026</t>
+          <t>FIRF GERAES</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -1446,26 +1446,22 @@
           <t>BRHAPVDBS014</t>
         </is>
       </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>362409-HAP</t>
-        </is>
-      </c>
+      <c r="F23" t="inlineStr"/>
       <c r="G23" t="inlineStr">
         <is>
           <t>2026-07-10 00:00:00</t>
         </is>
       </c>
       <c r="H23" t="n">
-        <v>1.212386</v>
+        <v>1.398388</v>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>ISIN</t>
         </is>
       </c>
       <c r="J23" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="24">
@@ -1476,40 +1472,44 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>KLABIN S/A</t>
+          <t>HAPVIDA PARTICIPACOES E INVESTIMENTOS S/A</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>BH INFRA</t>
+          <t>JERA2026</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>KLBNA2</t>
+          <t>HAPV21</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>BRKLBNDBS004</t>
-        </is>
-      </c>
-      <c r="F24" t="inlineStr"/>
+          <t>BRHAPVDBS014</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>362409-HAP</t>
+        </is>
+      </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>2029-03-19 00:00:00</t>
+          <t>2026-07-10 00:00:00</t>
         </is>
       </c>
       <c r="H24" t="n">
-        <v>1.030755</v>
+        <v>1.398388</v>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>ISIN</t>
+          <t>NA</t>
         </is>
       </c>
       <c r="J24" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="25">
@@ -1525,7 +1525,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>FIRF GERAES 30</t>
+          <t>BH INFRA</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -1545,7 +1545,7 @@
         </is>
       </c>
       <c r="H25" t="n">
-        <v>1.030755</v>
+        <v>1.036825</v>
       </c>
       <c r="I25" t="inlineStr">
         <is>
@@ -1569,7 +1569,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>FIRF GERAES</t>
+          <t>FIRF GERAES 30</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -1589,7 +1589,7 @@
         </is>
       </c>
       <c r="H26" t="n">
-        <v>1.030755</v>
+        <v>1.036825</v>
       </c>
       <c r="I26" t="inlineStr">
         <is>
@@ -1613,7 +1613,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>HORIZONTE FIM</t>
+          <t>FIRF GERAES</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -1633,7 +1633,7 @@
         </is>
       </c>
       <c r="H27" t="n">
-        <v>1.030755</v>
+        <v>1.036825</v>
       </c>
       <c r="I27" t="inlineStr">
         <is>
@@ -1657,7 +1657,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>REAL FIM</t>
+          <t>HORIZONTE FIM</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -1670,70 +1670,70 @@
           <t>BRKLBNDBS004</t>
         </is>
       </c>
-      <c r="F28" t="inlineStr">
-        <is>
-          <t>353017-KLB</t>
-        </is>
-      </c>
+      <c r="F28" t="inlineStr"/>
       <c r="G28" t="inlineStr">
         <is>
           <t>2029-03-19 00:00:00</t>
         </is>
       </c>
       <c r="H28" t="n">
-        <v>1.030755</v>
+        <v>1.036825</v>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>ISIN</t>
         </is>
       </c>
       <c r="J28" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Letra Financeira</t>
+          <t>Debêntures</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>BANCO XP</t>
+          <t>KLABIN S/A</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>BMG SEG</t>
+          <t>REAL FIM</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LF00240072E</t>
+          <t>KLBNA2</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>BRBCXPLFIKS5</t>
-        </is>
-      </c>
-      <c r="F29" t="inlineStr"/>
+          <t>BRKLBNDBS004</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>353017-KLB</t>
+        </is>
+      </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>2026-03-02 00:00:00</t>
+          <t>2029-03-19 00:00:00</t>
         </is>
       </c>
       <c r="H29" t="n">
-        <v>1.0225</v>
+        <v>1.036825</v>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>MATRIZ</t>
+          <t>NA</t>
         </is>
       </c>
       <c r="J29" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="30">
@@ -1749,31 +1749,31 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>FIRF GERAES</t>
+          <t>BMG SEG</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LF0024007Y4</t>
+          <t>LF00240072E</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>BRBCXPLFIO68</t>
+          <t>BRBCXPLFIKS5</t>
         </is>
       </c>
       <c r="F30" t="inlineStr"/>
       <c r="G30" t="inlineStr">
         <is>
-          <t>2026-03-16 00:00:00</t>
+          <t>2026-03-02 00:00:00</t>
         </is>
       </c>
       <c r="H30" t="n">
-        <v>1.02110484018471</v>
+        <v>1.0225</v>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>ISIN</t>
+          <t>MATRIZ</t>
         </is>
       </c>
       <c r="J30" t="b">
@@ -1783,7 +1783,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>CDB</t>
+          <t>Letra Financeira</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1793,31 +1793,27 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>BMG SEG</t>
+          <t>FIRF GERAES</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LF0024008OB</t>
+          <t>LF0024007Y4</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>BRBCXPLFIO76</t>
-        </is>
-      </c>
-      <c r="F31" t="inlineStr">
-        <is>
-          <t>614522-CDB</t>
-        </is>
-      </c>
+          <t>BRBCXPLFIO68</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr"/>
       <c r="G31" t="inlineStr">
         <is>
-          <t>2026-03-23 00:00:00</t>
+          <t>2026-03-16 00:00:00</t>
         </is>
       </c>
       <c r="H31" t="n">
-        <v>1.023669954692576</v>
+        <v>1.0225</v>
       </c>
       <c r="I31" t="inlineStr">
         <is>
@@ -1831,7 +1827,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Letra Financeira</t>
+          <t>CDB</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1841,7 +1837,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>FIRF GERAES</t>
+          <t>BMG SEG</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -1854,18 +1850,22 @@
           <t>BRBCXPLFIO76</t>
         </is>
       </c>
-      <c r="F32" t="inlineStr"/>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>614522-CDB</t>
+        </is>
+      </c>
       <c r="G32" t="inlineStr">
         <is>
           <t>2026-03-23 00:00:00</t>
         </is>
       </c>
       <c r="H32" t="n">
-        <v>1.02110484018471</v>
+        <v>1.0225</v>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>ISIN</t>
+          <t>MATRIZ</t>
         </is>
       </c>
       <c r="J32" t="b">
@@ -1880,32 +1880,32 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>BANCO MERCANTIL DO BRASIL S.A.</t>
+          <t>BANCO XP</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>FIRF GERAES 30</t>
+          <t>FIRF GERAES</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LF002400KBT</t>
+          <t>LF0024008OB</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>BRBMEBLFI8V4</t>
+          <t>BRBCXPLFIO76</t>
         </is>
       </c>
       <c r="F33" t="inlineStr"/>
       <c r="G33" t="inlineStr">
         <is>
-          <t>2026-07-31 00:00:00</t>
+          <t>2026-03-23 00:00:00</t>
         </is>
       </c>
       <c r="H33" t="n">
-        <v>1.03646883318903</v>
+        <v>1.02110484018471</v>
       </c>
       <c r="I33" t="inlineStr">
         <is>
@@ -1929,12 +1929,12 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>FIRF GERAES</t>
+          <t>FIRF GERAES 30</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LF002400KBU</t>
+          <t>LF002400KBT</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
@@ -1949,7 +1949,7 @@
         </is>
       </c>
       <c r="H34" t="n">
-        <v>1.03646883318903</v>
+        <v>1.03494410423184</v>
       </c>
       <c r="I34" t="inlineStr">
         <is>
@@ -1978,7 +1978,7 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LF002400KBW</t>
+          <t>LF002400KBU</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
@@ -1993,7 +1993,7 @@
         </is>
       </c>
       <c r="H35" t="n">
-        <v>1.03646883318903</v>
+        <v>1.03494410423184</v>
       </c>
       <c r="I35" t="inlineStr">
         <is>
@@ -2017,12 +2017,12 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>MANACA INFRA</t>
+          <t>FIRF GERAES</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LF002400KBX</t>
+          <t>LF002400KBW</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
@@ -2037,7 +2037,7 @@
         </is>
       </c>
       <c r="H36" t="n">
-        <v>1.03646883318903</v>
+        <v>1.03494410423184</v>
       </c>
       <c r="I36" t="inlineStr">
         <is>
@@ -2061,12 +2061,12 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>FIRF GERAES 30</t>
+          <t>MANACA INFRA</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>LF002400KBY</t>
+          <t>LF002400KBX</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
@@ -2081,7 +2081,7 @@
         </is>
       </c>
       <c r="H37" t="n">
-        <v>1.03646883318903</v>
+        <v>1.03494410423184</v>
       </c>
       <c r="I37" t="inlineStr">
         <is>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>BMG SEG</t>
+          <t>FIRF GERAES 30</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>LF002400KC0</t>
+          <t>LF002400KBY</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
@@ -2125,11 +2125,11 @@
         </is>
       </c>
       <c r="H38" t="n">
-        <v>1.052487262760346</v>
+        <v>1.03494410423184</v>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>MATRIZ</t>
+          <t>ISIN</t>
         </is>
       </c>
       <c r="J38" t="b">
@@ -2149,7 +2149,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>JERA2026</t>
+          <t>BMG SEG</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -2162,18 +2162,14 @@
           <t>BRBMEBLFI8V4</t>
         </is>
       </c>
-      <c r="F39" t="inlineStr">
-        <is>
-          <t>567797-LF0</t>
-        </is>
-      </c>
+      <c r="F39" t="inlineStr"/>
       <c r="G39" t="inlineStr">
         <is>
           <t>2026-07-31 00:00:00</t>
         </is>
       </c>
       <c r="H39" t="n">
-        <v>1.052487262760346</v>
+        <v>1.052475915166362</v>
       </c>
       <c r="I39" t="inlineStr">
         <is>
@@ -2197,12 +2193,12 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>REAL FIM</t>
+          <t>JERA2026</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>LF002400KC1</t>
+          <t>LF002400KC0</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
@@ -2212,7 +2208,7 @@
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>567798-LF0</t>
+          <t>567797-LF0</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
@@ -2221,7 +2217,7 @@
         </is>
       </c>
       <c r="H40" t="n">
-        <v>1.052487262760346</v>
+        <v>1.052475915166362</v>
       </c>
       <c r="I40" t="inlineStr">
         <is>
@@ -2245,12 +2241,12 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>TOPAZIO INFRA</t>
+          <t>REAL FIM</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>LF002400KC2</t>
+          <t>LF002400KC1</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
@@ -2258,18 +2254,22 @@
           <t>BRBMEBLFI8V4</t>
         </is>
       </c>
-      <c r="F41" t="inlineStr"/>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>567798-LF0</t>
+        </is>
+      </c>
       <c r="G41" t="inlineStr">
         <is>
           <t>2026-07-31 00:00:00</t>
         </is>
       </c>
       <c r="H41" t="n">
-        <v>1.03646883318903</v>
+        <v>1.052475915166362</v>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>ISIN</t>
+          <t>MATRIZ</t>
         </is>
       </c>
       <c r="J41" t="b">
@@ -2279,37 +2279,37 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>LFSC</t>
+          <t>Letra Financeira</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>BANCO ABC BRASIL S.A.</t>
+          <t>BANCO MERCANTIL DO BRASIL S.A.</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>FIRF GERAES</t>
+          <t>TOPAZIO INFRA</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>LFSC19003FD</t>
+          <t>LF002400KC2</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>BRABCBLFN7I2</t>
+          <t>BRBMEBLFI8V4</t>
         </is>
       </c>
       <c r="F42" t="inlineStr"/>
       <c r="G42" t="inlineStr">
         <is>
-          <t>2024-10-17 00:00:00</t>
+          <t>2026-07-31 00:00:00</t>
         </is>
       </c>
       <c r="H42" t="n">
-        <v>0.0108</v>
+        <v>1.03494410423184</v>
       </c>
       <c r="I42" t="inlineStr">
         <is>
@@ -2333,12 +2333,12 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>HORIZONTE FIM</t>
+          <t>FIRF GERAES</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>LFSC19003W3</t>
+          <t>LFSC19003FD</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
@@ -2353,7 +2353,7 @@
         </is>
       </c>
       <c r="H43" t="n">
-        <v>0.0108</v>
+        <v>0.01</v>
       </c>
       <c r="I43" t="inlineStr">
         <is>
@@ -2377,12 +2377,12 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>FIRF GERAES 30</t>
+          <t>HORIZONTE FIM</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>LFSC19003W4</t>
+          <t>LFSC19003W3</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
@@ -2397,7 +2397,7 @@
         </is>
       </c>
       <c r="H44" t="n">
-        <v>0.0108</v>
+        <v>0.01</v>
       </c>
       <c r="I44" t="inlineStr">
         <is>
@@ -2416,32 +2416,32 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>BANCO DO NORDESTE DO BRASIL S.A.</t>
+          <t>BANCO ABC BRASIL S.A.</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>HORIZONTE FIM</t>
+          <t>FIRF GERAES 30</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>LFSC190054C</t>
+          <t>LFSC19003W4</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>BRBNBRLFI013</t>
+          <t>BRABCBLFN7I2</t>
         </is>
       </c>
       <c r="F45" t="inlineStr"/>
       <c r="G45" t="inlineStr">
         <is>
-          <t>2024-06-11 00:00:00</t>
+          <t>2024-10-17 00:00:00</t>
         </is>
       </c>
       <c r="H45" t="n">
-        <v>1.65</v>
+        <v>0.01</v>
       </c>
       <c r="I45" t="inlineStr">
         <is>
@@ -2465,17 +2465,17 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>BH INFRA</t>
+          <t>HORIZONTE FIM</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>LFSC190054D</t>
+          <t>LFSC190054C</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>BRBNBRLFI021</t>
+          <t>BRBNBRLFI013</t>
         </is>
       </c>
       <c r="F46" t="inlineStr"/>
@@ -2485,7 +2485,7 @@
         </is>
       </c>
       <c r="H46" t="n">
-        <v>1.65</v>
+        <v>1.77</v>
       </c>
       <c r="I46" t="inlineStr">
         <is>
@@ -2509,7 +2509,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>FIRF GERAES</t>
+          <t>BH INFRA</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -2529,7 +2529,7 @@
         </is>
       </c>
       <c r="H47" t="n">
-        <v>1.65</v>
+        <v>1.77</v>
       </c>
       <c r="I47" t="inlineStr">
         <is>
@@ -2553,7 +2553,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>HORIZONTE FIM</t>
+          <t>FIRF GERAES</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -2573,7 +2573,7 @@
         </is>
       </c>
       <c r="H48" t="n">
-        <v>1.65</v>
+        <v>1.77</v>
       </c>
       <c r="I48" t="inlineStr">
         <is>
@@ -2597,7 +2597,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>MANACA INFRA</t>
+          <t>HORIZONTE FIM</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -2617,7 +2617,7 @@
         </is>
       </c>
       <c r="H49" t="n">
-        <v>1.65</v>
+        <v>1.77</v>
       </c>
       <c r="I49" t="inlineStr">
         <is>
@@ -2641,27 +2641,27 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>FIRF GERAES 30</t>
+          <t>MANACA INFRA</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>LFSC190054I</t>
+          <t>LFSC190054D</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>BRBNBRLFI039</t>
+          <t>BRBNBRLFI021</t>
         </is>
       </c>
       <c r="F50" t="inlineStr"/>
       <c r="G50" t="inlineStr">
         <is>
-          <t>2024-06-12 00:00:00</t>
+          <t>2024-06-11 00:00:00</t>
         </is>
       </c>
       <c r="H50" t="n">
-        <v>1.65</v>
+        <v>1.77</v>
       </c>
       <c r="I50" t="inlineStr">
         <is>
@@ -2685,7 +2685,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>HORIZONTE FIM</t>
+          <t>FIRF GERAES 30</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -2705,7 +2705,7 @@
         </is>
       </c>
       <c r="H51" t="n">
-        <v>1.65</v>
+        <v>1.77</v>
       </c>
       <c r="I51" t="inlineStr">
         <is>
@@ -2734,12 +2734,12 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>LFSC190059S</t>
+          <t>LFSC190054I</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>BRBNBRLFI062</t>
+          <t>BRBNBRLFI039</t>
         </is>
       </c>
       <c r="F52" t="inlineStr"/>
@@ -2749,7 +2749,7 @@
         </is>
       </c>
       <c r="H52" t="n">
-        <v>1.65</v>
+        <v>1.77</v>
       </c>
       <c r="I52" t="inlineStr">
         <is>
@@ -2773,27 +2773,27 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>FIRF GERAES 30</t>
+          <t>HORIZONTE FIM</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>LFSC19005FF</t>
+          <t>LFSC190059S</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>BRBNBRLFI0C5</t>
+          <t>BRBNBRLFI062</t>
         </is>
       </c>
       <c r="F53" t="inlineStr"/>
       <c r="G53" t="inlineStr">
         <is>
-          <t>2024-06-18 00:00:00</t>
+          <t>2024-06-12 00:00:00</t>
         </is>
       </c>
       <c r="H53" t="n">
-        <v>1.65</v>
+        <v>1.77</v>
       </c>
       <c r="I53" t="inlineStr">
         <is>
@@ -2817,7 +2817,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>HORIZONTE FIM</t>
+          <t>FIRF GERAES 30</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -2837,7 +2837,7 @@
         </is>
       </c>
       <c r="H54" t="n">
-        <v>1.65</v>
+        <v>1.77</v>
       </c>
       <c r="I54" t="inlineStr">
         <is>
@@ -2866,22 +2866,22 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>LFSC19005L1</t>
+          <t>LFSC19005FF</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>BRBNBRLFI0F8</t>
+          <t>BRBNBRLFI0C5</t>
         </is>
       </c>
       <c r="F55" t="inlineStr"/>
       <c r="G55" t="inlineStr">
         <is>
-          <t>2024-06-19 00:00:00</t>
+          <t>2024-06-18 00:00:00</t>
         </is>
       </c>
       <c r="H55" t="n">
-        <v>1.65</v>
+        <v>1.77</v>
       </c>
       <c r="I55" t="inlineStr">
         <is>
@@ -2905,27 +2905,27 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>BH INFRA</t>
+          <t>HORIZONTE FIM</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>LFSC19005L3</t>
+          <t>LFSC19005L1</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>BRBNBRLFI0G6</t>
+          <t>BRBNBRLFI0F8</t>
         </is>
       </c>
       <c r="F56" t="inlineStr"/>
       <c r="G56" t="inlineStr">
         <is>
-          <t>2024-06-21 00:00:00</t>
+          <t>2024-06-19 00:00:00</t>
         </is>
       </c>
       <c r="H56" t="n">
-        <v>1.65</v>
+        <v>1.77</v>
       </c>
       <c r="I56" t="inlineStr">
         <is>
@@ -2949,7 +2949,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>FIRF GERAES 30</t>
+          <t>BH INFRA</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -2969,7 +2969,7 @@
         </is>
       </c>
       <c r="H57" t="n">
-        <v>1.65</v>
+        <v>1.77</v>
       </c>
       <c r="I57" t="inlineStr">
         <is>
@@ -2988,7 +2988,7 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>BANCO ABC BRASIL S.A.</t>
+          <t>BANCO DO NORDESTE DO BRASIL S.A.</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -2998,22 +2998,22 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>LFSC19007G2</t>
+          <t>LFSC19005L3</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>BRABCBLFIM30</t>
+          <t>BRBNBRLFI0G6</t>
         </is>
       </c>
       <c r="F58" t="inlineStr"/>
       <c r="G58" t="inlineStr">
         <is>
-          <t>2024-10-17 00:00:00</t>
+          <t>2024-06-21 00:00:00</t>
         </is>
       </c>
       <c r="H58" t="n">
-        <v>0.004631489999999999</v>
+        <v>1.77</v>
       </c>
       <c r="I58" t="inlineStr">
         <is>
@@ -3027,37 +3027,41 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>LFSN</t>
+          <t>LFSC</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>BANCO SAFRA S.A.</t>
+          <t>BANCO ABC BRASIL S.A.</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>BH INFRA</t>
+          <t>FIRF GERAES 30</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>LFSN1800D4W</t>
-        </is>
-      </c>
-      <c r="E59" t="inlineStr"/>
+          <t>LFSC19007G2</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>BRABCBLFIM30</t>
+        </is>
+      </c>
       <c r="F59" t="inlineStr"/>
       <c r="G59" t="inlineStr">
         <is>
-          <t>2026-06-08 00:00:00</t>
+          <t>2024-10-17 00:00:00</t>
         </is>
       </c>
       <c r="H59" t="n">
-        <v>1.015982556066905</v>
+        <v>0.00450832</v>
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>MATRIZ</t>
+          <t>ISIN</t>
         </is>
       </c>
       <c r="J59" t="b">
@@ -3072,32 +3076,32 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>BANCO BRADESCO S.A.</t>
+          <t>BANCO SAFRA S.A.</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>CARMEL INFRA</t>
+          <t>BH INFRA</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>LFSN1800DG1</t>
+          <t>LFSN1800D4W</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>BRBBDCLTR2X9</t>
+          <t>BRBMGBLFI6I3</t>
         </is>
       </c>
       <c r="F60" t="inlineStr"/>
       <c r="G60" t="inlineStr">
         <is>
-          <t>2026-08-03 00:00:00</t>
+          <t>2026-06-08 00:00:00</t>
         </is>
       </c>
       <c r="H60" t="n">
-        <v>1.011717717542436</v>
+        <v>1.015964370154562</v>
       </c>
       <c r="I60" t="inlineStr">
         <is>
@@ -3121,7 +3125,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>JERA2026</t>
+          <t>CARMEL INFRA</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -3134,18 +3138,14 @@
           <t>BRBBDCLTR2X9</t>
         </is>
       </c>
-      <c r="F61" t="inlineStr">
-        <is>
-          <t>407137-LFS</t>
-        </is>
-      </c>
+      <c r="F61" t="inlineStr"/>
       <c r="G61" t="inlineStr">
         <is>
           <t>2026-08-03 00:00:00</t>
         </is>
       </c>
       <c r="H61" t="n">
-        <v>1.011717717542436</v>
+        <v>1.003</v>
       </c>
       <c r="I61" t="inlineStr">
         <is>
@@ -3169,31 +3169,35 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>FIRF GERAES</t>
+          <t>JERA2026</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>LFSN1800DIG</t>
+          <t>LFSN1800DG1</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>BRBBDCLTROH4</t>
-        </is>
-      </c>
-      <c r="F62" t="inlineStr"/>
+          <t>BRBBDCLTR2X9</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>407137-LFS</t>
+        </is>
+      </c>
       <c r="G62" t="inlineStr">
         <is>
           <t>2026-08-03 00:00:00</t>
         </is>
       </c>
       <c r="H62" t="n">
-        <v>1.02361</v>
+        <v>1.003</v>
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>ISIN</t>
+          <t>MATRIZ</t>
         </is>
       </c>
       <c r="J62" t="b">
@@ -3208,32 +3212,32 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>BANCO SAFRA S.A.</t>
+          <t>BANCO BRADESCO S.A.</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>BORDEAUX INFRA</t>
+          <t>FIRF GERAES</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>LFSN1800DS5</t>
+          <t>LFSN1800DIG</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>BRBSAFLNN8B3</t>
+          <t>BRBBDCLTROH4</t>
         </is>
       </c>
       <c r="F63" t="inlineStr"/>
       <c r="G63" t="inlineStr">
         <is>
-          <t>2026-08-17 00:00:00</t>
+          <t>2026-08-03 00:00:00</t>
         </is>
       </c>
       <c r="H63" t="n">
-        <v>1.02462</v>
+        <v>1.022904</v>
       </c>
       <c r="I63" t="inlineStr">
         <is>
@@ -3257,7 +3261,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>CARMEL INFRA</t>
+          <t>BORDEAUX INFRA</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -3277,11 +3281,11 @@
         </is>
       </c>
       <c r="H64" t="n">
-        <v>1.015989988663004</v>
+        <v>1.02462</v>
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>MATRIZ</t>
+          <t>ISIN</t>
         </is>
       </c>
       <c r="J64" t="b">
@@ -3301,7 +3305,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>JERA2026</t>
+          <t>CARMEL INFRA</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -3314,18 +3318,14 @@
           <t>BRBSAFLNN8B3</t>
         </is>
       </c>
-      <c r="F65" t="inlineStr">
-        <is>
-          <t>335769-LFS</t>
-        </is>
-      </c>
+      <c r="F65" t="inlineStr"/>
       <c r="G65" t="inlineStr">
         <is>
           <t>2026-08-17 00:00:00</t>
         </is>
       </c>
       <c r="H65" t="n">
-        <v>1.015989988663004</v>
+        <v>1.015974093275516</v>
       </c>
       <c r="I65" t="inlineStr">
         <is>
@@ -3344,36 +3344,40 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>BANCO ABC BRASIL S.A.</t>
+          <t>BANCO SAFRA S.A.</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>FIRF GERAES</t>
+          <t>JERA2026</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>LFSN1800E2G</t>
+          <t>LFSN1800DS5</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>BRABCBLFIM22</t>
-        </is>
-      </c>
-      <c r="F66" t="inlineStr"/>
+          <t>BRBSAFLNN8B3</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>335769-LFS</t>
+        </is>
+      </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>2025-09-29 00:00:00</t>
+          <t>2026-08-17 00:00:00</t>
         </is>
       </c>
       <c r="H66" t="n">
-        <v>0.004631489999999999</v>
+        <v>1.015974093275516</v>
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>ISIN</t>
+          <t>MATRIZ</t>
         </is>
       </c>
       <c r="J66" t="b">
@@ -3388,7 +3392,7 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>BANCO SAFRA S.A.</t>
+          <t>BANCO ABC BRASIL S.A.</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
@@ -3398,22 +3402,22 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>LFSN1800HXO</t>
+          <t>LFSN1800E2G</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>BRBSAFLNN7R1</t>
+          <t>BRABCBLFIM22</t>
         </is>
       </c>
       <c r="F67" t="inlineStr"/>
       <c r="G67" t="inlineStr">
         <is>
-          <t>2026-11-06 00:00:00</t>
+          <t>2025-09-29 00:00:00</t>
         </is>
       </c>
       <c r="H67" t="n">
-        <v>1.032666</v>
+        <v>0.00450832</v>
       </c>
       <c r="I67" t="inlineStr">
         <is>
@@ -3442,22 +3446,22 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>LFSN1900008</t>
+          <t>LFSN1800HXO</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>BRBSAFLFNBB5</t>
+          <t>BRBSAFLNN7R1</t>
         </is>
       </c>
       <c r="F68" t="inlineStr"/>
       <c r="G68" t="inlineStr">
         <is>
-          <t>2027-01-08 00:00:00</t>
+          <t>2026-11-06 00:00:00</t>
         </is>
       </c>
       <c r="H68" t="n">
-        <v>1.03773</v>
+        <v>1.030045</v>
       </c>
       <c r="I68" t="inlineStr">
         <is>
@@ -3476,36 +3480,36 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>BANCO BTG PACTUAL S.A.</t>
+          <t>BANCO SAFRA S.A.</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>CARMEL INFRA</t>
+          <t>FIRF GERAES</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>LFSN19001BC</t>
+          <t>LFSN1900008</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>BRBPACLFIVQ4</t>
+          <t>BRBSAFLFNBB5</t>
         </is>
       </c>
       <c r="F69" t="inlineStr"/>
       <c r="G69" t="inlineStr">
         <is>
-          <t>2027-04-09 00:00:00</t>
+          <t>2027-01-08 00:00:00</t>
         </is>
       </c>
       <c r="H69" t="n">
-        <v>1.050497965289035</v>
+        <v>1.035227</v>
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>MATRIZ</t>
+          <t>ISIN</t>
         </is>
       </c>
       <c r="J69" t="b">
@@ -3525,7 +3529,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>JERA2026</t>
+          <t>CARMEL INFRA</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -3538,18 +3542,14 @@
           <t>BRBPACLFIVQ4</t>
         </is>
       </c>
-      <c r="F70" t="inlineStr">
-        <is>
-          <t>353997-N L</t>
-        </is>
-      </c>
+      <c r="F70" t="inlineStr"/>
       <c r="G70" t="inlineStr">
         <is>
           <t>2027-04-09 00:00:00</t>
         </is>
       </c>
       <c r="H70" t="n">
-        <v>1.050497965289035</v>
+        <v>1.04956988070436</v>
       </c>
       <c r="I70" t="inlineStr">
         <is>
@@ -3573,12 +3573,12 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>BH INFRA</t>
+          <t>JERA2026</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>LFSN19001BH</t>
+          <t>LFSN19001BC</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
@@ -3586,18 +3586,22 @@
           <t>BRBPACLFIVQ4</t>
         </is>
       </c>
-      <c r="F71" t="inlineStr"/>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>353997-N L</t>
+        </is>
+      </c>
       <c r="G71" t="inlineStr">
         <is>
           <t>2027-04-09 00:00:00</t>
         </is>
       </c>
       <c r="H71" t="n">
-        <v>1.039847</v>
+        <v>1.04956988070436</v>
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>ISIN</t>
+          <t>MATRIZ</t>
         </is>
       </c>
       <c r="J71" t="b">
@@ -3617,27 +3621,27 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>FIRF GERAES 30</t>
+          <t>BH INFRA</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>LFSN19006KM</t>
+          <t>LFSN19001BH</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>BRBPACLFIWC2</t>
+          <t>BRBPACLFIVQ4</t>
         </is>
       </c>
       <c r="F72" t="inlineStr"/>
       <c r="G72" t="inlineStr">
         <is>
-          <t>2028-05-31 00:00:00</t>
+          <t>2027-04-09 00:00:00</t>
         </is>
       </c>
       <c r="H72" t="n">
-        <v>1.053379</v>
+        <v>1.038705</v>
       </c>
       <c r="I72" t="inlineStr">
         <is>
@@ -3661,7 +3665,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>HORIZONTE FIM</t>
+          <t>FIRF GERAES 30</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -3681,7 +3685,7 @@
         </is>
       </c>
       <c r="H73" t="n">
-        <v>1.053379</v>
+        <v>1.052538</v>
       </c>
       <c r="I73" t="inlineStr">
         <is>
@@ -3705,7 +3709,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>MANACA INFRA</t>
+          <t>HORIZONTE FIM</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -3725,7 +3729,7 @@
         </is>
       </c>
       <c r="H74" t="n">
-        <v>1.053379</v>
+        <v>1.052538</v>
       </c>
       <c r="I74" t="inlineStr">
         <is>
@@ -3749,7 +3753,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>REAL FIM</t>
+          <t>MANACA INFRA</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -3762,22 +3766,18 @@
           <t>BRBPACLFIWC2</t>
         </is>
       </c>
-      <c r="F75" t="inlineStr">
-        <is>
-          <t>513453-LFS</t>
-        </is>
-      </c>
+      <c r="F75" t="inlineStr"/>
       <c r="G75" t="inlineStr">
         <is>
           <t>2028-05-31 00:00:00</t>
         </is>
       </c>
       <c r="H75" t="n">
-        <v>1.064916450955605</v>
+        <v>1.052538</v>
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>MATRIZ</t>
+          <t>ISIN</t>
         </is>
       </c>
       <c r="J75" t="b">
@@ -3797,12 +3797,12 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>FIRF GERAES</t>
+          <t>REAL FIM</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>LFSN19006KN</t>
+          <t>LFSN19006KM</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
@@ -3810,18 +3810,22 @@
           <t>BRBPACLFIWC2</t>
         </is>
       </c>
-      <c r="F76" t="inlineStr"/>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>513453-LFS</t>
+        </is>
+      </c>
       <c r="G76" t="inlineStr">
         <is>
           <t>2028-05-31 00:00:00</t>
         </is>
       </c>
       <c r="H76" t="n">
-        <v>1.053379</v>
+        <v>1.064335532557892</v>
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>ISIN</t>
+          <t>MATRIZ</t>
         </is>
       </c>
       <c r="J76" t="b">
@@ -3836,32 +3840,32 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>BANCO BMG S.A.</t>
+          <t>BANCO BTG PACTUAL S.A.</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>BH INFRA</t>
+          <t>FIRF GERAES</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>LFSN1900971</t>
+          <t>LFSN19006KN</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>BRBMGBLFI489</t>
+          <t>BRBPACLFIWC2</t>
         </is>
       </c>
       <c r="F77" t="inlineStr"/>
       <c r="G77" t="inlineStr">
         <is>
-          <t>2026-06-22 00:00:00</t>
+          <t>2028-05-31 00:00:00</t>
         </is>
       </c>
       <c r="H77" t="n">
-        <v>1.200691</v>
+        <v>1.052538</v>
       </c>
       <c r="I77" t="inlineStr">
         <is>
@@ -3885,7 +3889,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>BORDEAUX INFRA</t>
+          <t>BH INFRA</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -3929,7 +3933,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>FIRF GERAES 30</t>
+          <t>BORDEAUX INFRA</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -3973,7 +3977,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>FIRF GERAES</t>
+          <t>FIRF GERAES 30</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -4017,27 +4021,27 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>BH INFRA</t>
+          <t>FIRF GERAES</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>LFSN19009YU</t>
+          <t>LFSN1900971</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>BRBMGBLFI6I3</t>
+          <t>BRBMGBLFI489</t>
         </is>
       </c>
       <c r="F81" t="inlineStr"/>
       <c r="G81" t="inlineStr">
         <is>
-          <t>2026-06-26 00:00:00</t>
+          <t>2026-06-22 00:00:00</t>
         </is>
       </c>
       <c r="H81" t="n">
-        <v>1.204881</v>
+        <v>1.200691</v>
       </c>
       <c r="I81" t="inlineStr">
         <is>
@@ -4061,7 +4065,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>FIRF GERAES</t>
+          <t>BH INFRA</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -4081,11 +4085,11 @@
         </is>
       </c>
       <c r="H82" t="n">
-        <v>1.204881</v>
+        <v>1.118375923140385</v>
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>ISIN</t>
+          <t>MATRIZ</t>
         </is>
       </c>
       <c r="J82" t="b">
@@ -4100,36 +4104,32 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>BANCO SAFRA S.A.</t>
+          <t>BANCO BMG S.A.</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>FIRF GERAES 30</t>
+          <t>CARMEL INFRA</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>LFSN1900CR5</t>
-        </is>
-      </c>
-      <c r="E83" t="inlineStr">
-        <is>
-          <t>BRBSAFLFNG47</t>
-        </is>
-      </c>
+          <t>LFSN19009YU</t>
+        </is>
+      </c>
+      <c r="E83" t="inlineStr"/>
       <c r="F83" t="inlineStr"/>
       <c r="G83" t="inlineStr">
         <is>
-          <t>2029-08-13 00:00:00</t>
+          <t>2026-06-26 00:00:00</t>
         </is>
       </c>
       <c r="H83" t="n">
-        <v>1.093356</v>
+        <v>1.118375923140385</v>
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t>ISIN</t>
+          <t>MATRIZ</t>
         </is>
       </c>
       <c r="J83" t="b">
@@ -4139,45 +4139,41 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>CDB</t>
+          <t>LFSN</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>AGIBANK</t>
+          <t>BANCO BMG S.A.</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>BMG SEG</t>
+          <t>FIRF GERAES</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>CDB3251WXH0</t>
+          <t>LFSN19009YU</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>BRAGBKC00M66</t>
-        </is>
-      </c>
-      <c r="F84" t="inlineStr">
-        <is>
-          <t>614522-CDB</t>
-        </is>
-      </c>
+          <t>BRBMGBLFI6I3</t>
+        </is>
+      </c>
+      <c r="F84" t="inlineStr"/>
       <c r="G84" t="inlineStr">
         <is>
-          <t>2027-03-08 00:00:00</t>
+          <t>2026-06-26 00:00:00</t>
         </is>
       </c>
       <c r="H84" t="n">
-        <v>1.062862511354904</v>
+        <v>1.200691</v>
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t>MATRIZ</t>
+          <t>ISIN</t>
         </is>
       </c>
       <c r="J84" t="b">
@@ -4187,45 +4183,41 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>CDB</t>
+          <t>LFSN</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>AGIBANK</t>
+          <t>BANCO SAFRA S.A.</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>JERA2026</t>
+          <t>FIRF GERAES 30</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>CDB3251WXH0</t>
+          <t>LFSN1900CR5</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>BRAGBKC00M66</t>
-        </is>
-      </c>
-      <c r="F85" t="inlineStr">
-        <is>
-          <t>353997-N L</t>
-        </is>
-      </c>
+          <t>BRBSAFLFNG47</t>
+        </is>
+      </c>
+      <c r="F85" t="inlineStr"/>
       <c r="G85" t="inlineStr">
         <is>
-          <t>2027-03-08 00:00:00</t>
+          <t>2029-08-13 00:00:00</t>
         </is>
       </c>
       <c r="H85" t="n">
-        <v>1.062862511354904</v>
+        <v>1.092185</v>
       </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t>MATRIZ</t>
+          <t>ISIN</t>
         </is>
       </c>
       <c r="J85" t="b">
@@ -4245,7 +4237,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>REAL FIM</t>
+          <t>BMG SEG</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -4260,7 +4252,7 @@
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>353997-N L</t>
+          <t>614522-CDB</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
@@ -4269,7 +4261,7 @@
         </is>
       </c>
       <c r="H86" t="n">
-        <v>1.062862511354904</v>
+        <v>1.062308713517584</v>
       </c>
       <c r="I86" t="inlineStr">
         <is>
@@ -4288,36 +4280,36 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>BANCO XP</t>
+          <t>AGIBANK</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>BMG SEG</t>
+          <t>JERA2026</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>LF00240072E</t>
+          <t>CDB3251WXH0</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>BRBCXPLFIKS5</t>
+          <t>BRAGBKC00M66</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>614522-CDB</t>
+          <t>353997-N L</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>2026-03-02 00:00:00</t>
+          <t>2027-03-08 00:00:00</t>
         </is>
       </c>
       <c r="H87" t="n">
-        <v>1.0225</v>
+        <v>1.062308713517584</v>
       </c>
       <c r="I87" t="inlineStr">
         <is>
@@ -4336,22 +4328,22 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>BANCO XP</t>
+          <t>AGIBANK</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>JERA2026</t>
+          <t>REAL FIM</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>LF00240072E</t>
+          <t>CDB3251WXH0</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>BRBCXPLFIKS5</t>
+          <t>BRAGBKC00M66</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
@@ -4361,11 +4353,11 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>2026-03-02 00:00:00</t>
+          <t>2027-03-08 00:00:00</t>
         </is>
       </c>
       <c r="H88" t="n">
-        <v>1.0225</v>
+        <v>1.062308713517584</v>
       </c>
       <c r="I88" t="inlineStr">
         <is>
@@ -4384,36 +4376,36 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>BANCO BMG S.A.</t>
+          <t>BANCO XP</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>JERA2026</t>
+          <t>BMG SEG</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>LFSC19002CD</t>
+          <t>LF00240072E</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>BRBMGBLFI7Q4</t>
+          <t>BRBCXPLFIKS5</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>609712-LFS</t>
+          <t>614522-CDB</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>2029-04-09 00:00:00</t>
+          <t>2026-03-02 00:00:00</t>
         </is>
       </c>
       <c r="H89" t="n">
-        <v>1.144378917056012</v>
+        <v>1.0225</v>
       </c>
       <c r="I89" t="inlineStr">
         <is>
@@ -4432,7 +4424,7 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>BANCO BMG S.A.</t>
+          <t>BANCO XP</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
@@ -4442,26 +4434,26 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>LFSC19002CE</t>
+          <t>LF00240072E</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>BRBMGBLFI7P6</t>
+          <t>BRBCXPLFIKS5</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>609711-LFS</t>
+          <t>353997-N L</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>2029-04-09 00:00:00</t>
+          <t>2026-03-02 00:00:00</t>
         </is>
       </c>
       <c r="H90" t="n">
-        <v>1.144378917056012</v>
+        <v>1.0225</v>
       </c>
       <c r="I90" t="inlineStr">
         <is>
@@ -4490,33 +4482,129 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
+          <t>LFSC19002CD</t>
+        </is>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>BRBMGBLFI7Q4</t>
+        </is>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>609712-LFS</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>2029-04-09 00:00:00</t>
+        </is>
+      </c>
+      <c r="H91" t="n">
+        <v>1.143387612258942</v>
+      </c>
+      <c r="I91" t="inlineStr">
+        <is>
+          <t>MATRIZ</t>
+        </is>
+      </c>
+      <c r="J91" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>CDB</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>BANCO BMG S.A.</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>JERA2026</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>LFSC19002CE</t>
+        </is>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>BRBMGBLFI7P6</t>
+        </is>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>609711-LFS</t>
+        </is>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>2029-04-09 00:00:00</t>
+        </is>
+      </c>
+      <c r="H92" t="n">
+        <v>1.143387612258942</v>
+      </c>
+      <c r="I92" t="inlineStr">
+        <is>
+          <t>MATRIZ</t>
+        </is>
+      </c>
+      <c r="J92" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>CDB</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>BANCO BMG S.A.</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>JERA2026</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
           <t>LFSC19002HS</t>
         </is>
       </c>
-      <c r="E91" t="inlineStr">
+      <c r="E93" t="inlineStr">
         <is>
           <t>BRBMGBLFI7R2</t>
         </is>
       </c>
-      <c r="F91" t="inlineStr">
+      <c r="F93" t="inlineStr">
         <is>
           <t>609713-LFS</t>
         </is>
       </c>
-      <c r="G91" t="inlineStr">
+      <c r="G93" t="inlineStr">
         <is>
           <t>2029-04-09 00:00:00</t>
         </is>
       </c>
-      <c r="H91" t="n">
-        <v>1.144378917056012</v>
-      </c>
-      <c r="I91" t="inlineStr">
+      <c r="H93" t="n">
+        <v>1.143387612258942</v>
+      </c>
+      <c r="I93" t="inlineStr">
         <is>
           <t>MATRIZ</t>
         </is>
       </c>
-      <c r="J91" t="b">
+      <c r="J93" t="b">
         <v>0</v>
       </c>
     </row>

--- a/Dados/ativos_mapeados_com_taxa_efetiva.xlsx
+++ b/Dados/ativos_mapeados_com_taxa_efetiva.xlsx
@@ -4117,7 +4117,11 @@
           <t>LFSN19009YU</t>
         </is>
       </c>
-      <c r="E83" t="inlineStr"/>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>BRBMGBLFI6I3</t>
+        </is>
+      </c>
       <c r="F83" t="inlineStr"/>
       <c r="G83" t="inlineStr">
         <is>

--- a/Dados/ativos_mapeados_com_taxa_efetiva.xlsx
+++ b/Dados/ativos_mapeados_com_taxa_efetiva.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J93"/>
+  <dimension ref="A1:J94"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -645,7 +645,7 @@
         </is>
       </c>
       <c r="H5" t="n">
-        <v>1.062308713517584</v>
+        <v>1.062225867980001</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
@@ -689,7 +689,7 @@
         </is>
       </c>
       <c r="H6" t="n">
-        <v>1.062308713517584</v>
+        <v>1.062225867980001</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
@@ -865,7 +865,7 @@
         </is>
       </c>
       <c r="H10" t="n">
-        <v>1.03139917489967</v>
+        <v>1.031363574402692</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
@@ -909,7 +909,7 @@
         </is>
       </c>
       <c r="H11" t="n">
-        <v>1.03139917489967</v>
+        <v>1.031363574402692</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
@@ -953,7 +953,7 @@
         </is>
       </c>
       <c r="H12" t="n">
-        <v>1.03139917489967</v>
+        <v>1.031363574402692</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
@@ -1001,7 +1001,7 @@
         </is>
       </c>
       <c r="H13" t="n">
-        <v>1.03139917489967</v>
+        <v>1.031363574402692</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
@@ -1045,7 +1045,7 @@
         </is>
       </c>
       <c r="H14" t="n">
-        <v>1.03139917489967</v>
+        <v>1.031363574402692</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
@@ -1093,7 +1093,7 @@
         </is>
       </c>
       <c r="H15" t="n">
-        <v>1.03139917489967</v>
+        <v>1.031363574402692</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
@@ -1229,7 +1229,7 @@
         </is>
       </c>
       <c r="H18" t="n">
-        <v>1.026450628376097</v>
+        <v>1.026416579612311</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
@@ -1365,7 +1365,7 @@
         </is>
       </c>
       <c r="H21" t="n">
-        <v>1.026450628376097</v>
+        <v>1.026416579612311</v>
       </c>
       <c r="I21" t="inlineStr">
         <is>
@@ -2169,7 +2169,7 @@
         </is>
       </c>
       <c r="H39" t="n">
-        <v>1.052475915166362</v>
+        <v>1.052473999350764</v>
       </c>
       <c r="I39" t="inlineStr">
         <is>
@@ -2217,7 +2217,7 @@
         </is>
       </c>
       <c r="H40" t="n">
-        <v>1.052475915166362</v>
+        <v>1.052473999350764</v>
       </c>
       <c r="I40" t="inlineStr">
         <is>
@@ -2265,7 +2265,7 @@
         </is>
       </c>
       <c r="H41" t="n">
-        <v>1.052475915166362</v>
+        <v>1.052473999350764</v>
       </c>
       <c r="I41" t="inlineStr">
         <is>
@@ -3091,7 +3091,7 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>BRBMGBLFI6I3</t>
+          <t>BRBSAFLNND73</t>
         </is>
       </c>
       <c r="F60" t="inlineStr"/>
@@ -3101,11 +3101,11 @@
         </is>
       </c>
       <c r="H60" t="n">
-        <v>1.015964370154562</v>
+        <v>0.147021202949582</v>
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>MATRIZ</t>
+          <t>ISIN</t>
         </is>
       </c>
       <c r="J60" t="b">
@@ -3120,32 +3120,28 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>BANCO BRADESCO S.A.</t>
+          <t>BANCO SAFRA S.A.</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>CARMEL INFRA</t>
+          <t>BH INFRA</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>LFSN1800DG1</t>
-        </is>
-      </c>
-      <c r="E61" t="inlineStr">
-        <is>
-          <t>BRBBDCLTR2X9</t>
-        </is>
-      </c>
+          <t>LFSN1800D4W</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr"/>
       <c r="F61" t="inlineStr"/>
       <c r="G61" t="inlineStr">
         <is>
-          <t>2026-08-03 00:00:00</t>
+          <t>2026-08-06 00:00:00</t>
         </is>
       </c>
       <c r="H61" t="n">
-        <v>1.003</v>
+        <v>1.01583554041482</v>
       </c>
       <c r="I61" t="inlineStr">
         <is>
@@ -3169,7 +3165,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>JERA2026</t>
+          <t>CARMEL INFRA</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -3182,11 +3178,7 @@
           <t>BRBBDCLTR2X9</t>
         </is>
       </c>
-      <c r="F62" t="inlineStr">
-        <is>
-          <t>407137-LFS</t>
-        </is>
-      </c>
+      <c r="F62" t="inlineStr"/>
       <c r="G62" t="inlineStr">
         <is>
           <t>2026-08-03 00:00:00</t>
@@ -3217,31 +3209,35 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>FIRF GERAES</t>
+          <t>JERA2026</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>LFSN1800DIG</t>
+          <t>LFSN1800DG1</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>BRBBDCLTROH4</t>
-        </is>
-      </c>
-      <c r="F63" t="inlineStr"/>
+          <t>BRBBDCLTR2X9</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>407137-LFS</t>
+        </is>
+      </c>
       <c r="G63" t="inlineStr">
         <is>
           <t>2026-08-03 00:00:00</t>
         </is>
       </c>
       <c r="H63" t="n">
-        <v>1.022904</v>
+        <v>1.003</v>
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>ISIN</t>
+          <t>MATRIZ</t>
         </is>
       </c>
       <c r="J63" t="b">
@@ -3256,32 +3252,32 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>BANCO SAFRA S.A.</t>
+          <t>BANCO BRADESCO S.A.</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>BORDEAUX INFRA</t>
+          <t>FIRF GERAES</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>LFSN1800DS5</t>
+          <t>LFSN1800DIG</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>BRBSAFLNN8B3</t>
+          <t>BRBBDCLTROH4</t>
         </is>
       </c>
       <c r="F64" t="inlineStr"/>
       <c r="G64" t="inlineStr">
         <is>
-          <t>2026-08-17 00:00:00</t>
+          <t>2026-08-03 00:00:00</t>
         </is>
       </c>
       <c r="H64" t="n">
-        <v>1.02462</v>
+        <v>1.022904</v>
       </c>
       <c r="I64" t="inlineStr">
         <is>
@@ -3305,7 +3301,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>CARMEL INFRA</t>
+          <t>BORDEAUX INFRA</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -3325,11 +3321,11 @@
         </is>
       </c>
       <c r="H65" t="n">
-        <v>1.015974093275516</v>
+        <v>1.02462</v>
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>MATRIZ</t>
+          <t>ISIN</t>
         </is>
       </c>
       <c r="J65" t="b">
@@ -3349,7 +3345,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>JERA2026</t>
+          <t>CARMEL INFRA</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -3362,18 +3358,14 @@
           <t>BRBSAFLNN8B3</t>
         </is>
       </c>
-      <c r="F66" t="inlineStr">
-        <is>
-          <t>335769-LFS</t>
-        </is>
-      </c>
+      <c r="F66" t="inlineStr"/>
       <c r="G66" t="inlineStr">
         <is>
           <t>2026-08-17 00:00:00</t>
         </is>
       </c>
       <c r="H66" t="n">
-        <v>1.015974093275516</v>
+        <v>1.015971455536625</v>
       </c>
       <c r="I66" t="inlineStr">
         <is>
@@ -3392,36 +3384,40 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>BANCO ABC BRASIL S.A.</t>
+          <t>BANCO SAFRA S.A.</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>FIRF GERAES</t>
+          <t>JERA2026</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>LFSN1800E2G</t>
+          <t>LFSN1800DS5</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>BRABCBLFIM22</t>
-        </is>
-      </c>
-      <c r="F67" t="inlineStr"/>
+          <t>BRBSAFLNN8B3</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>335769-LFS</t>
+        </is>
+      </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>2025-09-29 00:00:00</t>
+          <t>2026-08-17 00:00:00</t>
         </is>
       </c>
       <c r="H67" t="n">
-        <v>0.00450832</v>
+        <v>1.015971455536625</v>
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>ISIN</t>
+          <t>MATRIZ</t>
         </is>
       </c>
       <c r="J67" t="b">
@@ -3436,7 +3432,7 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>BANCO SAFRA S.A.</t>
+          <t>BANCO ABC BRASIL S.A.</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
@@ -3446,22 +3442,22 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>LFSN1800HXO</t>
+          <t>LFSN1800E2G</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>BRBSAFLNN7R1</t>
+          <t>BRABCBLFIM22</t>
         </is>
       </c>
       <c r="F68" t="inlineStr"/>
       <c r="G68" t="inlineStr">
         <is>
-          <t>2026-11-06 00:00:00</t>
+          <t>2025-09-29 00:00:00</t>
         </is>
       </c>
       <c r="H68" t="n">
-        <v>1.030045</v>
+        <v>0.00450832</v>
       </c>
       <c r="I68" t="inlineStr">
         <is>
@@ -3490,22 +3486,22 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>LFSN1900008</t>
+          <t>LFSN1800HXO</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>BRBSAFLFNBB5</t>
+          <t>BRBSAFLNN7R1</t>
         </is>
       </c>
       <c r="F69" t="inlineStr"/>
       <c r="G69" t="inlineStr">
         <is>
-          <t>2027-01-08 00:00:00</t>
+          <t>2026-11-06 00:00:00</t>
         </is>
       </c>
       <c r="H69" t="n">
-        <v>1.035227</v>
+        <v>1.030045</v>
       </c>
       <c r="I69" t="inlineStr">
         <is>
@@ -3524,36 +3520,36 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>BANCO BTG PACTUAL S.A.</t>
+          <t>BANCO SAFRA S.A.</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>CARMEL INFRA</t>
+          <t>FIRF GERAES</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>LFSN19001BC</t>
+          <t>LFSN1900008</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>BRBPACLFIVQ4</t>
+          <t>BRBSAFLFNBB5</t>
         </is>
       </c>
       <c r="F70" t="inlineStr"/>
       <c r="G70" t="inlineStr">
         <is>
-          <t>2027-04-09 00:00:00</t>
+          <t>2027-01-08 00:00:00</t>
         </is>
       </c>
       <c r="H70" t="n">
-        <v>1.04956988070436</v>
+        <v>1.035227</v>
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>MATRIZ</t>
+          <t>ISIN</t>
         </is>
       </c>
       <c r="J70" t="b">
@@ -3573,7 +3569,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>JERA2026</t>
+          <t>CARMEL INFRA</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -3586,18 +3582,14 @@
           <t>BRBPACLFIVQ4</t>
         </is>
       </c>
-      <c r="F71" t="inlineStr">
-        <is>
-          <t>353997-N L</t>
-        </is>
-      </c>
+      <c r="F71" t="inlineStr"/>
       <c r="G71" t="inlineStr">
         <is>
           <t>2027-04-09 00:00:00</t>
         </is>
       </c>
       <c r="H71" t="n">
-        <v>1.04956988070436</v>
+        <v>1.049431474242896</v>
       </c>
       <c r="I71" t="inlineStr">
         <is>
@@ -3621,12 +3613,12 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>BH INFRA</t>
+          <t>JERA2026</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>LFSN19001BH</t>
+          <t>LFSN19001BC</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
@@ -3634,18 +3626,22 @@
           <t>BRBPACLFIVQ4</t>
         </is>
       </c>
-      <c r="F72" t="inlineStr"/>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>353997-N L</t>
+        </is>
+      </c>
       <c r="G72" t="inlineStr">
         <is>
           <t>2027-04-09 00:00:00</t>
         </is>
       </c>
       <c r="H72" t="n">
-        <v>1.038705</v>
+        <v>1.049431474242896</v>
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>ISIN</t>
+          <t>MATRIZ</t>
         </is>
       </c>
       <c r="J72" t="b">
@@ -3665,27 +3661,27 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>FIRF GERAES 30</t>
+          <t>BH INFRA</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>LFSN19006KM</t>
+          <t>LFSN19001BH</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>BRBPACLFIWC2</t>
+          <t>BRBPACLFIVQ4</t>
         </is>
       </c>
       <c r="F73" t="inlineStr"/>
       <c r="G73" t="inlineStr">
         <is>
-          <t>2028-05-31 00:00:00</t>
+          <t>2027-04-09 00:00:00</t>
         </is>
       </c>
       <c r="H73" t="n">
-        <v>1.052538</v>
+        <v>1.038705</v>
       </c>
       <c r="I73" t="inlineStr">
         <is>
@@ -3709,7 +3705,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>HORIZONTE FIM</t>
+          <t>FIRF GERAES 30</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -3753,7 +3749,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>MANACA INFRA</t>
+          <t>HORIZONTE FIM</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -3797,7 +3793,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>REAL FIM</t>
+          <t>MANACA INFRA</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -3810,22 +3806,18 @@
           <t>BRBPACLFIWC2</t>
         </is>
       </c>
-      <c r="F76" t="inlineStr">
-        <is>
-          <t>513453-LFS</t>
-        </is>
-      </c>
+      <c r="F76" t="inlineStr"/>
       <c r="G76" t="inlineStr">
         <is>
           <t>2028-05-31 00:00:00</t>
         </is>
       </c>
       <c r="H76" t="n">
-        <v>1.064335532557892</v>
+        <v>1.052538</v>
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>MATRIZ</t>
+          <t>ISIN</t>
         </is>
       </c>
       <c r="J76" t="b">
@@ -3845,12 +3837,12 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>FIRF GERAES</t>
+          <t>REAL FIM</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>LFSN19006KN</t>
+          <t>LFSN19006KM</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
@@ -3858,18 +3850,22 @@
           <t>BRBPACLFIWC2</t>
         </is>
       </c>
-      <c r="F77" t="inlineStr"/>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>513453-LFS</t>
+        </is>
+      </c>
       <c r="G77" t="inlineStr">
         <is>
           <t>2028-05-31 00:00:00</t>
         </is>
       </c>
       <c r="H77" t="n">
-        <v>1.052538</v>
+        <v>1.064250120861257</v>
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>ISIN</t>
+          <t>MATRIZ</t>
         </is>
       </c>
       <c r="J77" t="b">
@@ -3884,32 +3880,32 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>BANCO BMG S.A.</t>
+          <t>BANCO BTG PACTUAL S.A.</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>BH INFRA</t>
+          <t>FIRF GERAES</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>LFSN1900971</t>
+          <t>LFSN19006KN</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>BRBMGBLFI489</t>
+          <t>BRBPACLFIWC2</t>
         </is>
       </c>
       <c r="F78" t="inlineStr"/>
       <c r="G78" t="inlineStr">
         <is>
-          <t>2026-06-22 00:00:00</t>
+          <t>2028-05-31 00:00:00</t>
         </is>
       </c>
       <c r="H78" t="n">
-        <v>1.200691</v>
+        <v>1.052538</v>
       </c>
       <c r="I78" t="inlineStr">
         <is>
@@ -3933,7 +3929,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>BORDEAUX INFRA</t>
+          <t>BH INFRA</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -3977,7 +3973,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>FIRF GERAES 30</t>
+          <t>BORDEAUX INFRA</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -4021,7 +4017,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>FIRF GERAES</t>
+          <t>FIRF GERAES 30</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -4065,31 +4061,31 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>BH INFRA</t>
+          <t>FIRF GERAES</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>LFSN19009YU</t>
+          <t>LFSN1900971</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>BRBMGBLFI6I3</t>
+          <t>BRBMGBLFI489</t>
         </is>
       </c>
       <c r="F82" t="inlineStr"/>
       <c r="G82" t="inlineStr">
         <is>
-          <t>2026-06-26 00:00:00</t>
+          <t>2026-06-22 00:00:00</t>
         </is>
       </c>
       <c r="H82" t="n">
-        <v>1.118375923140385</v>
+        <v>1.200691</v>
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>MATRIZ</t>
+          <t>ISIN</t>
         </is>
       </c>
       <c r="J82" t="b">
@@ -4109,7 +4105,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>CARMEL INFRA</t>
+          <t>BH INFRA</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -4129,7 +4125,7 @@
         </is>
       </c>
       <c r="H83" t="n">
-        <v>1.118375923140385</v>
+        <v>1.118351397841887</v>
       </c>
       <c r="I83" t="inlineStr">
         <is>
@@ -4153,7 +4149,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>FIRF GERAES</t>
+          <t>CARMEL INFRA</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -4173,11 +4169,11 @@
         </is>
       </c>
       <c r="H84" t="n">
-        <v>1.200691</v>
+        <v>1.118351397841887</v>
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t>ISIN</t>
+          <t>MATRIZ</t>
         </is>
       </c>
       <c r="J84" t="b">
@@ -4192,32 +4188,32 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>BANCO SAFRA S.A.</t>
+          <t>BANCO BMG S.A.</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>FIRF GERAES 30</t>
+          <t>FIRF GERAES</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>LFSN1900CR5</t>
+          <t>LFSN19009YU</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>BRBSAFLFNG47</t>
+          <t>BRBMGBLFI6I3</t>
         </is>
       </c>
       <c r="F85" t="inlineStr"/>
       <c r="G85" t="inlineStr">
         <is>
-          <t>2029-08-13 00:00:00</t>
+          <t>2026-06-26 00:00:00</t>
         </is>
       </c>
       <c r="H85" t="n">
-        <v>1.092185</v>
+        <v>1.200691</v>
       </c>
       <c r="I85" t="inlineStr">
         <is>
@@ -4231,45 +4227,41 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>CDB</t>
+          <t>LFSN</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>AGIBANK</t>
+          <t>BANCO SAFRA S.A.</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>BMG SEG</t>
+          <t>FIRF GERAES 30</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>CDB3251WXH0</t>
+          <t>LFSN1900CR5</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>BRAGBKC00M66</t>
-        </is>
-      </c>
-      <c r="F86" t="inlineStr">
-        <is>
-          <t>614522-CDB</t>
-        </is>
-      </c>
+          <t>BRBSAFLFNG47</t>
+        </is>
+      </c>
+      <c r="F86" t="inlineStr"/>
       <c r="G86" t="inlineStr">
         <is>
-          <t>2027-03-08 00:00:00</t>
+          <t>2029-08-13 00:00:00</t>
         </is>
       </c>
       <c r="H86" t="n">
-        <v>1.062308713517584</v>
+        <v>1.092185</v>
       </c>
       <c r="I86" t="inlineStr">
         <is>
-          <t>MATRIZ</t>
+          <t>ISIN</t>
         </is>
       </c>
       <c r="J86" t="b">
@@ -4289,7 +4281,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>JERA2026</t>
+          <t>BMG SEG</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -4304,7 +4296,7 @@
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>353997-N L</t>
+          <t>614522-CDB</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
@@ -4313,7 +4305,7 @@
         </is>
       </c>
       <c r="H87" t="n">
-        <v>1.062308713517584</v>
+        <v>1.062225867980001</v>
       </c>
       <c r="I87" t="inlineStr">
         <is>
@@ -4337,7 +4329,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>REAL FIM</t>
+          <t>JERA2026</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -4361,7 +4353,7 @@
         </is>
       </c>
       <c r="H88" t="n">
-        <v>1.062308713517584</v>
+        <v>1.062225867980001</v>
       </c>
       <c r="I88" t="inlineStr">
         <is>
@@ -4380,36 +4372,36 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>BANCO XP</t>
+          <t>AGIBANK</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>BMG SEG</t>
+          <t>REAL FIM</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>LF00240072E</t>
+          <t>CDB3251WXH0</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>BRBCXPLFIKS5</t>
+          <t>BRAGBKC00M66</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>614522-CDB</t>
+          <t>353997-N L</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>2026-03-02 00:00:00</t>
+          <t>2027-03-08 00:00:00</t>
         </is>
       </c>
       <c r="H89" t="n">
-        <v>1.0225</v>
+        <v>1.062225867980001</v>
       </c>
       <c r="I89" t="inlineStr">
         <is>
@@ -4433,7 +4425,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>JERA2026</t>
+          <t>BMG SEG</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -4448,7 +4440,7 @@
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>353997-N L</t>
+          <t>614522-CDB</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
@@ -4476,7 +4468,7 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>BANCO BMG S.A.</t>
+          <t>BANCO XP</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
@@ -4486,26 +4478,26 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>LFSC19002CD</t>
+          <t>LF00240072E</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>BRBMGBLFI7Q4</t>
+          <t>BRBCXPLFIKS5</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>609712-LFS</t>
+          <t>353997-N L</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>2029-04-09 00:00:00</t>
+          <t>2026-03-02 00:00:00</t>
         </is>
       </c>
       <c r="H91" t="n">
-        <v>1.143387612258942</v>
+        <v>1.0225</v>
       </c>
       <c r="I91" t="inlineStr">
         <is>
@@ -4534,17 +4526,17 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>LFSC19002CE</t>
+          <t>LFSC19002CD</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>BRBMGBLFI7P6</t>
+          <t>BRBMGBLFI7Q4</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>609711-LFS</t>
+          <t>609712-LFS</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
@@ -4553,7 +4545,7 @@
         </is>
       </c>
       <c r="H92" t="n">
-        <v>1.143387612258942</v>
+        <v>1.143243424338988</v>
       </c>
       <c r="I92" t="inlineStr">
         <is>
@@ -4582,33 +4574,81 @@
       </c>
       <c r="D93" t="inlineStr">
         <is>
+          <t>LFSC19002CE</t>
+        </is>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>BRBMGBLFI7P6</t>
+        </is>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>609711-LFS</t>
+        </is>
+      </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>2029-04-09 00:00:00</t>
+        </is>
+      </c>
+      <c r="H93" t="n">
+        <v>1.143243424338988</v>
+      </c>
+      <c r="I93" t="inlineStr">
+        <is>
+          <t>MATRIZ</t>
+        </is>
+      </c>
+      <c r="J93" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>CDB</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>BANCO BMG S.A.</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>JERA2026</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
           <t>LFSC19002HS</t>
         </is>
       </c>
-      <c r="E93" t="inlineStr">
+      <c r="E94" t="inlineStr">
         <is>
           <t>BRBMGBLFI7R2</t>
         </is>
       </c>
-      <c r="F93" t="inlineStr">
+      <c r="F94" t="inlineStr">
         <is>
           <t>609713-LFS</t>
         </is>
       </c>
-      <c r="G93" t="inlineStr">
+      <c r="G94" t="inlineStr">
         <is>
           <t>2029-04-09 00:00:00</t>
         </is>
       </c>
-      <c r="H93" t="n">
-        <v>1.143387612258942</v>
-      </c>
-      <c r="I93" t="inlineStr">
+      <c r="H94" t="n">
+        <v>1.143243424338988</v>
+      </c>
+      <c r="I94" t="inlineStr">
         <is>
           <t>MATRIZ</t>
         </is>
       </c>
-      <c r="J93" t="b">
+      <c r="J94" t="b">
         <v>0</v>
       </c>
     </row>

--- a/Dados/ativos_mapeados_com_taxa_efetiva.xlsx
+++ b/Dados/ativos_mapeados_com_taxa_efetiva.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="Z:\Asset Management\Equipe\Lívia\HedgeCDI\Projeto-Hedge-CDI\Dados\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A0980315-A43E-42CA-A52D-7E2089A8A461}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EF825533-F100-4356-9575-A70D95CD50D8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="20370" yWindow="-1260" windowWidth="21840" windowHeight="13020" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="taxa_efetiva" sheetId="1" r:id="rId1"/>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="682" uniqueCount="175">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="668" uniqueCount="171">
   <si>
     <t>Sub Classe</t>
   </si>
@@ -391,18 +391,6 @@
   </si>
   <si>
     <t>BANCO SAFRA S.A.</t>
-  </si>
-  <si>
-    <t>LFSN1800D4W</t>
-  </si>
-  <si>
-    <t>BRBSAFLNND73</t>
-  </si>
-  <si>
-    <t>2026-06-08 00:00:00</t>
-  </si>
-  <si>
-    <t>2026-08-06 00:00:00</t>
   </si>
   <si>
     <t>BANCO BRADESCO S.A.</t>
@@ -919,7 +907,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:J94"/>
+  <dimension ref="A1:J92"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="15.140625" bestFit="1" customWidth="1"/>
@@ -2680,25 +2668,25 @@
         <v>118</v>
       </c>
       <c r="B60" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="C60" t="s">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="D60" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="E60" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="G60" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="H60">
-        <v>0.14702120294958201</v>
+        <v>1.0029999999999999</v>
       </c>
       <c r="I60" t="s">
-        <v>4</v>
+        <v>23</v>
       </c>
       <c r="J60" t="b">
         <v>0</v>
@@ -2709,22 +2697,25 @@
         <v>118</v>
       </c>
       <c r="B61" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="C61" t="s">
-        <v>18</v>
+        <v>32</v>
       </c>
       <c r="D61" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="E61" t="s">
-        <v>121</v>
+        <v>122</v>
+      </c>
+      <c r="F61" t="s">
+        <v>124</v>
       </c>
       <c r="G61" t="s">
         <v>123</v>
       </c>
       <c r="H61">
-        <v>1.01583554041482</v>
+        <v>1.0029999999999999</v>
       </c>
       <c r="I61" t="s">
         <v>23</v>
@@ -2738,10 +2729,10 @@
         <v>118</v>
       </c>
       <c r="B62" t="s">
-        <v>124</v>
+        <v>120</v>
       </c>
       <c r="C62" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="D62" t="s">
         <v>125</v>
@@ -2750,13 +2741,13 @@
         <v>126</v>
       </c>
       <c r="G62" t="s">
-        <v>127</v>
+        <v>123</v>
       </c>
       <c r="H62">
-        <v>1.0029999999999999</v>
+        <v>1.022904</v>
       </c>
       <c r="I62" t="s">
-        <v>23</v>
+        <v>4</v>
       </c>
       <c r="J62" t="b">
         <v>0</v>
@@ -2767,28 +2758,25 @@
         <v>118</v>
       </c>
       <c r="B63" t="s">
-        <v>124</v>
+        <v>119</v>
       </c>
       <c r="C63" t="s">
-        <v>32</v>
+        <v>127</v>
       </c>
       <c r="D63" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="E63" t="s">
-        <v>126</v>
-      </c>
-      <c r="F63" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="G63" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="H63">
-        <v>1.0029999999999999</v>
+        <v>1.0246200000000001</v>
       </c>
       <c r="I63" t="s">
-        <v>23</v>
+        <v>4</v>
       </c>
       <c r="J63" t="b">
         <v>0</v>
@@ -2799,25 +2787,25 @@
         <v>118</v>
       </c>
       <c r="B64" t="s">
-        <v>124</v>
+        <v>119</v>
       </c>
       <c r="C64" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="D64" t="s">
+        <v>128</v>
+      </c>
+      <c r="E64" t="s">
         <v>129</v>
       </c>
-      <c r="E64" t="s">
+      <c r="G64" t="s">
         <v>130</v>
       </c>
-      <c r="G64" t="s">
-        <v>127</v>
-      </c>
       <c r="H64">
-        <v>1.022904</v>
+        <v>1.015971455536625</v>
       </c>
       <c r="I64" t="s">
-        <v>4</v>
+        <v>23</v>
       </c>
       <c r="J64" t="b">
         <v>0</v>
@@ -2831,22 +2819,25 @@
         <v>119</v>
       </c>
       <c r="C65" t="s">
+        <v>32</v>
+      </c>
+      <c r="D65" t="s">
+        <v>128</v>
+      </c>
+      <c r="E65" t="s">
+        <v>129</v>
+      </c>
+      <c r="F65" t="s">
         <v>131</v>
       </c>
-      <c r="D65" t="s">
-        <v>132</v>
-      </c>
-      <c r="E65" t="s">
-        <v>133</v>
-      </c>
       <c r="G65" t="s">
-        <v>134</v>
+        <v>130</v>
       </c>
       <c r="H65">
-        <v>1.0246200000000001</v>
+        <v>1.015971455536625</v>
       </c>
       <c r="I65" t="s">
-        <v>4</v>
+        <v>23</v>
       </c>
       <c r="J65" t="b">
         <v>0</v>
@@ -2857,10 +2848,10 @@
         <v>118</v>
       </c>
       <c r="B66" t="s">
-        <v>119</v>
+        <v>90</v>
       </c>
       <c r="C66" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="D66" t="s">
         <v>132</v>
@@ -2872,10 +2863,10 @@
         <v>134</v>
       </c>
       <c r="H66">
-        <v>1.015971455536625</v>
+        <v>4.5083199999999997E-3</v>
       </c>
       <c r="I66" t="s">
-        <v>23</v>
+        <v>4</v>
       </c>
       <c r="J66" t="b">
         <v>0</v>
@@ -2889,25 +2880,22 @@
         <v>119</v>
       </c>
       <c r="C67" t="s">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="D67" t="s">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="E67" t="s">
-        <v>133</v>
-      </c>
-      <c r="F67" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="G67" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="H67">
-        <v>1.015971455536625</v>
+        <v>1.0300450000000001</v>
       </c>
       <c r="I67" t="s">
-        <v>23</v>
+        <v>4</v>
       </c>
       <c r="J67" t="b">
         <v>0</v>
@@ -2918,22 +2906,22 @@
         <v>118</v>
       </c>
       <c r="B68" t="s">
-        <v>90</v>
+        <v>119</v>
       </c>
       <c r="C68" t="s">
         <v>26</v>
       </c>
       <c r="D68" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="E68" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="G68" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="H68">
-        <v>4.5083199999999997E-3</v>
+        <v>1.0352269999999999</v>
       </c>
       <c r="I68" t="s">
         <v>4</v>
@@ -2947,25 +2935,25 @@
         <v>118</v>
       </c>
       <c r="B69" t="s">
-        <v>119</v>
+        <v>11</v>
       </c>
       <c r="C69" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="D69" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="E69" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="G69" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="H69">
-        <v>1.0300450000000001</v>
+        <v>1.0494314742428961</v>
       </c>
       <c r="I69" t="s">
-        <v>4</v>
+        <v>23</v>
       </c>
       <c r="J69" t="b">
         <v>0</v>
@@ -2976,25 +2964,28 @@
         <v>118</v>
       </c>
       <c r="B70" t="s">
-        <v>119</v>
+        <v>11</v>
       </c>
       <c r="C70" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="D70" t="s">
+        <v>141</v>
+      </c>
+      <c r="E70" t="s">
         <v>142</v>
       </c>
-      <c r="E70" t="s">
+      <c r="F70" t="s">
+        <v>144</v>
+      </c>
+      <c r="G70" t="s">
         <v>143</v>
       </c>
-      <c r="G70" t="s">
-        <v>144</v>
-      </c>
       <c r="H70">
-        <v>1.0352269999999999</v>
+        <v>1.0494314742428961</v>
       </c>
       <c r="I70" t="s">
-        <v>4</v>
+        <v>23</v>
       </c>
       <c r="J70" t="b">
         <v>0</v>
@@ -3008,22 +2999,22 @@
         <v>11</v>
       </c>
       <c r="C71" t="s">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="D71" t="s">
         <v>145</v>
       </c>
       <c r="E71" t="s">
-        <v>146</v>
+        <v>142</v>
       </c>
       <c r="G71" t="s">
-        <v>147</v>
+        <v>143</v>
       </c>
       <c r="H71">
-        <v>1.0494314742428961</v>
+        <v>1.038705</v>
       </c>
       <c r="I71" t="s">
-        <v>23</v>
+        <v>4</v>
       </c>
       <c r="J71" t="b">
         <v>0</v>
@@ -3037,25 +3028,22 @@
         <v>11</v>
       </c>
       <c r="C72" t="s">
-        <v>32</v>
+        <v>25</v>
       </c>
       <c r="D72" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E72" t="s">
-        <v>146</v>
-      </c>
-      <c r="F72" t="s">
+        <v>147</v>
+      </c>
+      <c r="G72" t="s">
         <v>148</v>
       </c>
-      <c r="G72" t="s">
-        <v>147</v>
-      </c>
       <c r="H72">
-        <v>1.0494314742428961</v>
+        <v>1.052538</v>
       </c>
       <c r="I72" t="s">
-        <v>23</v>
+        <v>4</v>
       </c>
       <c r="J72" t="b">
         <v>0</v>
@@ -3069,19 +3057,19 @@
         <v>11</v>
       </c>
       <c r="C73" t="s">
-        <v>18</v>
+        <v>62</v>
       </c>
       <c r="D73" t="s">
-        <v>149</v>
+        <v>146</v>
       </c>
       <c r="E73" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="G73" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="H73">
-        <v>1.038705</v>
+        <v>1.052538</v>
       </c>
       <c r="I73" t="s">
         <v>4</v>
@@ -3098,16 +3086,16 @@
         <v>11</v>
       </c>
       <c r="C74" t="s">
-        <v>25</v>
+        <v>34</v>
       </c>
       <c r="D74" t="s">
-        <v>150</v>
+        <v>146</v>
       </c>
       <c r="E74" t="s">
-        <v>151</v>
+        <v>147</v>
       </c>
       <c r="G74" t="s">
-        <v>152</v>
+        <v>148</v>
       </c>
       <c r="H74">
         <v>1.052538</v>
@@ -3127,22 +3115,25 @@
         <v>11</v>
       </c>
       <c r="C75" t="s">
-        <v>62</v>
+        <v>35</v>
       </c>
       <c r="D75" t="s">
-        <v>150</v>
+        <v>146</v>
       </c>
       <c r="E75" t="s">
-        <v>151</v>
+        <v>147</v>
+      </c>
+      <c r="F75" t="s">
+        <v>149</v>
       </c>
       <c r="G75" t="s">
-        <v>152</v>
+        <v>148</v>
       </c>
       <c r="H75">
-        <v>1.052538</v>
+        <v>1.0642501208612569</v>
       </c>
       <c r="I75" t="s">
-        <v>4</v>
+        <v>23</v>
       </c>
       <c r="J75" t="b">
         <v>0</v>
@@ -3156,16 +3147,16 @@
         <v>11</v>
       </c>
       <c r="C76" t="s">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="D76" t="s">
         <v>150</v>
       </c>
       <c r="E76" t="s">
-        <v>151</v>
+        <v>147</v>
       </c>
       <c r="G76" t="s">
-        <v>152</v>
+        <v>148</v>
       </c>
       <c r="H76">
         <v>1.052538</v>
@@ -3182,28 +3173,25 @@
         <v>118</v>
       </c>
       <c r="B77" t="s">
-        <v>11</v>
+        <v>151</v>
       </c>
       <c r="C77" t="s">
-        <v>35</v>
+        <v>18</v>
       </c>
       <c r="D77" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="E77" t="s">
-        <v>151</v>
-      </c>
-      <c r="F77" t="s">
         <v>153</v>
       </c>
       <c r="G77" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="H77">
-        <v>1.0642501208612569</v>
+        <v>1.200691</v>
       </c>
       <c r="I77" t="s">
-        <v>23</v>
+        <v>4</v>
       </c>
       <c r="J77" t="b">
         <v>0</v>
@@ -3214,22 +3202,22 @@
         <v>118</v>
       </c>
       <c r="B78" t="s">
-        <v>11</v>
+        <v>151</v>
       </c>
       <c r="C78" t="s">
-        <v>26</v>
+        <v>127</v>
       </c>
       <c r="D78" t="s">
+        <v>152</v>
+      </c>
+      <c r="E78" t="s">
+        <v>153</v>
+      </c>
+      <c r="G78" t="s">
         <v>154</v>
       </c>
-      <c r="E78" t="s">
-        <v>151</v>
-      </c>
-      <c r="G78" t="s">
-        <v>152</v>
-      </c>
       <c r="H78">
-        <v>1.052538</v>
+        <v>1.200691</v>
       </c>
       <c r="I78" t="s">
         <v>4</v>
@@ -3243,19 +3231,19 @@
         <v>118</v>
       </c>
       <c r="B79" t="s">
-        <v>155</v>
+        <v>151</v>
       </c>
       <c r="C79" t="s">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="D79" t="s">
-        <v>156</v>
+        <v>152</v>
       </c>
       <c r="E79" t="s">
-        <v>157</v>
+        <v>153</v>
       </c>
       <c r="G79" t="s">
-        <v>158</v>
+        <v>154</v>
       </c>
       <c r="H79">
         <v>1.200691</v>
@@ -3272,19 +3260,19 @@
         <v>118</v>
       </c>
       <c r="B80" t="s">
-        <v>155</v>
+        <v>151</v>
       </c>
       <c r="C80" t="s">
-        <v>131</v>
+        <v>26</v>
       </c>
       <c r="D80" t="s">
-        <v>156</v>
+        <v>152</v>
       </c>
       <c r="E80" t="s">
-        <v>157</v>
+        <v>153</v>
       </c>
       <c r="G80" t="s">
-        <v>158</v>
+        <v>154</v>
       </c>
       <c r="H80">
         <v>1.200691</v>
@@ -3301,25 +3289,25 @@
         <v>118</v>
       </c>
       <c r="B81" t="s">
+        <v>151</v>
+      </c>
+      <c r="C81" t="s">
+        <v>18</v>
+      </c>
+      <c r="D81" t="s">
         <v>155</v>
       </c>
-      <c r="C81" t="s">
-        <v>25</v>
-      </c>
-      <c r="D81" t="s">
+      <c r="E81" t="s">
         <v>156</v>
       </c>
-      <c r="E81" t="s">
+      <c r="G81" t="s">
         <v>157</v>
       </c>
-      <c r="G81" t="s">
-        <v>158</v>
-      </c>
       <c r="H81">
-        <v>1.200691</v>
+        <v>1.1183513978418871</v>
       </c>
       <c r="I81" t="s">
-        <v>4</v>
+        <v>23</v>
       </c>
       <c r="J81" t="b">
         <v>0</v>
@@ -3330,25 +3318,25 @@
         <v>118</v>
       </c>
       <c r="B82" t="s">
+        <v>151</v>
+      </c>
+      <c r="C82" t="s">
+        <v>24</v>
+      </c>
+      <c r="D82" t="s">
         <v>155</v>
       </c>
-      <c r="C82" t="s">
-        <v>26</v>
-      </c>
-      <c r="D82" t="s">
+      <c r="E82" t="s">
         <v>156</v>
       </c>
-      <c r="E82" t="s">
+      <c r="G82" t="s">
         <v>157</v>
       </c>
-      <c r="G82" t="s">
-        <v>158</v>
-      </c>
       <c r="H82">
-        <v>1.200691</v>
+        <v>1.1183513978418871</v>
       </c>
       <c r="I82" t="s">
-        <v>4</v>
+        <v>23</v>
       </c>
       <c r="J82" t="b">
         <v>0</v>
@@ -3359,25 +3347,25 @@
         <v>118</v>
       </c>
       <c r="B83" t="s">
+        <v>151</v>
+      </c>
+      <c r="C83" t="s">
+        <v>26</v>
+      </c>
+      <c r="D83" t="s">
         <v>155</v>
       </c>
-      <c r="C83" t="s">
-        <v>18</v>
-      </c>
-      <c r="D83" t="s">
-        <v>159</v>
-      </c>
       <c r="E83" t="s">
-        <v>160</v>
+        <v>156</v>
       </c>
       <c r="G83" t="s">
-        <v>161</v>
+        <v>157</v>
       </c>
       <c r="H83">
-        <v>1.1183513978418871</v>
+        <v>1.200691</v>
       </c>
       <c r="I83" t="s">
-        <v>23</v>
+        <v>4</v>
       </c>
       <c r="J83" t="b">
         <v>0</v>
@@ -3388,25 +3376,25 @@
         <v>118</v>
       </c>
       <c r="B84" t="s">
-        <v>155</v>
+        <v>119</v>
       </c>
       <c r="C84" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D84" t="s">
+        <v>158</v>
+      </c>
+      <c r="E84" t="s">
         <v>159</v>
       </c>
-      <c r="E84" t="s">
+      <c r="G84" t="s">
         <v>160</v>
       </c>
-      <c r="G84" t="s">
-        <v>161</v>
-      </c>
       <c r="H84">
-        <v>1.1183513978418871</v>
+        <v>1.092185</v>
       </c>
       <c r="I84" t="s">
-        <v>23</v>
+        <v>4</v>
       </c>
       <c r="J84" t="b">
         <v>0</v>
@@ -3414,28 +3402,31 @@
     </row>
     <row r="85" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
-        <v>118</v>
+        <v>10</v>
       </c>
       <c r="B85" t="s">
-        <v>155</v>
+        <v>17</v>
       </c>
       <c r="C85" t="s">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="D85" t="s">
-        <v>159</v>
+        <v>19</v>
       </c>
       <c r="E85" t="s">
-        <v>160</v>
+        <v>20</v>
+      </c>
+      <c r="F85" t="s">
+        <v>74</v>
       </c>
       <c r="G85" t="s">
-        <v>161</v>
+        <v>21</v>
       </c>
       <c r="H85">
-        <v>1.200691</v>
+        <v>1.062225867980001</v>
       </c>
       <c r="I85" t="s">
-        <v>4</v>
+        <v>23</v>
       </c>
       <c r="J85" t="b">
         <v>0</v>
@@ -3443,28 +3434,31 @@
     </row>
     <row r="86" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
-        <v>118</v>
+        <v>10</v>
       </c>
       <c r="B86" t="s">
-        <v>119</v>
+        <v>17</v>
       </c>
       <c r="C86" t="s">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="D86" t="s">
-        <v>162</v>
+        <v>19</v>
       </c>
       <c r="E86" t="s">
-        <v>163</v>
+        <v>20</v>
+      </c>
+      <c r="F86" t="s">
+        <v>144</v>
       </c>
       <c r="G86" t="s">
-        <v>164</v>
+        <v>21</v>
       </c>
       <c r="H86">
-        <v>1.092185</v>
+        <v>1.062225867980001</v>
       </c>
       <c r="I86" t="s">
-        <v>4</v>
+        <v>23</v>
       </c>
       <c r="J86" t="b">
         <v>0</v>
@@ -3478,7 +3472,7 @@
         <v>17</v>
       </c>
       <c r="C87" t="s">
-        <v>22</v>
+        <v>35</v>
       </c>
       <c r="D87" t="s">
         <v>19</v>
@@ -3487,7 +3481,7 @@
         <v>20</v>
       </c>
       <c r="F87" t="s">
-        <v>74</v>
+        <v>144</v>
       </c>
       <c r="G87" t="s">
         <v>21</v>
@@ -3507,25 +3501,25 @@
         <v>10</v>
       </c>
       <c r="B88" t="s">
-        <v>17</v>
+        <v>65</v>
       </c>
       <c r="C88" t="s">
-        <v>32</v>
+        <v>22</v>
       </c>
       <c r="D88" t="s">
-        <v>19</v>
+        <v>66</v>
       </c>
       <c r="E88" t="s">
-        <v>20</v>
+        <v>67</v>
       </c>
       <c r="F88" t="s">
-        <v>148</v>
+        <v>74</v>
       </c>
       <c r="G88" t="s">
-        <v>21</v>
+        <v>68</v>
       </c>
       <c r="H88">
-        <v>1.062225867980001</v>
+        <v>1.0225</v>
       </c>
       <c r="I88" t="s">
         <v>23</v>
@@ -3539,25 +3533,25 @@
         <v>10</v>
       </c>
       <c r="B89" t="s">
-        <v>17</v>
+        <v>65</v>
       </c>
       <c r="C89" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="D89" t="s">
-        <v>19</v>
+        <v>66</v>
       </c>
       <c r="E89" t="s">
-        <v>20</v>
+        <v>67</v>
       </c>
       <c r="F89" t="s">
-        <v>148</v>
+        <v>144</v>
       </c>
       <c r="G89" t="s">
-        <v>21</v>
+        <v>68</v>
       </c>
       <c r="H89">
-        <v>1.062225867980001</v>
+        <v>1.0225</v>
       </c>
       <c r="I89" t="s">
         <v>23</v>
@@ -3571,25 +3565,25 @@
         <v>10</v>
       </c>
       <c r="B90" t="s">
-        <v>65</v>
+        <v>151</v>
       </c>
       <c r="C90" t="s">
-        <v>22</v>
+        <v>32</v>
       </c>
       <c r="D90" t="s">
-        <v>66</v>
+        <v>161</v>
       </c>
       <c r="E90" t="s">
-        <v>67</v>
+        <v>162</v>
       </c>
       <c r="F90" t="s">
-        <v>74</v>
+        <v>163</v>
       </c>
       <c r="G90" t="s">
-        <v>68</v>
+        <v>164</v>
       </c>
       <c r="H90">
-        <v>1.0225</v>
+        <v>1.143243424338988</v>
       </c>
       <c r="I90" t="s">
         <v>23</v>
@@ -3603,25 +3597,25 @@
         <v>10</v>
       </c>
       <c r="B91" t="s">
-        <v>65</v>
+        <v>151</v>
       </c>
       <c r="C91" t="s">
         <v>32</v>
       </c>
       <c r="D91" t="s">
-        <v>66</v>
+        <v>165</v>
       </c>
       <c r="E91" t="s">
-        <v>67</v>
+        <v>166</v>
       </c>
       <c r="F91" t="s">
-        <v>148</v>
+        <v>167</v>
       </c>
       <c r="G91" t="s">
-        <v>68</v>
+        <v>164</v>
       </c>
       <c r="H91">
-        <v>1.0225</v>
+        <v>1.143243424338988</v>
       </c>
       <c r="I91" t="s">
         <v>23</v>
@@ -3635,22 +3629,22 @@
         <v>10</v>
       </c>
       <c r="B92" t="s">
-        <v>155</v>
+        <v>151</v>
       </c>
       <c r="C92" t="s">
         <v>32</v>
       </c>
       <c r="D92" t="s">
-        <v>165</v>
+        <v>168</v>
       </c>
       <c r="E92" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="F92" t="s">
-        <v>167</v>
+        <v>170</v>
       </c>
       <c r="G92" t="s">
-        <v>168</v>
+        <v>164</v>
       </c>
       <c r="H92">
         <v>1.143243424338988</v>
@@ -3659,70 +3653,6 @@
         <v>23</v>
       </c>
       <c r="J92" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="93" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A93" t="s">
-        <v>10</v>
-      </c>
-      <c r="B93" t="s">
-        <v>155</v>
-      </c>
-      <c r="C93" t="s">
-        <v>32</v>
-      </c>
-      <c r="D93" t="s">
-        <v>169</v>
-      </c>
-      <c r="E93" t="s">
-        <v>170</v>
-      </c>
-      <c r="F93" t="s">
-        <v>171</v>
-      </c>
-      <c r="G93" t="s">
-        <v>168</v>
-      </c>
-      <c r="H93">
-        <v>1.143243424338988</v>
-      </c>
-      <c r="I93" t="s">
-        <v>23</v>
-      </c>
-      <c r="J93" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="94" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A94" t="s">
-        <v>10</v>
-      </c>
-      <c r="B94" t="s">
-        <v>155</v>
-      </c>
-      <c r="C94" t="s">
-        <v>32</v>
-      </c>
-      <c r="D94" t="s">
-        <v>172</v>
-      </c>
-      <c r="E94" t="s">
-        <v>173</v>
-      </c>
-      <c r="F94" t="s">
-        <v>174</v>
-      </c>
-      <c r="G94" t="s">
-        <v>168</v>
-      </c>
-      <c r="H94">
-        <v>1.143243424338988</v>
-      </c>
-      <c r="I94" t="s">
-        <v>23</v>
-      </c>
-      <c r="J94" t="b">
         <v>0</v>
       </c>
     </row>

--- a/Dados/ativos_mapeados_com_taxa_efetiva.xlsx
+++ b/Dados/ativos_mapeados_com_taxa_efetiva.xlsx
@@ -645,7 +645,7 @@
         </is>
       </c>
       <c r="H5" t="n">
-        <v>1.062057211262014</v>
+        <v>1.061149722669342</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
@@ -689,7 +689,7 @@
         </is>
       </c>
       <c r="H6" t="n">
-        <v>1.062057211262014</v>
+        <v>1.061149722669342</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
@@ -865,7 +865,7 @@
         </is>
       </c>
       <c r="H10" t="n">
-        <v>1.031289039803715</v>
+        <v>1.031248332333468</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
@@ -909,7 +909,7 @@
         </is>
       </c>
       <c r="H11" t="n">
-        <v>1.031289039803715</v>
+        <v>1.031248332333468</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
@@ -953,7 +953,7 @@
         </is>
       </c>
       <c r="H12" t="n">
-        <v>1.031289039803715</v>
+        <v>1.031248332333468</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
@@ -1001,7 +1001,7 @@
         </is>
       </c>
       <c r="H13" t="n">
-        <v>1.031289039803715</v>
+        <v>1.031248332333468</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
@@ -1045,7 +1045,7 @@
         </is>
       </c>
       <c r="H14" t="n">
-        <v>1.031289039803715</v>
+        <v>1.031248332333468</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
@@ -1093,7 +1093,7 @@
         </is>
       </c>
       <c r="H15" t="n">
-        <v>1.031289039803715</v>
+        <v>1.031248332333468</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
@@ -1229,7 +1229,7 @@
         </is>
       </c>
       <c r="H18" t="n">
-        <v>1.026345366730454</v>
+        <v>1.026248647833826</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
@@ -1365,7 +1365,7 @@
         </is>
       </c>
       <c r="H21" t="n">
-        <v>1.026345366730454</v>
+        <v>1.026248647833826</v>
       </c>
       <c r="I21" t="inlineStr">
         <is>
@@ -2169,7 +2169,7 @@
         </is>
       </c>
       <c r="H39" t="n">
-        <v>1.052469894043259</v>
+        <v>1.05244167048356</v>
       </c>
       <c r="I39" t="inlineStr">
         <is>
@@ -2217,7 +2217,7 @@
         </is>
       </c>
       <c r="H40" t="n">
-        <v>1.052469894043259</v>
+        <v>1.05244167048356</v>
       </c>
       <c r="I40" t="inlineStr">
         <is>
@@ -2265,7 +2265,7 @@
         </is>
       </c>
       <c r="H41" t="n">
-        <v>1.052469894043259</v>
+        <v>1.05244167048356</v>
       </c>
       <c r="I41" t="inlineStr">
         <is>
@@ -3369,7 +3369,7 @@
         </is>
       </c>
       <c r="H66" t="n">
-        <v>1.015965846893313</v>
+        <v>1.016674697392376</v>
       </c>
       <c r="I66" t="inlineStr">
         <is>
@@ -3417,7 +3417,7 @@
         </is>
       </c>
       <c r="H67" t="n">
-        <v>1.015965846893313</v>
+        <v>1.016674697392376</v>
       </c>
       <c r="I67" t="inlineStr">
         <is>
@@ -3593,7 +3593,7 @@
         </is>
       </c>
       <c r="H71" t="n">
-        <v>1.04915005170302</v>
+        <v>1.047643703409001</v>
       </c>
       <c r="I71" t="inlineStr">
         <is>
@@ -3641,7 +3641,7 @@
         </is>
       </c>
       <c r="H72" t="n">
-        <v>1.04915005170302</v>
+        <v>1.047643703409001</v>
       </c>
       <c r="I72" t="inlineStr">
         <is>
@@ -3865,7 +3865,7 @@
         </is>
       </c>
       <c r="H77" t="n">
-        <v>1.064077413125327</v>
+        <v>1.063174317446572</v>
       </c>
       <c r="I77" t="inlineStr">
         <is>
@@ -4129,7 +4129,7 @@
         </is>
       </c>
       <c r="H83" t="n">
-        <v>1.118297360929818</v>
+        <v>1.117861003798787</v>
       </c>
       <c r="I83" t="inlineStr">
         <is>
@@ -4173,7 +4173,7 @@
         </is>
       </c>
       <c r="H84" t="n">
-        <v>1.118297360929818</v>
+        <v>1.117861003798787</v>
       </c>
       <c r="I84" t="inlineStr">
         <is>
@@ -4309,7 +4309,7 @@
         </is>
       </c>
       <c r="H87" t="n">
-        <v>1.062057211262014</v>
+        <v>1.061149722669342</v>
       </c>
       <c r="I87" t="inlineStr">
         <is>
@@ -4357,7 +4357,7 @@
         </is>
       </c>
       <c r="H88" t="n">
-        <v>1.062057211262014</v>
+        <v>1.061149722669342</v>
       </c>
       <c r="I88" t="inlineStr">
         <is>
@@ -4405,7 +4405,7 @@
         </is>
       </c>
       <c r="H89" t="n">
-        <v>1.062057211262014</v>
+        <v>1.061149722669342</v>
       </c>
       <c r="I89" t="inlineStr">
         <is>
@@ -4549,7 +4549,7 @@
         </is>
       </c>
       <c r="H92" t="n">
-        <v>1.142953074773417</v>
+        <v>1.141460654663127</v>
       </c>
       <c r="I92" t="inlineStr">
         <is>
@@ -4597,7 +4597,7 @@
         </is>
       </c>
       <c r="H93" t="n">
-        <v>1.142953074773417</v>
+        <v>1.141460654663127</v>
       </c>
       <c r="I93" t="inlineStr">
         <is>
@@ -4645,7 +4645,7 @@
         </is>
       </c>
       <c r="H94" t="n">
-        <v>1.142953074773417</v>
+        <v>1.141460654663127</v>
       </c>
       <c r="I94" t="inlineStr">
         <is>

--- a/Dados/ativos_mapeados_com_taxa_efetiva.xlsx
+++ b/Dados/ativos_mapeados_com_taxa_efetiva.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J94"/>
+  <dimension ref="A1:J97"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -645,7 +645,7 @@
         </is>
       </c>
       <c r="H5" t="n">
-        <v>1.061149722669342</v>
+        <v>1.060547767429206</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
@@ -689,7 +689,7 @@
         </is>
       </c>
       <c r="H6" t="n">
-        <v>1.061149722669342</v>
+        <v>1.060547767429206</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
@@ -865,7 +865,7 @@
         </is>
       </c>
       <c r="H10" t="n">
-        <v>1.031248332333468</v>
+        <v>1.032493742512773</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
@@ -909,7 +909,7 @@
         </is>
       </c>
       <c r="H11" t="n">
-        <v>1.031248332333468</v>
+        <v>1.032493742512773</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
@@ -953,7 +953,7 @@
         </is>
       </c>
       <c r="H12" t="n">
-        <v>1.031248332333468</v>
+        <v>1.032493742512773</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
@@ -1001,7 +1001,7 @@
         </is>
       </c>
       <c r="H13" t="n">
-        <v>1.031248332333468</v>
+        <v>1.032493742512773</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
@@ -1045,7 +1045,7 @@
         </is>
       </c>
       <c r="H14" t="n">
-        <v>1.031248332333468</v>
+        <v>1.032493742512773</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
@@ -1093,7 +1093,7 @@
         </is>
       </c>
       <c r="H15" t="n">
-        <v>1.031248332333468</v>
+        <v>1.032493742512773</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
@@ -1229,7 +1229,7 @@
         </is>
       </c>
       <c r="H18" t="n">
-        <v>1.026248647833826</v>
+        <v>1.0274945388866</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
@@ -1365,7 +1365,7 @@
         </is>
       </c>
       <c r="H21" t="n">
-        <v>1.026248647833826</v>
+        <v>1.0274945388866</v>
       </c>
       <c r="I21" t="inlineStr">
         <is>
@@ -2169,7 +2169,7 @@
         </is>
       </c>
       <c r="H39" t="n">
-        <v>1.05244167048356</v>
+        <v>1.052414316056567</v>
       </c>
       <c r="I39" t="inlineStr">
         <is>
@@ -2217,7 +2217,7 @@
         </is>
       </c>
       <c r="H40" t="n">
-        <v>1.05244167048356</v>
+        <v>1.052414316056567</v>
       </c>
       <c r="I40" t="inlineStr">
         <is>
@@ -2265,7 +2265,7 @@
         </is>
       </c>
       <c r="H41" t="n">
-        <v>1.05244167048356</v>
+        <v>1.052414316056567</v>
       </c>
       <c r="I41" t="inlineStr">
         <is>
@@ -3164,7 +3164,7 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>BANCO BRADESCO S.A.</t>
+          <t>BANCO SAFRA S.A.</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -3174,22 +3174,22 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>LFSN1800DG1</t>
+          <t>LFSN1800D4W</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>BRBBDCLTR2X9</t>
+          <t>BRBSAFLNND73</t>
         </is>
       </c>
       <c r="F62" t="inlineStr"/>
       <c r="G62" t="inlineStr">
         <is>
-          <t>2026-08-03 00:00:00</t>
+          <t>2026-06-08 00:00:00</t>
         </is>
       </c>
       <c r="H62" t="n">
-        <v>1.003</v>
+        <v>1.016611580343873</v>
       </c>
       <c r="I62" t="inlineStr">
         <is>
@@ -3213,7 +3213,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>JERA2026</t>
+          <t>CARMEL INFRA</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -3226,11 +3226,7 @@
           <t>BRBBDCLTR2X9</t>
         </is>
       </c>
-      <c r="F63" t="inlineStr">
-        <is>
-          <t>407137-LFS</t>
-        </is>
-      </c>
+      <c r="F63" t="inlineStr"/>
       <c r="G63" t="inlineStr">
         <is>
           <t>2026-08-03 00:00:00</t>
@@ -3261,31 +3257,35 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>FIRF GERAES</t>
+          <t>JERA2026</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>LFSN1800DIG</t>
+          <t>LFSN1800DG1</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>BRBBDCLTROH4</t>
-        </is>
-      </c>
-      <c r="F64" t="inlineStr"/>
+          <t>BRBBDCLTR2X9</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>407137-LFS</t>
+        </is>
+      </c>
       <c r="G64" t="inlineStr">
         <is>
           <t>2026-08-03 00:00:00</t>
         </is>
       </c>
       <c r="H64" t="n">
-        <v>1.022904</v>
+        <v>1.003</v>
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>ISIN</t>
+          <t>MATRIZ</t>
         </is>
       </c>
       <c r="J64" t="b">
@@ -3300,32 +3300,32 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>BANCO SAFRA S.A.</t>
+          <t>BANCO BRADESCO S.A.</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>BORDEAUX INFRA</t>
+          <t>FIRF GERAES</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>LFSN1800DS5</t>
+          <t>LFSN1800DIG</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>BRBSAFLNN8B3</t>
+          <t>BRBBDCLTROH4</t>
         </is>
       </c>
       <c r="F65" t="inlineStr"/>
       <c r="G65" t="inlineStr">
         <is>
-          <t>2026-08-17 00:00:00</t>
+          <t>2026-08-03 00:00:00</t>
         </is>
       </c>
       <c r="H65" t="n">
-        <v>1.021813</v>
+        <v>1.022904</v>
       </c>
       <c r="I65" t="inlineStr">
         <is>
@@ -3349,7 +3349,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>CARMEL INFRA</t>
+          <t>BORDEAUX INFRA</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -3369,11 +3369,11 @@
         </is>
       </c>
       <c r="H66" t="n">
-        <v>1.016674697392376</v>
+        <v>1.021813</v>
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>MATRIZ</t>
+          <t>ISIN</t>
         </is>
       </c>
       <c r="J66" t="b">
@@ -3393,7 +3393,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>JERA2026</t>
+          <t>CARMEL INFRA</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -3406,18 +3406,14 @@
           <t>BRBSAFLNN8B3</t>
         </is>
       </c>
-      <c r="F67" t="inlineStr">
-        <is>
-          <t>335769-LFS</t>
-        </is>
-      </c>
+      <c r="F67" t="inlineStr"/>
       <c r="G67" t="inlineStr">
         <is>
           <t>2026-08-17 00:00:00</t>
         </is>
       </c>
       <c r="H67" t="n">
-        <v>1.016674697392376</v>
+        <v>1.016639262782153</v>
       </c>
       <c r="I67" t="inlineStr">
         <is>
@@ -3436,36 +3432,40 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>BANCO ABC BRASIL S.A.</t>
+          <t>BANCO SAFRA S.A.</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>FIRF GERAES</t>
+          <t>JERA2026</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>LFSN1800E2G</t>
+          <t>LFSN1800DS5</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>BRABCBLFIM22</t>
-        </is>
-      </c>
-      <c r="F68" t="inlineStr"/>
+          <t>BRBSAFLNN8B3</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>335769-LFS</t>
+        </is>
+      </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>2025-09-29 00:00:00</t>
+          <t>2026-08-17 00:00:00</t>
         </is>
       </c>
       <c r="H68" t="n">
-        <v>0.00450832</v>
+        <v>1.016639262782153</v>
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>ISIN</t>
+          <t>MATRIZ</t>
         </is>
       </c>
       <c r="J68" t="b">
@@ -3480,7 +3480,7 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>BANCO SAFRA S.A.</t>
+          <t>BANCO ABC BRASIL S.A.</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
@@ -3490,22 +3490,22 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>LFSN1800HXO</t>
+          <t>LFSN1800E2G</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>BRBSAFLNN7R1</t>
+          <t>BRABCBLFIM22</t>
         </is>
       </c>
       <c r="F69" t="inlineStr"/>
       <c r="G69" t="inlineStr">
         <is>
-          <t>2026-11-06 00:00:00</t>
+          <t>2025-09-29 00:00:00</t>
         </is>
       </c>
       <c r="H69" t="n">
-        <v>1.030045</v>
+        <v>0.00450832</v>
       </c>
       <c r="I69" t="inlineStr">
         <is>
@@ -3534,22 +3534,22 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>LFSN1900008</t>
+          <t>LFSN1800HXO</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>BRBSAFLFNBB5</t>
+          <t>BRBSAFLNN7R1</t>
         </is>
       </c>
       <c r="F70" t="inlineStr"/>
       <c r="G70" t="inlineStr">
         <is>
-          <t>2027-01-08 00:00:00</t>
+          <t>2026-11-06 00:00:00</t>
         </is>
       </c>
       <c r="H70" t="n">
-        <v>1.035227</v>
+        <v>1.030045</v>
       </c>
       <c r="I70" t="inlineStr">
         <is>
@@ -3568,36 +3568,36 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>BANCO BTG PACTUAL S.A.</t>
+          <t>BANCO SAFRA S.A.</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>CARMEL INFRA</t>
+          <t>FIRF GERAES</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>LFSN19001BC</t>
+          <t>LFSN1900008</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>BRBPACLFIVQ4</t>
+          <t>BRBSAFLFNBB5</t>
         </is>
       </c>
       <c r="F71" t="inlineStr"/>
       <c r="G71" t="inlineStr">
         <is>
-          <t>2027-04-09 00:00:00</t>
+          <t>2027-01-08 00:00:00</t>
         </is>
       </c>
       <c r="H71" t="n">
-        <v>1.047643703409001</v>
+        <v>1.035227</v>
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>MATRIZ</t>
+          <t>ISIN</t>
         </is>
       </c>
       <c r="J71" t="b">
@@ -3617,7 +3617,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>JERA2026</t>
+          <t>CARMEL INFRA</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -3630,18 +3630,14 @@
           <t>BRBPACLFIVQ4</t>
         </is>
       </c>
-      <c r="F72" t="inlineStr">
-        <is>
-          <t>353997-N L</t>
-        </is>
-      </c>
+      <c r="F72" t="inlineStr"/>
       <c r="G72" t="inlineStr">
         <is>
           <t>2027-04-09 00:00:00</t>
         </is>
       </c>
       <c r="H72" t="n">
-        <v>1.047643703409001</v>
+        <v>1.046651801284736</v>
       </c>
       <c r="I72" t="inlineStr">
         <is>
@@ -3665,12 +3661,12 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>BH INFRA</t>
+          <t>JERA2026</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>LFSN19001BH</t>
+          <t>LFSN19001BC</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
@@ -3678,18 +3674,22 @@
           <t>BRBPACLFIVQ4</t>
         </is>
       </c>
-      <c r="F73" t="inlineStr"/>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>353997-N L</t>
+        </is>
+      </c>
       <c r="G73" t="inlineStr">
         <is>
           <t>2027-04-09 00:00:00</t>
         </is>
       </c>
       <c r="H73" t="n">
-        <v>1.038705</v>
+        <v>1.046651801284736</v>
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>ISIN</t>
+          <t>MATRIZ</t>
         </is>
       </c>
       <c r="J73" t="b">
@@ -3709,27 +3709,27 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>FIRF GERAES 30</t>
+          <t>BH INFRA</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>LFSN19006KM</t>
+          <t>LFSN19001BH</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>BRBPACLFIWC2</t>
+          <t>BRBPACLFIVQ4</t>
         </is>
       </c>
       <c r="F74" t="inlineStr"/>
       <c r="G74" t="inlineStr">
         <is>
-          <t>2028-05-31 00:00:00</t>
+          <t>2027-04-09 00:00:00</t>
         </is>
       </c>
       <c r="H74" t="n">
-        <v>1.052538</v>
+        <v>1.038705</v>
       </c>
       <c r="I74" t="inlineStr">
         <is>
@@ -3753,31 +3753,31 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>HORIZONTE FIM</t>
+          <t>FIRF GERAES</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>LFSN19006KM</t>
+          <t>LFSN19001BH</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>BRBPACLFIWC2</t>
+          <t>BRBPACLFIVQ4</t>
         </is>
       </c>
       <c r="F75" t="inlineStr"/>
       <c r="G75" t="inlineStr">
         <is>
-          <t>2028-05-31 00:00:00</t>
+          <t>2027-04-09 00:00:00</t>
         </is>
       </c>
       <c r="H75" t="n">
-        <v>1.052538</v>
+        <v>1.046651801284736</v>
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>ISIN</t>
+          <t>MATRIZ</t>
         </is>
       </c>
       <c r="J75" t="b">
@@ -3797,7 +3797,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>MANACA INFRA</t>
+          <t>FIRF GERAES 30</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -3841,7 +3841,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>REAL FIM</t>
+          <t>HORIZONTE FIM</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -3854,22 +3854,18 @@
           <t>BRBPACLFIWC2</t>
         </is>
       </c>
-      <c r="F77" t="inlineStr">
-        <is>
-          <t>513453-LFS</t>
-        </is>
-      </c>
+      <c r="F77" t="inlineStr"/>
       <c r="G77" t="inlineStr">
         <is>
           <t>2028-05-31 00:00:00</t>
         </is>
       </c>
       <c r="H77" t="n">
-        <v>1.063174317446572</v>
+        <v>1.052538</v>
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>MATRIZ</t>
+          <t>ISIN</t>
         </is>
       </c>
       <c r="J77" t="b">
@@ -3889,12 +3885,12 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>FIRF GERAES</t>
+          <t>MANACA INFRA</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>LFSN19006KN</t>
+          <t>LFSN19006KM</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
@@ -3928,36 +3924,40 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>BANCO BMG S.A.</t>
+          <t>BANCO BTG PACTUAL S.A.</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>BH INFRA</t>
+          <t>REAL FIM</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>LFSN1900971</t>
+          <t>LFSN19006KM</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>BRBMGBLFI489</t>
-        </is>
-      </c>
-      <c r="F79" t="inlineStr"/>
+          <t>BRBPACLFIWC2</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>513453-LFS</t>
+        </is>
+      </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>2026-06-22 00:00:00</t>
+          <t>2028-05-31 00:00:00</t>
         </is>
       </c>
       <c r="H79" t="n">
-        <v>1.196383</v>
+        <v>1.062598589137548</v>
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>ISIN</t>
+          <t>MATRIZ</t>
         </is>
       </c>
       <c r="J79" t="b">
@@ -3972,32 +3972,32 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>BANCO BMG S.A.</t>
+          <t>BANCO BTG PACTUAL S.A.</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>BORDEAUX INFRA</t>
+          <t>FIRF GERAES</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>LFSN1900971</t>
+          <t>LFSN19006KN</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>BRBMGBLFI489</t>
+          <t>BRBPACLFIWC2</t>
         </is>
       </c>
       <c r="F80" t="inlineStr"/>
       <c r="G80" t="inlineStr">
         <is>
-          <t>2026-06-22 00:00:00</t>
+          <t>2028-05-31 00:00:00</t>
         </is>
       </c>
       <c r="H80" t="n">
-        <v>1.196383</v>
+        <v>1.052538</v>
       </c>
       <c r="I80" t="inlineStr">
         <is>
@@ -4021,7 +4021,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>FIRF GERAES 30</t>
+          <t>BH INFRA</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -4065,7 +4065,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>FIRF GERAES</t>
+          <t>BORDEAUX INFRA</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -4109,27 +4109,27 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>BH INFRA</t>
+          <t>CARMEL INFRA</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>LFSN19009YU</t>
+          <t>LFSN1900971</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>BRBMGBLFI6I3</t>
+          <t>BRBMGBLFI489</t>
         </is>
       </c>
       <c r="F83" t="inlineStr"/>
       <c r="G83" t="inlineStr">
         <is>
-          <t>2026-06-26 00:00:00</t>
+          <t>2026-06-22 00:00:00</t>
         </is>
       </c>
       <c r="H83" t="n">
-        <v>1.117861003798787</v>
+        <v>1.116966051517022</v>
       </c>
       <c r="I83" t="inlineStr">
         <is>
@@ -4153,31 +4153,31 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>CARMEL INFRA</t>
+          <t>FIRF GERAES 30</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>LFSN19009YU</t>
+          <t>LFSN1900971</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>BRBMGBLFI6I3</t>
+          <t>BRBMGBLFI489</t>
         </is>
       </c>
       <c r="F84" t="inlineStr"/>
       <c r="G84" t="inlineStr">
         <is>
-          <t>2026-06-26 00:00:00</t>
+          <t>2026-06-22 00:00:00</t>
         </is>
       </c>
       <c r="H84" t="n">
-        <v>1.117861003798787</v>
+        <v>1.196383</v>
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t>MATRIZ</t>
+          <t>ISIN</t>
         </is>
       </c>
       <c r="J84" t="b">
@@ -4202,22 +4202,22 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>LFSN19009YU</t>
+          <t>LFSN1900971</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>BRBMGBLFI6I3</t>
+          <t>BRBMGBLFI489</t>
         </is>
       </c>
       <c r="F85" t="inlineStr"/>
       <c r="G85" t="inlineStr">
         <is>
-          <t>2026-06-26 00:00:00</t>
+          <t>2026-06-22 00:00:00</t>
         </is>
       </c>
       <c r="H85" t="n">
-        <v>1.200691</v>
+        <v>1.196383</v>
       </c>
       <c r="I85" t="inlineStr">
         <is>
@@ -4236,36 +4236,36 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>BANCO SAFRA S.A.</t>
+          <t>BANCO BMG S.A.</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>FIRF GERAES 30</t>
+          <t>BH INFRA</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>LFSN1900CR5</t>
+          <t>LFSN19009YU</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>BRBSAFLFNG47</t>
+          <t>BRBMGBLFI6I3</t>
         </is>
       </c>
       <c r="F86" t="inlineStr"/>
       <c r="G86" t="inlineStr">
         <is>
-          <t>2029-08-13 00:00:00</t>
+          <t>2026-06-26 00:00:00</t>
         </is>
       </c>
       <c r="H86" t="n">
-        <v>1.092185</v>
+        <v>1.117289146782183</v>
       </c>
       <c r="I86" t="inlineStr">
         <is>
-          <t>ISIN</t>
+          <t>MATRIZ</t>
         </is>
       </c>
       <c r="J86" t="b">
@@ -4275,41 +4275,37 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>CDB</t>
+          <t>LFSN</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>AGIBANK</t>
+          <t>BANCO BMG S.A.</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>BMG SEG</t>
+          <t>CARMEL INFRA</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>CDB3251WXH0</t>
+          <t>LFSN19009YU</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>BRAGBKC00M66</t>
-        </is>
-      </c>
-      <c r="F87" t="inlineStr">
-        <is>
-          <t>614522-CDB</t>
-        </is>
-      </c>
+          <t>BRBMGBLFI6I3</t>
+        </is>
+      </c>
+      <c r="F87" t="inlineStr"/>
       <c r="G87" t="inlineStr">
         <is>
-          <t>2027-03-08 00:00:00</t>
+          <t>2026-06-26 00:00:00</t>
         </is>
       </c>
       <c r="H87" t="n">
-        <v>1.061149722669342</v>
+        <v>1.117289146782183</v>
       </c>
       <c r="I87" t="inlineStr">
         <is>
@@ -4323,45 +4319,41 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>CDB</t>
+          <t>LFSN</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>AGIBANK</t>
+          <t>BANCO BMG S.A.</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>JERA2026</t>
+          <t>FIRF GERAES</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>CDB3251WXH0</t>
+          <t>LFSN19009YU</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>BRAGBKC00M66</t>
-        </is>
-      </c>
-      <c r="F88" t="inlineStr">
-        <is>
-          <t>353997-N L</t>
-        </is>
-      </c>
+          <t>BRBMGBLFI6I3</t>
+        </is>
+      </c>
+      <c r="F88" t="inlineStr"/>
       <c r="G88" t="inlineStr">
         <is>
-          <t>2027-03-08 00:00:00</t>
+          <t>2026-06-26 00:00:00</t>
         </is>
       </c>
       <c r="H88" t="n">
-        <v>1.061149722669342</v>
+        <v>1.200691</v>
       </c>
       <c r="I88" t="inlineStr">
         <is>
-          <t>MATRIZ</t>
+          <t>ISIN</t>
         </is>
       </c>
       <c r="J88" t="b">
@@ -4371,45 +4363,41 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>CDB</t>
+          <t>LFSN</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>AGIBANK</t>
+          <t>BANCO SAFRA S.A.</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>REAL FIM</t>
+          <t>FIRF GERAES 30</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>CDB3251WXH0</t>
+          <t>LFSN1900CR5</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>BRAGBKC00M66</t>
-        </is>
-      </c>
-      <c r="F89" t="inlineStr">
-        <is>
-          <t>353997-N L</t>
-        </is>
-      </c>
+          <t>BRBSAFLFNG47</t>
+        </is>
+      </c>
+      <c r="F89" t="inlineStr"/>
       <c r="G89" t="inlineStr">
         <is>
-          <t>2027-03-08 00:00:00</t>
+          <t>2029-08-13 00:00:00</t>
         </is>
       </c>
       <c r="H89" t="n">
-        <v>1.061149722669342</v>
+        <v>1.092185</v>
       </c>
       <c r="I89" t="inlineStr">
         <is>
-          <t>MATRIZ</t>
+          <t>ISIN</t>
         </is>
       </c>
       <c r="J89" t="b">
@@ -4424,7 +4412,7 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>BANCO XP</t>
+          <t>AGIBANK</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
@@ -4434,12 +4422,12 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>LF00240072E</t>
+          <t>CDB3251WXH0</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>BRBCXPLFIKS5</t>
+          <t>BRAGBKC00M66</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
@@ -4449,11 +4437,11 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>2026-03-02 00:00:00</t>
+          <t>2027-03-08 00:00:00</t>
         </is>
       </c>
       <c r="H90" t="n">
-        <v>1.0225</v>
+        <v>1.060547767429206</v>
       </c>
       <c r="I90" t="inlineStr">
         <is>
@@ -4472,7 +4460,7 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>BANCO XP</t>
+          <t>AGIBANK</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
@@ -4482,12 +4470,12 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>LF00240072E</t>
+          <t>CDB3251WXH0</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>BRBCXPLFIKS5</t>
+          <t>BRAGBKC00M66</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
@@ -4497,11 +4485,11 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>2026-03-02 00:00:00</t>
+          <t>2027-03-08 00:00:00</t>
         </is>
       </c>
       <c r="H91" t="n">
-        <v>1.0225</v>
+        <v>1.060547767429206</v>
       </c>
       <c r="I91" t="inlineStr">
         <is>
@@ -4520,36 +4508,36 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>BANCO BMG S.A.</t>
+          <t>AGIBANK</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>JERA2026</t>
+          <t>REAL FIM</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>LFSC19002CD</t>
+          <t>CDB3251WXH0</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>BRBMGBLFI7Q4</t>
+          <t>BRAGBKC00M66</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>609712-LFS</t>
+          <t>353997-N L</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>2029-04-09 00:00:00</t>
+          <t>2027-03-08 00:00:00</t>
         </is>
       </c>
       <c r="H92" t="n">
-        <v>1.141460654663127</v>
+        <v>1.060547767429206</v>
       </c>
       <c r="I92" t="inlineStr">
         <is>
@@ -4568,36 +4556,36 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>BANCO BMG S.A.</t>
+          <t>BANCO XP</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>JERA2026</t>
+          <t>BMG SEG</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>LFSC19002CE</t>
+          <t>LF00240072E</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>BRBMGBLFI7P6</t>
+          <t>BRBCXPLFIKS5</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>609711-LFS</t>
+          <t>614522-CDB</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>2029-04-09 00:00:00</t>
+          <t>2026-03-02 00:00:00</t>
         </is>
       </c>
       <c r="H93" t="n">
-        <v>1.141460654663127</v>
+        <v>1.0225</v>
       </c>
       <c r="I93" t="inlineStr">
         <is>
@@ -4616,43 +4604,187 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
+          <t>BANCO XP</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>JERA2026</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>LF00240072E</t>
+        </is>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>BRBCXPLFIKS5</t>
+        </is>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>353997-N L</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>2026-03-02 00:00:00</t>
+        </is>
+      </c>
+      <c r="H94" t="n">
+        <v>1.0225</v>
+      </c>
+      <c r="I94" t="inlineStr">
+        <is>
+          <t>MATRIZ</t>
+        </is>
+      </c>
+      <c r="J94" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>CDB</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
           <t>BANCO BMG S.A.</t>
         </is>
       </c>
-      <c r="C94" t="inlineStr">
+      <c r="C95" t="inlineStr">
         <is>
           <t>JERA2026</t>
         </is>
       </c>
-      <c r="D94" t="inlineStr">
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>LFSC19002CD</t>
+        </is>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>BRBMGBLFI7Q4</t>
+        </is>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>609712-LFS</t>
+        </is>
+      </c>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>2029-04-09 00:00:00</t>
+        </is>
+      </c>
+      <c r="H95" t="n">
+        <v>1.140531278354469</v>
+      </c>
+      <c r="I95" t="inlineStr">
+        <is>
+          <t>MATRIZ</t>
+        </is>
+      </c>
+      <c r="J95" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>CDB</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>BANCO BMG S.A.</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>JERA2026</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>LFSC19002CE</t>
+        </is>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>BRBMGBLFI7P6</t>
+        </is>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>609711-LFS</t>
+        </is>
+      </c>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>2029-04-09 00:00:00</t>
+        </is>
+      </c>
+      <c r="H96" t="n">
+        <v>1.140531278354469</v>
+      </c>
+      <c r="I96" t="inlineStr">
+        <is>
+          <t>MATRIZ</t>
+        </is>
+      </c>
+      <c r="J96" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>CDB</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>BANCO BMG S.A.</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>JERA2026</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr">
         <is>
           <t>LFSC19002HS</t>
         </is>
       </c>
-      <c r="E94" t="inlineStr">
+      <c r="E97" t="inlineStr">
         <is>
           <t>BRBMGBLFI7R2</t>
         </is>
       </c>
-      <c r="F94" t="inlineStr">
+      <c r="F97" t="inlineStr">
         <is>
           <t>609713-LFS</t>
         </is>
       </c>
-      <c r="G94" t="inlineStr">
+      <c r="G97" t="inlineStr">
         <is>
           <t>2029-04-09 00:00:00</t>
         </is>
       </c>
-      <c r="H94" t="n">
-        <v>1.141460654663127</v>
-      </c>
-      <c r="I94" t="inlineStr">
+      <c r="H97" t="n">
+        <v>1.140531278354469</v>
+      </c>
+      <c r="I97" t="inlineStr">
         <is>
           <t>MATRIZ</t>
         </is>
       </c>
-      <c r="J94" t="b">
+      <c r="J97" t="b">
         <v>0</v>
       </c>
     </row>

--- a/Dados/ativos_mapeados_com_taxa_efetiva.xlsx
+++ b/Dados/ativos_mapeados_com_taxa_efetiva.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J97"/>
+  <dimension ref="A1:J98"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -645,7 +645,7 @@
         </is>
       </c>
       <c r="H5" t="n">
-        <v>1.060547767429206</v>
+        <v>1.06011927746097</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
@@ -689,7 +689,7 @@
         </is>
       </c>
       <c r="H6" t="n">
-        <v>1.060547767429206</v>
+        <v>1.06011927746097</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
@@ -865,7 +865,7 @@
         </is>
       </c>
       <c r="H10" t="n">
-        <v>1.032493742512773</v>
+        <v>1.032491353300285</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
@@ -909,7 +909,7 @@
         </is>
       </c>
       <c r="H11" t="n">
-        <v>1.032493742512773</v>
+        <v>1.032491353300285</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
@@ -953,7 +953,7 @@
         </is>
       </c>
       <c r="H12" t="n">
-        <v>1.032493742512773</v>
+        <v>1.032491353300285</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
@@ -1001,7 +1001,7 @@
         </is>
       </c>
       <c r="H13" t="n">
-        <v>1.032493742512773</v>
+        <v>1.032491353300285</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
@@ -1045,7 +1045,7 @@
         </is>
       </c>
       <c r="H14" t="n">
-        <v>1.032493742512773</v>
+        <v>1.032491353300285</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
@@ -1093,7 +1093,7 @@
         </is>
       </c>
       <c r="H15" t="n">
-        <v>1.032493742512773</v>
+        <v>1.032491353300285</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
@@ -1229,7 +1229,7 @@
         </is>
       </c>
       <c r="H18" t="n">
-        <v>1.0274945388866</v>
+        <v>1.027492298438137</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
@@ -1365,7 +1365,7 @@
         </is>
       </c>
       <c r="H21" t="n">
-        <v>1.0274945388866</v>
+        <v>1.027492298438137</v>
       </c>
       <c r="I21" t="inlineStr">
         <is>
@@ -2169,7 +2169,7 @@
         </is>
       </c>
       <c r="H39" t="n">
-        <v>1.052414316056567</v>
+        <v>1.052387791224203</v>
       </c>
       <c r="I39" t="inlineStr">
         <is>
@@ -2217,7 +2217,7 @@
         </is>
       </c>
       <c r="H40" t="n">
-        <v>1.052414316056567</v>
+        <v>1.052387791224203</v>
       </c>
       <c r="I40" t="inlineStr">
         <is>
@@ -2265,7 +2265,7 @@
         </is>
       </c>
       <c r="H41" t="n">
-        <v>1.052414316056567</v>
+        <v>1.052387791224203</v>
       </c>
       <c r="I41" t="inlineStr">
         <is>
@@ -3177,11 +3177,7 @@
           <t>LFSN1800D4W</t>
         </is>
       </c>
-      <c r="E62" t="inlineStr">
-        <is>
-          <t>BRBSAFLNND73</t>
-        </is>
-      </c>
+      <c r="E62" t="inlineStr"/>
       <c r="F62" t="inlineStr"/>
       <c r="G62" t="inlineStr">
         <is>
@@ -3189,7 +3185,7 @@
         </is>
       </c>
       <c r="H62" t="n">
-        <v>1.016611580343873</v>
+        <v>1.01657005808601</v>
       </c>
       <c r="I62" t="inlineStr">
         <is>
@@ -3208,7 +3204,7 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>BANCO BRADESCO S.A.</t>
+          <t>BANCO SAFRA S.A.</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -3218,22 +3214,18 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>LFSN1800DG1</t>
-        </is>
-      </c>
-      <c r="E63" t="inlineStr">
-        <is>
-          <t>BRBBDCLTR2X9</t>
-        </is>
-      </c>
+          <t>LFSN1800D4W</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr"/>
       <c r="F63" t="inlineStr"/>
       <c r="G63" t="inlineStr">
         <is>
-          <t>2026-08-03 00:00:00</t>
+          <t>2026-08-06 00:00:00</t>
         </is>
       </c>
       <c r="H63" t="n">
-        <v>1.003</v>
+        <v>1.014073509362798</v>
       </c>
       <c r="I63" t="inlineStr">
         <is>
@@ -3257,7 +3249,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>JERA2026</t>
+          <t>CARMEL INFRA</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -3270,11 +3262,7 @@
           <t>BRBBDCLTR2X9</t>
         </is>
       </c>
-      <c r="F64" t="inlineStr">
-        <is>
-          <t>407137-LFS</t>
-        </is>
-      </c>
+      <c r="F64" t="inlineStr"/>
       <c r="G64" t="inlineStr">
         <is>
           <t>2026-08-03 00:00:00</t>
@@ -3305,31 +3293,35 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>FIRF GERAES</t>
+          <t>JERA2026</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>LFSN1800DIG</t>
+          <t>LFSN1800DG1</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>BRBBDCLTROH4</t>
-        </is>
-      </c>
-      <c r="F65" t="inlineStr"/>
+          <t>BRBBDCLTR2X9</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>407137-LFS</t>
+        </is>
+      </c>
       <c r="G65" t="inlineStr">
         <is>
           <t>2026-08-03 00:00:00</t>
         </is>
       </c>
       <c r="H65" t="n">
-        <v>1.022904</v>
+        <v>1.003</v>
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>ISIN</t>
+          <t>MATRIZ</t>
         </is>
       </c>
       <c r="J65" t="b">
@@ -3344,32 +3336,32 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>BANCO SAFRA S.A.</t>
+          <t>BANCO BRADESCO S.A.</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>BORDEAUX INFRA</t>
+          <t>FIRF GERAES</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>LFSN1800DS5</t>
+          <t>LFSN1800DIG</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>BRBSAFLNN8B3</t>
+          <t>BRBBDCLTROH4</t>
         </is>
       </c>
       <c r="F66" t="inlineStr"/>
       <c r="G66" t="inlineStr">
         <is>
-          <t>2026-08-17 00:00:00</t>
+          <t>2026-08-03 00:00:00</t>
         </is>
       </c>
       <c r="H66" t="n">
-        <v>1.021813</v>
+        <v>1.022904</v>
       </c>
       <c r="I66" t="inlineStr">
         <is>
@@ -3393,7 +3385,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>CARMEL INFRA</t>
+          <t>BORDEAUX INFRA</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -3413,11 +3405,11 @@
         </is>
       </c>
       <c r="H67" t="n">
-        <v>1.016639262782153</v>
+        <v>1.021813</v>
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>MATRIZ</t>
+          <t>ISIN</t>
         </is>
       </c>
       <c r="J67" t="b">
@@ -3437,7 +3429,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>JERA2026</t>
+          <t>CARMEL INFRA</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -3450,18 +3442,14 @@
           <t>BRBSAFLNN8B3</t>
         </is>
       </c>
-      <c r="F68" t="inlineStr">
-        <is>
-          <t>335769-LFS</t>
-        </is>
-      </c>
+      <c r="F68" t="inlineStr"/>
       <c r="G68" t="inlineStr">
         <is>
           <t>2026-08-17 00:00:00</t>
         </is>
       </c>
       <c r="H68" t="n">
-        <v>1.016639262782153</v>
+        <v>1.016607050561403</v>
       </c>
       <c r="I68" t="inlineStr">
         <is>
@@ -3480,36 +3468,40 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>BANCO ABC BRASIL S.A.</t>
+          <t>BANCO SAFRA S.A.</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>FIRF GERAES</t>
+          <t>JERA2026</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>LFSN1800E2G</t>
+          <t>LFSN1800DS5</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>BRABCBLFIM22</t>
-        </is>
-      </c>
-      <c r="F69" t="inlineStr"/>
+          <t>BRBSAFLNN8B3</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>335769-LFS</t>
+        </is>
+      </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>2025-09-29 00:00:00</t>
+          <t>2026-08-17 00:00:00</t>
         </is>
       </c>
       <c r="H69" t="n">
-        <v>0.00450832</v>
+        <v>1.016607050561403</v>
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>ISIN</t>
+          <t>MATRIZ</t>
         </is>
       </c>
       <c r="J69" t="b">
@@ -3524,7 +3516,7 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>BANCO SAFRA S.A.</t>
+          <t>BANCO ABC BRASIL S.A.</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
@@ -3534,22 +3526,22 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>LFSN1800HXO</t>
+          <t>LFSN1800E2G</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>BRBSAFLNN7R1</t>
+          <t>BRABCBLFIM22</t>
         </is>
       </c>
       <c r="F70" t="inlineStr"/>
       <c r="G70" t="inlineStr">
         <is>
-          <t>2026-11-06 00:00:00</t>
+          <t>2025-09-29 00:00:00</t>
         </is>
       </c>
       <c r="H70" t="n">
-        <v>1.030045</v>
+        <v>0.00450832</v>
       </c>
       <c r="I70" t="inlineStr">
         <is>
@@ -3578,22 +3570,22 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>LFSN1900008</t>
+          <t>LFSN1800HXO</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>BRBSAFLFNBB5</t>
+          <t>BRBSAFLNN7R1</t>
         </is>
       </c>
       <c r="F71" t="inlineStr"/>
       <c r="G71" t="inlineStr">
         <is>
-          <t>2027-01-08 00:00:00</t>
+          <t>2026-11-06 00:00:00</t>
         </is>
       </c>
       <c r="H71" t="n">
-        <v>1.035227</v>
+        <v>1.030045</v>
       </c>
       <c r="I71" t="inlineStr">
         <is>
@@ -3612,36 +3604,36 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>BANCO BTG PACTUAL S.A.</t>
+          <t>BANCO SAFRA S.A.</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>CARMEL INFRA</t>
+          <t>FIRF GERAES</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>LFSN19001BC</t>
+          <t>LFSN1900008</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>BRBPACLFIVQ4</t>
+          <t>BRBSAFLFNBB5</t>
         </is>
       </c>
       <c r="F72" t="inlineStr"/>
       <c r="G72" t="inlineStr">
         <is>
-          <t>2027-04-09 00:00:00</t>
+          <t>2027-01-08 00:00:00</t>
         </is>
       </c>
       <c r="H72" t="n">
-        <v>1.046651801284736</v>
+        <v>1.035227</v>
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>MATRIZ</t>
+          <t>ISIN</t>
         </is>
       </c>
       <c r="J72" t="b">
@@ -3661,7 +3653,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>JERA2026</t>
+          <t>CARMEL INFRA</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -3674,18 +3666,14 @@
           <t>BRBPACLFIVQ4</t>
         </is>
       </c>
-      <c r="F73" t="inlineStr">
-        <is>
-          <t>353997-N L</t>
-        </is>
-      </c>
+      <c r="F73" t="inlineStr"/>
       <c r="G73" t="inlineStr">
         <is>
           <t>2027-04-09 00:00:00</t>
         </is>
       </c>
       <c r="H73" t="n">
-        <v>1.046651801284736</v>
+        <v>1.045949244267564</v>
       </c>
       <c r="I73" t="inlineStr">
         <is>
@@ -3709,12 +3697,12 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>BH INFRA</t>
+          <t>JERA2026</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>LFSN19001BH</t>
+          <t>LFSN19001BC</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
@@ -3722,18 +3710,22 @@
           <t>BRBPACLFIVQ4</t>
         </is>
       </c>
-      <c r="F74" t="inlineStr"/>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>353997-N L</t>
+        </is>
+      </c>
       <c r="G74" t="inlineStr">
         <is>
           <t>2027-04-09 00:00:00</t>
         </is>
       </c>
       <c r="H74" t="n">
-        <v>1.038705</v>
+        <v>1.045949244267564</v>
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>ISIN</t>
+          <t>MATRIZ</t>
         </is>
       </c>
       <c r="J74" t="b">
@@ -3753,7 +3745,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>FIRF GERAES</t>
+          <t>BH INFRA</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -3773,11 +3765,11 @@
         </is>
       </c>
       <c r="H75" t="n">
-        <v>1.046651801284736</v>
+        <v>1.038705</v>
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>MATRIZ</t>
+          <t>ISIN</t>
         </is>
       </c>
       <c r="J75" t="b">
@@ -3797,31 +3789,31 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>FIRF GERAES 30</t>
+          <t>FIRF GERAES</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>LFSN19006KM</t>
+          <t>LFSN19001BH</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>BRBPACLFIWC2</t>
+          <t>BRBPACLFIVQ4</t>
         </is>
       </c>
       <c r="F76" t="inlineStr"/>
       <c r="G76" t="inlineStr">
         <is>
-          <t>2028-05-31 00:00:00</t>
+          <t>2027-04-09 00:00:00</t>
         </is>
       </c>
       <c r="H76" t="n">
-        <v>1.052538</v>
+        <v>1.045949244267564</v>
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>ISIN</t>
+          <t>MATRIZ</t>
         </is>
       </c>
       <c r="J76" t="b">
@@ -3841,7 +3833,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>HORIZONTE FIM</t>
+          <t>FIRF GERAES 30</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -3885,7 +3877,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>MANACA INFRA</t>
+          <t>HORIZONTE FIM</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -3929,7 +3921,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>REAL FIM</t>
+          <t>MANACA INFRA</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -3942,22 +3934,18 @@
           <t>BRBPACLFIWC2</t>
         </is>
       </c>
-      <c r="F79" t="inlineStr">
-        <is>
-          <t>513453-LFS</t>
-        </is>
-      </c>
+      <c r="F79" t="inlineStr"/>
       <c r="G79" t="inlineStr">
         <is>
           <t>2028-05-31 00:00:00</t>
         </is>
       </c>
       <c r="H79" t="n">
-        <v>1.062598589137548</v>
+        <v>1.052538</v>
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>MATRIZ</t>
+          <t>ISIN</t>
         </is>
       </c>
       <c r="J79" t="b">
@@ -3977,12 +3965,12 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>FIRF GERAES</t>
+          <t>REAL FIM</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>LFSN19006KN</t>
+          <t>LFSN19006KM</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
@@ -3990,18 +3978,22 @@
           <t>BRBPACLFIWC2</t>
         </is>
       </c>
-      <c r="F80" t="inlineStr"/>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>513453-LFS</t>
+        </is>
+      </c>
       <c r="G80" t="inlineStr">
         <is>
           <t>2028-05-31 00:00:00</t>
         </is>
       </c>
       <c r="H80" t="n">
-        <v>1.052538</v>
+        <v>1.062068476080854</v>
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>ISIN</t>
+          <t>MATRIZ</t>
         </is>
       </c>
       <c r="J80" t="b">
@@ -4016,32 +4008,32 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>BANCO BMG S.A.</t>
+          <t>BANCO BTG PACTUAL S.A.</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>BH INFRA</t>
+          <t>FIRF GERAES</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>LFSN1900971</t>
+          <t>LFSN19006KN</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>BRBMGBLFI489</t>
+          <t>BRBPACLFIWC2</t>
         </is>
       </c>
       <c r="F81" t="inlineStr"/>
       <c r="G81" t="inlineStr">
         <is>
-          <t>2026-06-22 00:00:00</t>
+          <t>2028-05-31 00:00:00</t>
         </is>
       </c>
       <c r="H81" t="n">
-        <v>1.196383</v>
+        <v>1.052538</v>
       </c>
       <c r="I81" t="inlineStr">
         <is>
@@ -4065,7 +4057,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>BORDEAUX INFRA</t>
+          <t>BH INFRA</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -4109,7 +4101,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>CARMEL INFRA</t>
+          <t>BORDEAUX INFRA</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -4129,11 +4121,11 @@
         </is>
       </c>
       <c r="H83" t="n">
-        <v>1.116966051517022</v>
+        <v>1.196383</v>
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t>MATRIZ</t>
+          <t>ISIN</t>
         </is>
       </c>
       <c r="J83" t="b">
@@ -4153,7 +4145,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>FIRF GERAES 30</t>
+          <t>CARMEL INFRA</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -4161,11 +4153,7 @@
           <t>LFSN1900971</t>
         </is>
       </c>
-      <c r="E84" t="inlineStr">
-        <is>
-          <t>BRBMGBLFI489</t>
-        </is>
-      </c>
+      <c r="E84" t="inlineStr"/>
       <c r="F84" t="inlineStr"/>
       <c r="G84" t="inlineStr">
         <is>
@@ -4173,11 +4161,11 @@
         </is>
       </c>
       <c r="H84" t="n">
-        <v>1.196383</v>
+        <v>1.11580367512627</v>
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t>ISIN</t>
+          <t>MATRIZ</t>
         </is>
       </c>
       <c r="J84" t="b">
@@ -4197,7 +4185,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>FIRF GERAES</t>
+          <t>FIRF GERAES 30</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -4241,31 +4229,31 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>BH INFRA</t>
+          <t>FIRF GERAES</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>LFSN19009YU</t>
+          <t>LFSN1900971</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>BRBMGBLFI6I3</t>
+          <t>BRBMGBLFI489</t>
         </is>
       </c>
       <c r="F86" t="inlineStr"/>
       <c r="G86" t="inlineStr">
         <is>
-          <t>2026-06-26 00:00:00</t>
+          <t>2026-06-22 00:00:00</t>
         </is>
       </c>
       <c r="H86" t="n">
-        <v>1.117289146782183</v>
+        <v>1.196383</v>
       </c>
       <c r="I86" t="inlineStr">
         <is>
-          <t>MATRIZ</t>
+          <t>ISIN</t>
         </is>
       </c>
       <c r="J86" t="b">
@@ -4285,7 +4273,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>CARMEL INFRA</t>
+          <t>BH INFRA</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -4305,7 +4293,7 @@
         </is>
       </c>
       <c r="H87" t="n">
-        <v>1.117289146782183</v>
+        <v>1.116507075431784</v>
       </c>
       <c r="I87" t="inlineStr">
         <is>
@@ -4329,7 +4317,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>FIRF GERAES</t>
+          <t>CARMEL INFRA</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -4349,11 +4337,11 @@
         </is>
       </c>
       <c r="H88" t="n">
-        <v>1.200691</v>
+        <v>1.116507075431784</v>
       </c>
       <c r="I88" t="inlineStr">
         <is>
-          <t>ISIN</t>
+          <t>MATRIZ</t>
         </is>
       </c>
       <c r="J88" t="b">
@@ -4368,32 +4356,32 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>BANCO SAFRA S.A.</t>
+          <t>BANCO BMG S.A.</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>FIRF GERAES 30</t>
+          <t>FIRF GERAES</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>LFSN1900CR5</t>
+          <t>LFSN19009YU</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>BRBSAFLFNG47</t>
+          <t>BRBMGBLFI6I3</t>
         </is>
       </c>
       <c r="F89" t="inlineStr"/>
       <c r="G89" t="inlineStr">
         <is>
-          <t>2029-08-13 00:00:00</t>
+          <t>2026-06-26 00:00:00</t>
         </is>
       </c>
       <c r="H89" t="n">
-        <v>1.092185</v>
+        <v>1.200691</v>
       </c>
       <c r="I89" t="inlineStr">
         <is>
@@ -4407,45 +4395,41 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>CDB</t>
+          <t>LFSN</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>AGIBANK</t>
+          <t>BANCO SAFRA S.A.</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>BMG SEG</t>
+          <t>FIRF GERAES 30</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>CDB3251WXH0</t>
+          <t>LFSN1900CR5</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>BRAGBKC00M66</t>
-        </is>
-      </c>
-      <c r="F90" t="inlineStr">
-        <is>
-          <t>614522-CDB</t>
-        </is>
-      </c>
+          <t>BRBSAFLFNG47</t>
+        </is>
+      </c>
+      <c r="F90" t="inlineStr"/>
       <c r="G90" t="inlineStr">
         <is>
-          <t>2027-03-08 00:00:00</t>
+          <t>2029-08-13 00:00:00</t>
         </is>
       </c>
       <c r="H90" t="n">
-        <v>1.060547767429206</v>
+        <v>1.092185</v>
       </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t>MATRIZ</t>
+          <t>ISIN</t>
         </is>
       </c>
       <c r="J90" t="b">
@@ -4465,7 +4449,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>JERA2026</t>
+          <t>BMG SEG</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -4480,7 +4464,7 @@
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>353997-N L</t>
+          <t>614522-CDB</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
@@ -4489,7 +4473,7 @@
         </is>
       </c>
       <c r="H91" t="n">
-        <v>1.060547767429206</v>
+        <v>1.06011927746097</v>
       </c>
       <c r="I91" t="inlineStr">
         <is>
@@ -4513,7 +4497,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>REAL FIM</t>
+          <t>JERA2026</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -4537,7 +4521,7 @@
         </is>
       </c>
       <c r="H92" t="n">
-        <v>1.060547767429206</v>
+        <v>1.06011927746097</v>
       </c>
       <c r="I92" t="inlineStr">
         <is>
@@ -4556,36 +4540,36 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>BANCO XP</t>
+          <t>AGIBANK</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>BMG SEG</t>
+          <t>REAL FIM</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>LF00240072E</t>
+          <t>CDB3251WXH0</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>BRBCXPLFIKS5</t>
+          <t>BRAGBKC00M66</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>614522-CDB</t>
+          <t>353997-N L</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>2026-03-02 00:00:00</t>
+          <t>2027-03-08 00:00:00</t>
         </is>
       </c>
       <c r="H93" t="n">
-        <v>1.0225</v>
+        <v>1.06011927746097</v>
       </c>
       <c r="I93" t="inlineStr">
         <is>
@@ -4609,7 +4593,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>JERA2026</t>
+          <t>BMG SEG</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -4624,7 +4608,7 @@
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>353997-N L</t>
+          <t>614522-CDB</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
@@ -4652,7 +4636,7 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>BANCO BMG S.A.</t>
+          <t>BANCO XP</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
@@ -4662,26 +4646,26 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>LFSC19002CD</t>
+          <t>LF00240072E</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>BRBMGBLFI7Q4</t>
+          <t>BRBCXPLFIKS5</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>609712-LFS</t>
+          <t>353997-N L</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>2029-04-09 00:00:00</t>
+          <t>2026-03-02 00:00:00</t>
         </is>
       </c>
       <c r="H95" t="n">
-        <v>1.140531278354469</v>
+        <v>1.0225</v>
       </c>
       <c r="I95" t="inlineStr">
         <is>
@@ -4710,17 +4694,17 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>LFSC19002CE</t>
+          <t>LFSC19002CD</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>BRBMGBLFI7P6</t>
+          <t>BRBMGBLFI7Q4</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>609711-LFS</t>
+          <t>609712-LFS</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
@@ -4729,7 +4713,7 @@
         </is>
       </c>
       <c r="H96" t="n">
-        <v>1.140531278354469</v>
+        <v>1.139896883451567</v>
       </c>
       <c r="I96" t="inlineStr">
         <is>
@@ -4758,33 +4742,81 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
+          <t>LFSC19002CE</t>
+        </is>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>BRBMGBLFI7P6</t>
+        </is>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>609711-LFS</t>
+        </is>
+      </c>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>2029-04-09 00:00:00</t>
+        </is>
+      </c>
+      <c r="H97" t="n">
+        <v>1.139896883451567</v>
+      </c>
+      <c r="I97" t="inlineStr">
+        <is>
+          <t>MATRIZ</t>
+        </is>
+      </c>
+      <c r="J97" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>CDB</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>BANCO BMG S.A.</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>JERA2026</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
           <t>LFSC19002HS</t>
         </is>
       </c>
-      <c r="E97" t="inlineStr">
+      <c r="E98" t="inlineStr">
         <is>
           <t>BRBMGBLFI7R2</t>
         </is>
       </c>
-      <c r="F97" t="inlineStr">
+      <c r="F98" t="inlineStr">
         <is>
           <t>609713-LFS</t>
         </is>
       </c>
-      <c r="G97" t="inlineStr">
+      <c r="G98" t="inlineStr">
         <is>
           <t>2029-04-09 00:00:00</t>
         </is>
       </c>
-      <c r="H97" t="n">
-        <v>1.140531278354469</v>
-      </c>
-      <c r="I97" t="inlineStr">
+      <c r="H98" t="n">
+        <v>1.139896883451567</v>
+      </c>
+      <c r="I98" t="inlineStr">
         <is>
           <t>MATRIZ</t>
         </is>
       </c>
-      <c r="J97" t="b">
+      <c r="J98" t="b">
         <v>0</v>
       </c>
     </row>

--- a/Dados/ativos_mapeados_com_taxa_efetiva.xlsx
+++ b/Dados/ativos_mapeados_com_taxa_efetiva.xlsx
@@ -513,7 +513,7 @@
         </is>
       </c>
       <c r="H2" t="n">
-        <v>1.01480445135206</v>
+        <v>1.0569</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
@@ -557,7 +557,7 @@
         </is>
       </c>
       <c r="H3" t="n">
-        <v>1.01480445135206</v>
+        <v>1.0569</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
@@ -601,11 +601,11 @@
         </is>
       </c>
       <c r="H4" t="n">
-        <v>1.04807792075738</v>
+        <v>1.059782354033702</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>ISIN</t>
+          <t>MATRIZ</t>
         </is>
       </c>
       <c r="J4" t="b">
@@ -645,7 +645,7 @@
         </is>
       </c>
       <c r="H5" t="n">
-        <v>1.06011927746097</v>
+        <v>1.059782354033702</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
@@ -689,7 +689,7 @@
         </is>
       </c>
       <c r="H6" t="n">
-        <v>1.06011927746097</v>
+        <v>1.059782354033702</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
@@ -733,7 +733,7 @@
         </is>
       </c>
       <c r="H7" t="n">
-        <v>1.04807792075738</v>
+        <v>1.04626203797649</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
@@ -777,7 +777,7 @@
         </is>
       </c>
       <c r="H8" t="n">
-        <v>1.04807792075738</v>
+        <v>1.0462620379765</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
@@ -821,7 +821,7 @@
         </is>
       </c>
       <c r="H9" t="n">
-        <v>1.04807792075738</v>
+        <v>1.04626203797649</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
@@ -865,7 +865,7 @@
         </is>
       </c>
       <c r="H10" t="n">
-        <v>1.032491353300285</v>
+        <v>1.032489255459689</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
@@ -909,7 +909,7 @@
         </is>
       </c>
       <c r="H11" t="n">
-        <v>1.032491353300285</v>
+        <v>1.032489255459689</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
@@ -953,7 +953,7 @@
         </is>
       </c>
       <c r="H12" t="n">
-        <v>1.032491353300285</v>
+        <v>1.032489255459689</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
@@ -1001,7 +1001,7 @@
         </is>
       </c>
       <c r="H13" t="n">
-        <v>1.032491353300285</v>
+        <v>1.032489255459689</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
@@ -1045,7 +1045,7 @@
         </is>
       </c>
       <c r="H14" t="n">
-        <v>1.032491353300285</v>
+        <v>1.032489255459689</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
@@ -1093,7 +1093,7 @@
         </is>
       </c>
       <c r="H15" t="n">
-        <v>1.032491353300285</v>
+        <v>1.032489255459689</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
@@ -1137,11 +1137,11 @@
         </is>
       </c>
       <c r="H16" t="n">
-        <v>1.0125</v>
+        <v>1.015</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>ISIN</t>
+          <t>MATRIZ</t>
         </is>
       </c>
       <c r="J16" t="b">
@@ -1181,11 +1181,11 @@
         </is>
       </c>
       <c r="H17" t="n">
-        <v>1.0125</v>
+        <v>1.015</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>ISIN</t>
+          <t>MATRIZ</t>
         </is>
       </c>
       <c r="J17" t="b">
@@ -1229,7 +1229,7 @@
         </is>
       </c>
       <c r="H18" t="n">
-        <v>1.027492298438137</v>
+        <v>1.027490341344469</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
@@ -1273,7 +1273,7 @@
         </is>
       </c>
       <c r="H19" t="n">
-        <v>1.02131</v>
+        <v>1.06</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
@@ -1317,7 +1317,7 @@
         </is>
       </c>
       <c r="H20" t="n">
-        <v>1.02131</v>
+        <v>1.06</v>
       </c>
       <c r="I20" t="inlineStr">
         <is>
@@ -1365,7 +1365,7 @@
         </is>
       </c>
       <c r="H21" t="n">
-        <v>1.027492298438137</v>
+        <v>1.027490341344469</v>
       </c>
       <c r="I21" t="inlineStr">
         <is>
@@ -1453,7 +1453,7 @@
         </is>
       </c>
       <c r="H23" t="n">
-        <v>1.409698</v>
+        <v>1.313164</v>
       </c>
       <c r="I23" t="inlineStr">
         <is>
@@ -1501,7 +1501,7 @@
         </is>
       </c>
       <c r="H24" t="n">
-        <v>1.409698</v>
+        <v>1.313164</v>
       </c>
       <c r="I24" t="inlineStr">
         <is>
@@ -1545,15 +1545,15 @@
         </is>
       </c>
       <c r="H25" t="n">
-        <v>1.03756</v>
+        <v>1.036354</v>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>ISIN</t>
+          <t>NA</t>
         </is>
       </c>
       <c r="J25" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="26">
@@ -1589,7 +1589,7 @@
         </is>
       </c>
       <c r="H26" t="n">
-        <v>1.03756</v>
+        <v>1.036354</v>
       </c>
       <c r="I26" t="inlineStr">
         <is>
@@ -1633,7 +1633,7 @@
         </is>
       </c>
       <c r="H27" t="n">
-        <v>1.03756</v>
+        <v>1.036354</v>
       </c>
       <c r="I27" t="inlineStr">
         <is>
@@ -1677,7 +1677,7 @@
         </is>
       </c>
       <c r="H28" t="n">
-        <v>1.03756</v>
+        <v>1.036354</v>
       </c>
       <c r="I28" t="inlineStr">
         <is>
@@ -1725,7 +1725,7 @@
         </is>
       </c>
       <c r="H29" t="n">
-        <v>1.03756</v>
+        <v>1.036354</v>
       </c>
       <c r="I29" t="inlineStr">
         <is>
@@ -1949,7 +1949,7 @@
         </is>
       </c>
       <c r="H34" t="n">
-        <v>1.03494410423184</v>
+        <v>1.03021815694302</v>
       </c>
       <c r="I34" t="inlineStr">
         <is>
@@ -1993,7 +1993,7 @@
         </is>
       </c>
       <c r="H35" t="n">
-        <v>1.03494410423184</v>
+        <v>1.03021815694302</v>
       </c>
       <c r="I35" t="inlineStr">
         <is>
@@ -2037,7 +2037,7 @@
         </is>
       </c>
       <c r="H36" t="n">
-        <v>1.03494410423184</v>
+        <v>1.03021815694302</v>
       </c>
       <c r="I36" t="inlineStr">
         <is>
@@ -2081,7 +2081,7 @@
         </is>
       </c>
       <c r="H37" t="n">
-        <v>1.03494410423184</v>
+        <v>1.03021815694302</v>
       </c>
       <c r="I37" t="inlineStr">
         <is>
@@ -2125,7 +2125,7 @@
         </is>
       </c>
       <c r="H38" t="n">
-        <v>1.03494410423184</v>
+        <v>1.03021815694302</v>
       </c>
       <c r="I38" t="inlineStr">
         <is>
@@ -2169,7 +2169,7 @@
         </is>
       </c>
       <c r="H39" t="n">
-        <v>1.052387791224203</v>
+        <v>1.05236056905854</v>
       </c>
       <c r="I39" t="inlineStr">
         <is>
@@ -2217,7 +2217,7 @@
         </is>
       </c>
       <c r="H40" t="n">
-        <v>1.052387791224203</v>
+        <v>1.05236056905854</v>
       </c>
       <c r="I40" t="inlineStr">
         <is>
@@ -2265,7 +2265,7 @@
         </is>
       </c>
       <c r="H41" t="n">
-        <v>1.052387791224203</v>
+        <v>1.05236056905854</v>
       </c>
       <c r="I41" t="inlineStr">
         <is>
@@ -2309,7 +2309,7 @@
         </is>
       </c>
       <c r="H42" t="n">
-        <v>1.03494410423184</v>
+        <v>1.03021815694302</v>
       </c>
       <c r="I42" t="inlineStr">
         <is>
@@ -2353,7 +2353,7 @@
         </is>
       </c>
       <c r="H43" t="n">
-        <v>0.01</v>
+        <v>0.0098</v>
       </c>
       <c r="I43" t="inlineStr">
         <is>
@@ -2397,7 +2397,7 @@
         </is>
       </c>
       <c r="H44" t="n">
-        <v>0.01</v>
+        <v>0.0098</v>
       </c>
       <c r="I44" t="inlineStr">
         <is>
@@ -2441,7 +2441,7 @@
         </is>
       </c>
       <c r="H45" t="n">
-        <v>0.01</v>
+        <v>0.0098</v>
       </c>
       <c r="I45" t="inlineStr">
         <is>
@@ -2485,7 +2485,7 @@
         </is>
       </c>
       <c r="H46" t="n">
-        <v>1.77</v>
+        <v>1.18113603052</v>
       </c>
       <c r="I46" t="inlineStr">
         <is>
@@ -2529,7 +2529,7 @@
         </is>
       </c>
       <c r="H47" t="n">
-        <v>1.77</v>
+        <v>1.18113603052</v>
       </c>
       <c r="I47" t="inlineStr">
         <is>
@@ -2573,7 +2573,7 @@
         </is>
       </c>
       <c r="H48" t="n">
-        <v>1.77</v>
+        <v>1.18113603052</v>
       </c>
       <c r="I48" t="inlineStr">
         <is>
@@ -2617,7 +2617,7 @@
         </is>
       </c>
       <c r="H49" t="n">
-        <v>1.77</v>
+        <v>1.18113603052</v>
       </c>
       <c r="I49" t="inlineStr">
         <is>
@@ -2661,7 +2661,7 @@
         </is>
       </c>
       <c r="H50" t="n">
-        <v>1.77</v>
+        <v>1.18113603052</v>
       </c>
       <c r="I50" t="inlineStr">
         <is>
@@ -2705,7 +2705,7 @@
         </is>
       </c>
       <c r="H51" t="n">
-        <v>1.77</v>
+        <v>1.18113603052</v>
       </c>
       <c r="I51" t="inlineStr">
         <is>
@@ -2749,7 +2749,7 @@
         </is>
       </c>
       <c r="H52" t="n">
-        <v>1.77</v>
+        <v>1.18113603052</v>
       </c>
       <c r="I52" t="inlineStr">
         <is>
@@ -2793,7 +2793,7 @@
         </is>
       </c>
       <c r="H53" t="n">
-        <v>1.77</v>
+        <v>1.18113603052</v>
       </c>
       <c r="I53" t="inlineStr">
         <is>
@@ -2837,7 +2837,7 @@
         </is>
       </c>
       <c r="H54" t="n">
-        <v>1.77</v>
+        <v>1.18113603052</v>
       </c>
       <c r="I54" t="inlineStr">
         <is>
@@ -2881,7 +2881,7 @@
         </is>
       </c>
       <c r="H55" t="n">
-        <v>1.77</v>
+        <v>1.18113603052</v>
       </c>
       <c r="I55" t="inlineStr">
         <is>
@@ -2925,7 +2925,7 @@
         </is>
       </c>
       <c r="H56" t="n">
-        <v>1.77</v>
+        <v>1.18113603052</v>
       </c>
       <c r="I56" t="inlineStr">
         <is>
@@ -2969,7 +2969,7 @@
         </is>
       </c>
       <c r="H57" t="n">
-        <v>1.77</v>
+        <v>1.18113603052</v>
       </c>
       <c r="I57" t="inlineStr">
         <is>
@@ -3013,7 +3013,7 @@
         </is>
       </c>
       <c r="H58" t="n">
-        <v>1.77</v>
+        <v>1.18113603052</v>
       </c>
       <c r="I58" t="inlineStr">
         <is>
@@ -3057,7 +3057,7 @@
         </is>
       </c>
       <c r="H59" t="n">
-        <v>0.00450832</v>
+        <v>0.00412858</v>
       </c>
       <c r="I59" t="inlineStr">
         <is>
@@ -3101,11 +3101,11 @@
         </is>
       </c>
       <c r="H60" t="n">
-        <v>0.147727727794061</v>
+        <v>1.016528537507554</v>
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>ISIN</t>
+          <t>MATRIZ</t>
         </is>
       </c>
       <c r="J60" t="b">
@@ -3145,11 +3145,11 @@
         </is>
       </c>
       <c r="H61" t="n">
-        <v>0.147727727794061</v>
+        <v>1.003</v>
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>ISIN</t>
+          <t>MATRIZ</t>
         </is>
       </c>
       <c r="J61" t="b">
@@ -3185,7 +3185,7 @@
         </is>
       </c>
       <c r="H62" t="n">
-        <v>1.01657005808601</v>
+        <v>1.016528537507554</v>
       </c>
       <c r="I62" t="inlineStr">
         <is>
@@ -3225,7 +3225,7 @@
         </is>
       </c>
       <c r="H63" t="n">
-        <v>1.014073509362798</v>
+        <v>1.003</v>
       </c>
       <c r="I63" t="inlineStr">
         <is>
@@ -3361,7 +3361,7 @@
         </is>
       </c>
       <c r="H66" t="n">
-        <v>1.022904</v>
+        <v>1.020749</v>
       </c>
       <c r="I66" t="inlineStr">
         <is>
@@ -3405,7 +3405,7 @@
         </is>
       </c>
       <c r="H67" t="n">
-        <v>1.021813</v>
+        <v>1.016004</v>
       </c>
       <c r="I67" t="inlineStr">
         <is>
@@ -3449,7 +3449,7 @@
         </is>
       </c>
       <c r="H68" t="n">
-        <v>1.016607050561403</v>
+        <v>1.016575989734313</v>
       </c>
       <c r="I68" t="inlineStr">
         <is>
@@ -3497,7 +3497,7 @@
         </is>
       </c>
       <c r="H69" t="n">
-        <v>1.016607050561403</v>
+        <v>1.016575989734313</v>
       </c>
       <c r="I69" t="inlineStr">
         <is>
@@ -3541,7 +3541,7 @@
         </is>
       </c>
       <c r="H70" t="n">
-        <v>0.00450832</v>
+        <v>0.00412858</v>
       </c>
       <c r="I70" t="inlineStr">
         <is>
@@ -3585,7 +3585,7 @@
         </is>
       </c>
       <c r="H71" t="n">
-        <v>1.030045</v>
+        <v>1.02462</v>
       </c>
       <c r="I71" t="inlineStr">
         <is>
@@ -3629,7 +3629,7 @@
         </is>
       </c>
       <c r="H72" t="n">
-        <v>1.035227</v>
+        <v>1.030045</v>
       </c>
       <c r="I72" t="inlineStr">
         <is>
@@ -3673,7 +3673,7 @@
         </is>
       </c>
       <c r="H73" t="n">
-        <v>1.045949244267564</v>
+        <v>1.045398856829075</v>
       </c>
       <c r="I73" t="inlineStr">
         <is>
@@ -3721,7 +3721,7 @@
         </is>
       </c>
       <c r="H74" t="n">
-        <v>1.045949244267564</v>
+        <v>1.045398856829075</v>
       </c>
       <c r="I74" t="inlineStr">
         <is>
@@ -3765,11 +3765,11 @@
         </is>
       </c>
       <c r="H75" t="n">
-        <v>1.038705</v>
+        <v>1.045398856829075</v>
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>ISIN</t>
+          <t>MATRIZ</t>
         </is>
       </c>
       <c r="J75" t="b">
@@ -3809,11 +3809,11 @@
         </is>
       </c>
       <c r="H76" t="n">
-        <v>1.045949244267564</v>
+        <v>1.036336</v>
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>MATRIZ</t>
+          <t>ISIN</t>
         </is>
       </c>
       <c r="J76" t="b">
@@ -3853,7 +3853,7 @@
         </is>
       </c>
       <c r="H77" t="n">
-        <v>1.052538</v>
+        <v>1.050808</v>
       </c>
       <c r="I77" t="inlineStr">
         <is>
@@ -3897,7 +3897,7 @@
         </is>
       </c>
       <c r="H78" t="n">
-        <v>1.052538</v>
+        <v>1.050808</v>
       </c>
       <c r="I78" t="inlineStr">
         <is>
@@ -3941,7 +3941,7 @@
         </is>
       </c>
       <c r="H79" t="n">
-        <v>1.052538</v>
+        <v>1.050808</v>
       </c>
       <c r="I79" t="inlineStr">
         <is>
@@ -3989,7 +3989,7 @@
         </is>
       </c>
       <c r="H80" t="n">
-        <v>1.062068476080854</v>
+        <v>1.061626607216338</v>
       </c>
       <c r="I80" t="inlineStr">
         <is>
@@ -4033,7 +4033,7 @@
         </is>
       </c>
       <c r="H81" t="n">
-        <v>1.052538</v>
+        <v>1.050808</v>
       </c>
       <c r="I81" t="inlineStr">
         <is>
@@ -4077,11 +4077,11 @@
         </is>
       </c>
       <c r="H82" t="n">
-        <v>1.196383</v>
+        <v>1.113579137078064</v>
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>ISIN</t>
+          <t>MATRIZ</t>
         </is>
       </c>
       <c r="J82" t="b">
@@ -4121,7 +4121,7 @@
         </is>
       </c>
       <c r="H83" t="n">
-        <v>1.196383</v>
+        <v>1.187403</v>
       </c>
       <c r="I83" t="inlineStr">
         <is>
@@ -4161,7 +4161,7 @@
         </is>
       </c>
       <c r="H84" t="n">
-        <v>1.11580367512627</v>
+        <v>1.113579137078064</v>
       </c>
       <c r="I84" t="inlineStr">
         <is>
@@ -4205,7 +4205,7 @@
         </is>
       </c>
       <c r="H85" t="n">
-        <v>1.196383</v>
+        <v>1.187403</v>
       </c>
       <c r="I85" t="inlineStr">
         <is>
@@ -4249,7 +4249,7 @@
         </is>
       </c>
       <c r="H86" t="n">
-        <v>1.196383</v>
+        <v>1.187403</v>
       </c>
       <c r="I86" t="inlineStr">
         <is>
@@ -4293,7 +4293,7 @@
         </is>
       </c>
       <c r="H87" t="n">
-        <v>1.116507075431784</v>
+        <v>1.115289929595834</v>
       </c>
       <c r="I87" t="inlineStr">
         <is>
@@ -4337,7 +4337,7 @@
         </is>
       </c>
       <c r="H88" t="n">
-        <v>1.116507075431784</v>
+        <v>1.115289929595834</v>
       </c>
       <c r="I88" t="inlineStr">
         <is>
@@ -4381,7 +4381,7 @@
         </is>
       </c>
       <c r="H89" t="n">
-        <v>1.200691</v>
+        <v>1.187403</v>
       </c>
       <c r="I89" t="inlineStr">
         <is>
@@ -4425,7 +4425,7 @@
         </is>
       </c>
       <c r="H90" t="n">
-        <v>1.092185</v>
+        <v>1.088496</v>
       </c>
       <c r="I90" t="inlineStr">
         <is>
@@ -4473,7 +4473,7 @@
         </is>
       </c>
       <c r="H91" t="n">
-        <v>1.06011927746097</v>
+        <v>1.059782354033702</v>
       </c>
       <c r="I91" t="inlineStr">
         <is>
@@ -4521,7 +4521,7 @@
         </is>
       </c>
       <c r="H92" t="n">
-        <v>1.06011927746097</v>
+        <v>1.059782354033702</v>
       </c>
       <c r="I92" t="inlineStr">
         <is>
@@ -4569,7 +4569,7 @@
         </is>
       </c>
       <c r="H93" t="n">
-        <v>1.06011927746097</v>
+        <v>1.059782354033702</v>
       </c>
       <c r="I93" t="inlineStr">
         <is>
@@ -4713,7 +4713,7 @@
         </is>
       </c>
       <c r="H96" t="n">
-        <v>1.139896883451567</v>
+        <v>1.139413068351466</v>
       </c>
       <c r="I96" t="inlineStr">
         <is>
@@ -4761,7 +4761,7 @@
         </is>
       </c>
       <c r="H97" t="n">
-        <v>1.139896883451567</v>
+        <v>1.139413068351466</v>
       </c>
       <c r="I97" t="inlineStr">
         <is>
@@ -4809,7 +4809,7 @@
         </is>
       </c>
       <c r="H98" t="n">
-        <v>1.139896883451567</v>
+        <v>1.139413068351466</v>
       </c>
       <c r="I98" t="inlineStr">
         <is>

--- a/Dados/ativos_mapeados_com_taxa_efetiva.xlsx
+++ b/Dados/ativos_mapeados_com_taxa_efetiva.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J98"/>
+  <dimension ref="A1:J99"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -513,11 +513,11 @@
         </is>
       </c>
       <c r="H2" t="n">
-        <v>1.0569</v>
+        <v>1.016679840302595</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>ISIN</t>
+          <t>MATRIZ</t>
         </is>
       </c>
       <c r="J2" t="b">
@@ -557,11 +557,11 @@
         </is>
       </c>
       <c r="H3" t="n">
-        <v>1.0569</v>
+        <v>1.016679840302595</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>ISIN</t>
+          <t>MATRIZ</t>
         </is>
       </c>
       <c r="J3" t="b">
@@ -576,32 +576,28 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>AGIBANK</t>
+          <t>BANCO BTG PACTUAL S.A.</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>BH INFRA</t>
+          <t>FIRF GERAES</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>CDB3251WXH0</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>BRAGBKC00M66</t>
-        </is>
-      </c>
+          <t>CDB3239C4TL</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr"/>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>2027-03-08 00:00:00</t>
+          <t>2026-07-20 00:00:00</t>
         </is>
       </c>
       <c r="H4" t="n">
-        <v>1.059782354033702</v>
+        <v>1.016679840302595</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
@@ -625,7 +621,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>BMG SEG</t>
+          <t>BH INFRA</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -645,7 +641,7 @@
         </is>
       </c>
       <c r="H5" t="n">
-        <v>1.059782354033702</v>
+        <v>1.058550815989044</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
@@ -669,7 +665,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>CARMEL INFRA</t>
+          <t>BMG SEG</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -689,7 +685,7 @@
         </is>
       </c>
       <c r="H6" t="n">
-        <v>1.059782354033702</v>
+        <v>1.058550815989044</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
@@ -713,7 +709,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>FIRF GERAES 30</t>
+          <t>CARMEL INFRA</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -733,7 +729,7 @@
         </is>
       </c>
       <c r="H7" t="n">
-        <v>1.04626203797649</v>
+        <v>1.04537937504615</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
@@ -757,7 +753,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>FIRF GERAES</t>
+          <t>FIRF GERAES 30</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -777,7 +773,7 @@
         </is>
       </c>
       <c r="H8" t="n">
-        <v>1.0462620379765</v>
+        <v>1.04537937504615</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
@@ -801,7 +797,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>TOPAZIO INFRA</t>
+          <t>FIRF GERAES</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -821,7 +817,7 @@
         </is>
       </c>
       <c r="H9" t="n">
-        <v>1.04626203797649</v>
+        <v>1.04537937504615</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
@@ -840,36 +836,36 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>PARANA BANCO S.A.</t>
+          <t>AGIBANK</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>BH INFRA</t>
+          <t>TOPAZIO INFRA</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>CDB3253PPYA</t>
+          <t>CDB3251WXH0</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>BRPRBCC059P8</t>
+          <t>BRAGBKC00M66</t>
         </is>
       </c>
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
-          <t>2026-03-10 00:00:00</t>
+          <t>2027-03-08 00:00:00</t>
         </is>
       </c>
       <c r="H10" t="n">
-        <v>1.032489255459689</v>
+        <v>1.04537937504615</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>MATRIZ</t>
+          <t>ISIN</t>
         </is>
       </c>
       <c r="J10" t="b">
@@ -889,7 +885,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>FIRF GERAES 30</t>
+          <t>BH INFRA</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -909,7 +905,7 @@
         </is>
       </c>
       <c r="H11" t="n">
-        <v>1.032489255459689</v>
+        <v>1.032479330249586</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
@@ -933,7 +929,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>FIRF GERAES</t>
+          <t>FIRF GERAES 30</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -953,7 +949,7 @@
         </is>
       </c>
       <c r="H12" t="n">
-        <v>1.032489255459689</v>
+        <v>1.032479330249586</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
@@ -977,7 +973,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>JERA2026</t>
+          <t>FIRF GERAES</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -990,18 +986,14 @@
           <t>BRPRBCC059P8</t>
         </is>
       </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>606488-CDB</t>
-        </is>
-      </c>
+      <c r="F13" t="inlineStr"/>
       <c r="G13" t="inlineStr">
         <is>
           <t>2026-03-10 00:00:00</t>
         </is>
       </c>
       <c r="H13" t="n">
-        <v>1.032489255459689</v>
+        <v>1.032479330249586</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
@@ -1025,7 +1017,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>MANACA INFRA</t>
+          <t>JERA2026</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -1038,14 +1030,18 @@
           <t>BRPRBCC059P8</t>
         </is>
       </c>
-      <c r="F14" t="inlineStr"/>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>606488-CDB</t>
+        </is>
+      </c>
       <c r="G14" t="inlineStr">
         <is>
           <t>2026-03-10 00:00:00</t>
         </is>
       </c>
       <c r="H14" t="n">
-        <v>1.032489255459689</v>
+        <v>1.032479330249586</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
@@ -1069,7 +1065,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>REAL FIM</t>
+          <t>MANACA INFRA</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -1082,18 +1078,14 @@
           <t>BRPRBCC059P8</t>
         </is>
       </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>606488-CDB</t>
-        </is>
-      </c>
+      <c r="F15" t="inlineStr"/>
       <c r="G15" t="inlineStr">
         <is>
           <t>2026-03-10 00:00:00</t>
         </is>
       </c>
       <c r="H15" t="n">
-        <v>1.032489255459689</v>
+        <v>1.032479330249586</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
@@ -1112,32 +1104,36 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>BANCO VOLKSWAGEN S/A</t>
+          <t>PARANA BANCO S.A.</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>BBRASIL FIM CP RESP</t>
+          <t>REAL FIM</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>CDB424EERW3</t>
+          <t>CDB3253PPYA</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>BRBVKWC00WA0</t>
-        </is>
-      </c>
-      <c r="F16" t="inlineStr"/>
+          <t>BRPRBCC059P8</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>606488-CDB</t>
+        </is>
+      </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>2026-05-04 00:00:00</t>
+          <t>2026-03-10 00:00:00</t>
         </is>
       </c>
       <c r="H16" t="n">
-        <v>1.015</v>
+        <v>1.032479330249586</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
@@ -1161,7 +1157,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>BBRASIL FIM</t>
+          <t>BBRASIL FIM CP RESP</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -1200,36 +1196,32 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>BANCO INTER SA</t>
+          <t>BANCO VOLKSWAGEN S/A</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>REAL FIM</t>
+          <t>BBRASIL FIM</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>CDB7257QUDF</t>
+          <t>CDB424EERW3</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>BRBIDIC002H4</t>
-        </is>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>613312-CDB</t>
-        </is>
-      </c>
+          <t>BRBVKWC00WA0</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr"/>
       <c r="G18" t="inlineStr">
         <is>
-          <t>2026-07-10 00:00:00</t>
+          <t>2026-05-04 00:00:00</t>
         </is>
       </c>
       <c r="H18" t="n">
-        <v>1.027490341344469</v>
+        <v>1.015</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
@@ -1253,12 +1245,12 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>FIRF GERAES</t>
+          <t>REAL FIM</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>CDB7257QUDG</t>
+          <t>CDB7257QUDF</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -1266,18 +1258,22 @@
           <t>BRBIDIC002H4</t>
         </is>
       </c>
-      <c r="F19" t="inlineStr"/>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>613312-CDB</t>
+        </is>
+      </c>
       <c r="G19" t="inlineStr">
         <is>
           <t>2026-07-10 00:00:00</t>
         </is>
       </c>
       <c r="H19" t="n">
-        <v>1.06</v>
+        <v>1.027481208289491</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>ISIN</t>
+          <t>MATRIZ</t>
         </is>
       </c>
       <c r="J19" t="b">
@@ -1297,12 +1293,12 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>FIRF GERAES 30</t>
+          <t>FIRF GERAES</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>CDB7257QUDH</t>
+          <t>CDB7257QUDG</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -1341,12 +1337,12 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>BMG SEG</t>
+          <t>FIRF GERAES 30</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>CDB7257QUDI</t>
+          <t>CDB7257QUDH</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -1354,22 +1350,18 @@
           <t>BRBIDIC002H4</t>
         </is>
       </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>613315-CDB</t>
-        </is>
-      </c>
+      <c r="F21" t="inlineStr"/>
       <c r="G21" t="inlineStr">
         <is>
           <t>2026-07-10 00:00:00</t>
         </is>
       </c>
       <c r="H21" t="n">
-        <v>1.027490341344469</v>
+        <v>1.06</v>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>MATRIZ</t>
+          <t>ISIN</t>
         </is>
       </c>
       <c r="J21" t="b">
@@ -1384,32 +1376,36 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>BANCO VOLKSWAGEN S/A</t>
+          <t>BANCO INTER SA</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>BBRASIL FIM CP RESP</t>
+          <t>BMG SEG</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>CDB925CDN0L</t>
+          <t>CDB7257QUDI</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>BRBVKWC01543</t>
-        </is>
-      </c>
-      <c r="F22" t="inlineStr"/>
+          <t>BRBIDIC002H4</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>613315-CDB</t>
+        </is>
+      </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>2025-12-22 00:00:00</t>
+          <t>2026-07-10 00:00:00</t>
         </is>
       </c>
       <c r="H22" t="n">
-        <v>1.015</v>
+        <v>1.027481208289491</v>
       </c>
       <c r="I22" t="inlineStr">
         <is>
@@ -1423,41 +1419,41 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Debêntures</t>
+          <t>CDB</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>HAPVIDA PARTICIPACOES E INVESTIMENTOS S/A</t>
+          <t>BANCO VOLKSWAGEN S/A</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>FIRF GERAES</t>
+          <t>BBRASIL FIM CP RESP</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>HAPV21</t>
+          <t>CDB925CDN0L</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>BRHAPVDBS014</t>
+          <t>BRBVKWC01543</t>
         </is>
       </c>
       <c r="F23" t="inlineStr"/>
       <c r="G23" t="inlineStr">
         <is>
-          <t>2026-07-10 00:00:00</t>
+          <t>2025-12-22 00:00:00</t>
         </is>
       </c>
       <c r="H23" t="n">
-        <v>1.313164</v>
+        <v>1.015</v>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>ISIN</t>
+          <t>MATRIZ</t>
         </is>
       </c>
       <c r="J23" t="b">
@@ -1477,7 +1473,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>JERA2026</t>
+          <t>FIRF GERAES</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -1490,26 +1486,22 @@
           <t>BRHAPVDBS014</t>
         </is>
       </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>362409-HAP</t>
-        </is>
-      </c>
+      <c r="F24" t="inlineStr"/>
       <c r="G24" t="inlineStr">
         <is>
           <t>2026-07-10 00:00:00</t>
         </is>
       </c>
       <c r="H24" t="n">
-        <v>1.313164</v>
+        <v>1.312943</v>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>ISIN</t>
         </is>
       </c>
       <c r="J24" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="25">
@@ -1520,32 +1512,36 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>KLABIN S/A</t>
+          <t>HAPVIDA PARTICIPACOES E INVESTIMENTOS S/A</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>BH INFRA</t>
+          <t>JERA2026</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>KLBNA2</t>
+          <t>HAPV21</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>BRKLBNDBS004</t>
-        </is>
-      </c>
-      <c r="F25" t="inlineStr"/>
+          <t>BRHAPVDBS014</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>362409-HAP</t>
+        </is>
+      </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>2029-03-19 00:00:00</t>
+          <t>2026-07-10 00:00:00</t>
         </is>
       </c>
       <c r="H25" t="n">
-        <v>1.036354</v>
+        <v>1.312943</v>
       </c>
       <c r="I25" t="inlineStr">
         <is>
@@ -1569,7 +1565,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>FIRF GERAES 30</t>
+          <t>BH INFRA</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -1589,15 +1585,15 @@
         </is>
       </c>
       <c r="H26" t="n">
-        <v>1.036354</v>
+        <v>1.031817</v>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>ISIN</t>
+          <t>NA</t>
         </is>
       </c>
       <c r="J26" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="27">
@@ -1613,7 +1609,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>FIRF GERAES</t>
+          <t>FIRF GERAES 30</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -1633,7 +1629,7 @@
         </is>
       </c>
       <c r="H27" t="n">
-        <v>1.036354</v>
+        <v>1.031817</v>
       </c>
       <c r="I27" t="inlineStr">
         <is>
@@ -1657,7 +1653,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>HORIZONTE FIM</t>
+          <t>FIRF GERAES</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -1677,7 +1673,7 @@
         </is>
       </c>
       <c r="H28" t="n">
-        <v>1.036354</v>
+        <v>1.031817</v>
       </c>
       <c r="I28" t="inlineStr">
         <is>
@@ -1701,7 +1697,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>REAL FIM</t>
+          <t>HORIZONTE FIM</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -1714,70 +1710,70 @@
           <t>BRKLBNDBS004</t>
         </is>
       </c>
-      <c r="F29" t="inlineStr">
-        <is>
-          <t>353017-KLB</t>
-        </is>
-      </c>
+      <c r="F29" t="inlineStr"/>
       <c r="G29" t="inlineStr">
         <is>
           <t>2029-03-19 00:00:00</t>
         </is>
       </c>
       <c r="H29" t="n">
-        <v>1.036354</v>
+        <v>1.031817</v>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>ISIN</t>
         </is>
       </c>
       <c r="J29" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Letra Financeira</t>
+          <t>Debêntures</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>BANCO XP</t>
+          <t>KLABIN S/A</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>BMG SEG</t>
+          <t>REAL FIM</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LF00240072E</t>
+          <t>KLBNA2</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>BRBCXPLFIKS5</t>
-        </is>
-      </c>
-      <c r="F30" t="inlineStr"/>
+          <t>BRKLBNDBS004</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>353017-KLB</t>
+        </is>
+      </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>2026-03-02 00:00:00</t>
+          <t>2029-03-19 00:00:00</t>
         </is>
       </c>
       <c r="H30" t="n">
-        <v>1.0225</v>
+        <v>1.031817</v>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>MATRIZ</t>
+          <t>NA</t>
         </is>
       </c>
       <c r="J30" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="31">
@@ -1793,23 +1789,23 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>FIRF GERAES</t>
+          <t>BMG SEG</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LF0024007Y4</t>
+          <t>LF00240072E</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>BRBCXPLFIO68</t>
+          <t>BRBCXPLFIKS5</t>
         </is>
       </c>
       <c r="F31" t="inlineStr"/>
       <c r="G31" t="inlineStr">
         <is>
-          <t>2026-03-16 00:00:00</t>
+          <t>2026-03-02 00:00:00</t>
         </is>
       </c>
       <c r="H31" t="n">
@@ -1827,7 +1823,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>CDB</t>
+          <t>Letra Financeira</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1837,27 +1833,23 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>BMG SEG</t>
+          <t>FIRF GERAES</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LF0024008OB</t>
+          <t>LF0024007Y4</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>BRBCXPLFIO76</t>
-        </is>
-      </c>
-      <c r="F32" t="inlineStr">
-        <is>
-          <t>614522-CDB</t>
-        </is>
-      </c>
+          <t>BRBCXPLFIO68</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr"/>
       <c r="G32" t="inlineStr">
         <is>
-          <t>2026-03-23 00:00:00</t>
+          <t>2026-03-16 00:00:00</t>
         </is>
       </c>
       <c r="H32" t="n">
@@ -1875,7 +1867,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Letra Financeira</t>
+          <t>CDB</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -1885,7 +1877,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>FIRF GERAES</t>
+          <t>BMG SEG</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -1898,7 +1890,11 @@
           <t>BRBCXPLFIO76</t>
         </is>
       </c>
-      <c r="F33" t="inlineStr"/>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>614522-CDB</t>
+        </is>
+      </c>
       <c r="G33" t="inlineStr">
         <is>
           <t>2026-03-23 00:00:00</t>
@@ -1924,36 +1920,36 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>BANCO MERCANTIL DO BRASIL S.A.</t>
+          <t>BANCO XP</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>FIRF GERAES 30</t>
+          <t>FIRF GERAES</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LF002400KBT</t>
+          <t>LF0024008OB</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>BRBMEBLFI8V4</t>
+          <t>BRBCXPLFIO76</t>
         </is>
       </c>
       <c r="F34" t="inlineStr"/>
       <c r="G34" t="inlineStr">
         <is>
-          <t>2026-07-31 00:00:00</t>
+          <t>2026-03-23 00:00:00</t>
         </is>
       </c>
       <c r="H34" t="n">
-        <v>1.03021815694302</v>
+        <v>1.0225</v>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>ISIN</t>
+          <t>MATRIZ</t>
         </is>
       </c>
       <c r="J34" t="b">
@@ -1973,12 +1969,12 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>FIRF GERAES</t>
+          <t>FIRF GERAES 30</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LF002400KBU</t>
+          <t>LF002400KBT</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
@@ -1993,7 +1989,7 @@
         </is>
       </c>
       <c r="H35" t="n">
-        <v>1.03021815694302</v>
+        <v>1.02858992832202</v>
       </c>
       <c r="I35" t="inlineStr">
         <is>
@@ -2022,7 +2018,7 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LF002400KBW</t>
+          <t>LF002400KBU</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
@@ -2037,7 +2033,7 @@
         </is>
       </c>
       <c r="H36" t="n">
-        <v>1.03021815694302</v>
+        <v>1.02858992832202</v>
       </c>
       <c r="I36" t="inlineStr">
         <is>
@@ -2061,12 +2057,12 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>MANACA INFRA</t>
+          <t>FIRF GERAES</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>LF002400KBX</t>
+          <t>LF002400KBW</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
@@ -2081,7 +2077,7 @@
         </is>
       </c>
       <c r="H37" t="n">
-        <v>1.03021815694302</v>
+        <v>1.02858992832202</v>
       </c>
       <c r="I37" t="inlineStr">
         <is>
@@ -2105,12 +2101,12 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>FIRF GERAES 30</t>
+          <t>MANACA INFRA</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>LF002400KBY</t>
+          <t>LF002400KBX</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
@@ -2125,7 +2121,7 @@
         </is>
       </c>
       <c r="H38" t="n">
-        <v>1.03021815694302</v>
+        <v>1.02858992832202</v>
       </c>
       <c r="I38" t="inlineStr">
         <is>
@@ -2149,12 +2145,12 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>BMG SEG</t>
+          <t>FIRF GERAES 30</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>LF002400KC0</t>
+          <t>LF002400KBY</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
@@ -2169,11 +2165,11 @@
         </is>
       </c>
       <c r="H39" t="n">
-        <v>1.05236056905854</v>
+        <v>1.02858992832202</v>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>MATRIZ</t>
+          <t>ISIN</t>
         </is>
       </c>
       <c r="J39" t="b">
@@ -2193,7 +2189,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>JERA2026</t>
+          <t>BMG SEG</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -2206,18 +2202,14 @@
           <t>BRBMEBLFI8V4</t>
         </is>
       </c>
-      <c r="F40" t="inlineStr">
-        <is>
-          <t>567797-LF0</t>
-        </is>
-      </c>
+      <c r="F40" t="inlineStr"/>
       <c r="G40" t="inlineStr">
         <is>
           <t>2026-07-31 00:00:00</t>
         </is>
       </c>
       <c r="H40" t="n">
-        <v>1.05236056905854</v>
+        <v>1.052138784815274</v>
       </c>
       <c r="I40" t="inlineStr">
         <is>
@@ -2241,12 +2233,12 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>REAL FIM</t>
+          <t>JERA2026</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>LF002400KC1</t>
+          <t>LF002400KC0</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
@@ -2256,7 +2248,7 @@
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>567798-LF0</t>
+          <t>567797-LF0</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
@@ -2265,7 +2257,7 @@
         </is>
       </c>
       <c r="H41" t="n">
-        <v>1.05236056905854</v>
+        <v>1.052138784815274</v>
       </c>
       <c r="I41" t="inlineStr">
         <is>
@@ -2289,12 +2281,12 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>TOPAZIO INFRA</t>
+          <t>REAL FIM</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>LF002400KC2</t>
+          <t>LF002400KC1</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
@@ -2302,18 +2294,22 @@
           <t>BRBMEBLFI8V4</t>
         </is>
       </c>
-      <c r="F42" t="inlineStr"/>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>567798-LF0</t>
+        </is>
+      </c>
       <c r="G42" t="inlineStr">
         <is>
           <t>2026-07-31 00:00:00</t>
         </is>
       </c>
       <c r="H42" t="n">
-        <v>1.03021815694302</v>
+        <v>1.052138784815274</v>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>ISIN</t>
+          <t>MATRIZ</t>
         </is>
       </c>
       <c r="J42" t="b">
@@ -2323,37 +2319,37 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>LFSC</t>
+          <t>Letra Financeira</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>BANCO ABC BRASIL S.A.</t>
+          <t>BANCO MERCANTIL DO BRASIL S.A.</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>FIRF GERAES</t>
+          <t>TOPAZIO INFRA</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>LFSC19003FD</t>
+          <t>LF002400KC2</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>BRABCBLFN7I2</t>
+          <t>BRBMEBLFI8V4</t>
         </is>
       </c>
       <c r="F43" t="inlineStr"/>
       <c r="G43" t="inlineStr">
         <is>
-          <t>2024-10-17 00:00:00</t>
+          <t>2026-07-31 00:00:00</t>
         </is>
       </c>
       <c r="H43" t="n">
-        <v>0.0098</v>
+        <v>1.02858992832202</v>
       </c>
       <c r="I43" t="inlineStr">
         <is>
@@ -2377,12 +2373,12 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>HORIZONTE FIM</t>
+          <t>FIRF GERAES</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>LFSC19003W3</t>
+          <t>LFSC19003FD</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
@@ -2397,7 +2393,7 @@
         </is>
       </c>
       <c r="H44" t="n">
-        <v>0.0098</v>
+        <v>0.009000000000000001</v>
       </c>
       <c r="I44" t="inlineStr">
         <is>
@@ -2421,12 +2417,12 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>FIRF GERAES 30</t>
+          <t>HORIZONTE FIM</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>LFSC19003W4</t>
+          <t>LFSC19003W3</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
@@ -2441,7 +2437,7 @@
         </is>
       </c>
       <c r="H45" t="n">
-        <v>0.0098</v>
+        <v>0.009000000000000001</v>
       </c>
       <c r="I45" t="inlineStr">
         <is>
@@ -2460,32 +2456,32 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>BANCO DO NORDESTE DO BRASIL S.A.</t>
+          <t>BANCO ABC BRASIL S.A.</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>HORIZONTE FIM</t>
+          <t>FIRF GERAES 30</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>LFSC190054C</t>
+          <t>LFSC19003W4</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>BRBNBRLFI013</t>
+          <t>BRABCBLFN7I2</t>
         </is>
       </c>
       <c r="F46" t="inlineStr"/>
       <c r="G46" t="inlineStr">
         <is>
-          <t>2024-06-11 00:00:00</t>
+          <t>2024-10-17 00:00:00</t>
         </is>
       </c>
       <c r="H46" t="n">
-        <v>1.18113603052</v>
+        <v>0.009000000000000001</v>
       </c>
       <c r="I46" t="inlineStr">
         <is>
@@ -2509,17 +2505,17 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>BH INFRA</t>
+          <t>HORIZONTE FIM</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>LFSC190054D</t>
+          <t>LFSC190054C</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>BRBNBRLFI021</t>
+          <t>BRBNBRLFI013</t>
         </is>
       </c>
       <c r="F47" t="inlineStr"/>
@@ -2553,7 +2549,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>FIRF GERAES</t>
+          <t>BH INFRA</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -2597,7 +2593,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>HORIZONTE FIM</t>
+          <t>FIRF GERAES</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -2641,7 +2637,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>MANACA INFRA</t>
+          <t>HORIZONTE FIM</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -2685,23 +2681,23 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>FIRF GERAES 30</t>
+          <t>MANACA INFRA</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>LFSC190054I</t>
+          <t>LFSC190054D</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>BRBNBRLFI039</t>
+          <t>BRBNBRLFI021</t>
         </is>
       </c>
       <c r="F51" t="inlineStr"/>
       <c r="G51" t="inlineStr">
         <is>
-          <t>2024-06-12 00:00:00</t>
+          <t>2024-06-11 00:00:00</t>
         </is>
       </c>
       <c r="H51" t="n">
@@ -2729,7 +2725,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>HORIZONTE FIM</t>
+          <t>FIRF GERAES 30</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -2778,12 +2774,12 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>LFSC190059S</t>
+          <t>LFSC190054I</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>BRBNBRLFI062</t>
+          <t>BRBNBRLFI039</t>
         </is>
       </c>
       <c r="F53" t="inlineStr"/>
@@ -2817,23 +2813,23 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>FIRF GERAES 30</t>
+          <t>HORIZONTE FIM</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>LFSC19005FF</t>
+          <t>LFSC190059S</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>BRBNBRLFI0C5</t>
+          <t>BRBNBRLFI062</t>
         </is>
       </c>
       <c r="F54" t="inlineStr"/>
       <c r="G54" t="inlineStr">
         <is>
-          <t>2024-06-18 00:00:00</t>
+          <t>2024-06-12 00:00:00</t>
         </is>
       </c>
       <c r="H54" t="n">
@@ -2861,7 +2857,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>HORIZONTE FIM</t>
+          <t>FIRF GERAES 30</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -2910,18 +2906,18 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>LFSC19005L1</t>
+          <t>LFSC19005FF</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>BRBNBRLFI0F8</t>
+          <t>BRBNBRLFI0C5</t>
         </is>
       </c>
       <c r="F56" t="inlineStr"/>
       <c r="G56" t="inlineStr">
         <is>
-          <t>2024-06-19 00:00:00</t>
+          <t>2024-06-18 00:00:00</t>
         </is>
       </c>
       <c r="H56" t="n">
@@ -2949,23 +2945,23 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>BH INFRA</t>
+          <t>HORIZONTE FIM</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>LFSC19005L3</t>
+          <t>LFSC19005L1</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>BRBNBRLFI0G6</t>
+          <t>BRBNBRLFI0F8</t>
         </is>
       </c>
       <c r="F57" t="inlineStr"/>
       <c r="G57" t="inlineStr">
         <is>
-          <t>2024-06-21 00:00:00</t>
+          <t>2024-06-19 00:00:00</t>
         </is>
       </c>
       <c r="H57" t="n">
@@ -2993,7 +2989,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>FIRF GERAES 30</t>
+          <t>BH INFRA</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -3032,7 +3028,7 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>BANCO ABC BRASIL S.A.</t>
+          <t>BANCO DO NORDESTE DO BRASIL S.A.</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -3042,22 +3038,22 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>LFSC19007G2</t>
+          <t>LFSC19005L3</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>BRABCBLFIM30</t>
+          <t>BRBNBRLFI0G6</t>
         </is>
       </c>
       <c r="F59" t="inlineStr"/>
       <c r="G59" t="inlineStr">
         <is>
-          <t>2024-10-17 00:00:00</t>
+          <t>2024-06-21 00:00:00</t>
         </is>
       </c>
       <c r="H59" t="n">
-        <v>0.00412858</v>
+        <v>1.18113603052</v>
       </c>
       <c r="I59" t="inlineStr">
         <is>
@@ -3071,41 +3067,41 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>LFSN</t>
+          <t>LFSC</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>BANCO SAFRA S.A.</t>
+          <t>BANCO ABC BRASIL S.A.</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>BH INFRA</t>
+          <t>FIRF GERAES 30</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>LFSN1800D4W</t>
+          <t>LFSC19007G2</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>BRBSAFLNND73</t>
+          <t>BRABCBLFIM30</t>
         </is>
       </c>
       <c r="F60" t="inlineStr"/>
       <c r="G60" t="inlineStr">
         <is>
-          <t>2026-06-08 00:00:00</t>
+          <t>2024-10-17 00:00:00</t>
         </is>
       </c>
       <c r="H60" t="n">
-        <v>1.016528537507554</v>
+        <v>0.00399851</v>
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>MATRIZ</t>
+          <t>ISIN</t>
         </is>
       </c>
       <c r="J60" t="b">
@@ -3141,11 +3137,11 @@
       <c r="F61" t="inlineStr"/>
       <c r="G61" t="inlineStr">
         <is>
-          <t>2026-08-06 00:00:00</t>
+          <t>2026-06-08 00:00:00</t>
         </is>
       </c>
       <c r="H61" t="n">
-        <v>1.003</v>
+        <v>1.016226620178901</v>
       </c>
       <c r="I61" t="inlineStr">
         <is>
@@ -3169,7 +3165,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>CARMEL INFRA</t>
+          <t>BH INFRA</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -3177,15 +3173,19 @@
           <t>LFSN1800D4W</t>
         </is>
       </c>
-      <c r="E62" t="inlineStr"/>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>BRBSAFLNND73</t>
+        </is>
+      </c>
       <c r="F62" t="inlineStr"/>
       <c r="G62" t="inlineStr">
         <is>
-          <t>2026-06-08 00:00:00</t>
+          <t>2026-08-06 00:00:00</t>
         </is>
       </c>
       <c r="H62" t="n">
-        <v>1.016528537507554</v>
+        <v>1.003</v>
       </c>
       <c r="I62" t="inlineStr">
         <is>
@@ -3221,11 +3221,11 @@
       <c r="F63" t="inlineStr"/>
       <c r="G63" t="inlineStr">
         <is>
-          <t>2026-08-06 00:00:00</t>
+          <t>2026-06-08 00:00:00</t>
         </is>
       </c>
       <c r="H63" t="n">
-        <v>1.003</v>
+        <v>1.016226620178901</v>
       </c>
       <c r="I63" t="inlineStr">
         <is>
@@ -3244,7 +3244,7 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>BANCO BRADESCO S.A.</t>
+          <t>BANCO SAFRA S.A.</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -3254,18 +3254,14 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>LFSN1800DG1</t>
-        </is>
-      </c>
-      <c r="E64" t="inlineStr">
-        <is>
-          <t>BRBBDCLTR2X9</t>
-        </is>
-      </c>
+          <t>LFSN1800D4W</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr"/>
       <c r="F64" t="inlineStr"/>
       <c r="G64" t="inlineStr">
         <is>
-          <t>2026-08-03 00:00:00</t>
+          <t>2026-08-06 00:00:00</t>
         </is>
       </c>
       <c r="H64" t="n">
@@ -3293,7 +3289,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>JERA2026</t>
+          <t>CARMEL INFRA</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -3306,22 +3302,18 @@
           <t>BRBBDCLTR2X9</t>
         </is>
       </c>
-      <c r="F65" t="inlineStr">
-        <is>
-          <t>407137-LFS</t>
-        </is>
-      </c>
+      <c r="F65" t="inlineStr"/>
       <c r="G65" t="inlineStr">
         <is>
           <t>2026-08-03 00:00:00</t>
         </is>
       </c>
       <c r="H65" t="n">
-        <v>1.003</v>
+        <v>1.020749</v>
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>MATRIZ</t>
+          <t>ISIN</t>
         </is>
       </c>
       <c r="J65" t="b">
@@ -3341,31 +3333,35 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>FIRF GERAES</t>
+          <t>JERA2026</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>LFSN1800DIG</t>
+          <t>LFSN1800DG1</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>BRBBDCLTROH4</t>
-        </is>
-      </c>
-      <c r="F66" t="inlineStr"/>
+          <t>BRBBDCLTR2X9</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>407137-LFS</t>
+        </is>
+      </c>
       <c r="G66" t="inlineStr">
         <is>
           <t>2026-08-03 00:00:00</t>
         </is>
       </c>
       <c r="H66" t="n">
-        <v>1.020749</v>
+        <v>1.003</v>
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>ISIN</t>
+          <t>MATRIZ</t>
         </is>
       </c>
       <c r="J66" t="b">
@@ -3380,32 +3376,32 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>BANCO SAFRA S.A.</t>
+          <t>BANCO BRADESCO S.A.</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>BORDEAUX INFRA</t>
+          <t>FIRF GERAES</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>LFSN1800DS5</t>
+          <t>LFSN1800DIG</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>BRBSAFLNN8B3</t>
+          <t>BRBBDCLTROH4</t>
         </is>
       </c>
       <c r="F67" t="inlineStr"/>
       <c r="G67" t="inlineStr">
         <is>
-          <t>2026-08-17 00:00:00</t>
+          <t>2026-08-03 00:00:00</t>
         </is>
       </c>
       <c r="H67" t="n">
-        <v>1.016004</v>
+        <v>1.020749</v>
       </c>
       <c r="I67" t="inlineStr">
         <is>
@@ -3429,7 +3425,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>CARMEL INFRA</t>
+          <t>BORDEAUX INFRA</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -3449,11 +3445,11 @@
         </is>
       </c>
       <c r="H68" t="n">
-        <v>1.016575989734313</v>
+        <v>1.012998</v>
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>MATRIZ</t>
+          <t>ISIN</t>
         </is>
       </c>
       <c r="J68" t="b">
@@ -3473,7 +3469,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>JERA2026</t>
+          <t>CARMEL INFRA</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -3486,22 +3482,18 @@
           <t>BRBSAFLNN8B3</t>
         </is>
       </c>
-      <c r="F69" t="inlineStr">
-        <is>
-          <t>335769-LFS</t>
-        </is>
-      </c>
+      <c r="F69" t="inlineStr"/>
       <c r="G69" t="inlineStr">
         <is>
           <t>2026-08-17 00:00:00</t>
         </is>
       </c>
       <c r="H69" t="n">
-        <v>1.016575989734313</v>
+        <v>1.012998</v>
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>MATRIZ</t>
+          <t>ISIN</t>
         </is>
       </c>
       <c r="J69" t="b">
@@ -3516,36 +3508,40 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>BANCO ABC BRASIL S.A.</t>
+          <t>BANCO SAFRA S.A.</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>FIRF GERAES</t>
+          <t>JERA2026</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>LFSN1800E2G</t>
+          <t>LFSN1800DS5</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>BRABCBLFIM22</t>
-        </is>
-      </c>
-      <c r="F70" t="inlineStr"/>
+          <t>BRBSAFLNN8B3</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>335769-LFS</t>
+        </is>
+      </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>2025-09-29 00:00:00</t>
+          <t>2026-08-17 00:00:00</t>
         </is>
       </c>
       <c r="H70" t="n">
-        <v>0.00412858</v>
+        <v>1.016379649932376</v>
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>ISIN</t>
+          <t>MATRIZ</t>
         </is>
       </c>
       <c r="J70" t="b">
@@ -3560,7 +3556,7 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>BANCO SAFRA S.A.</t>
+          <t>BANCO ABC BRASIL S.A.</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
@@ -3570,22 +3566,22 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>LFSN1800HXO</t>
+          <t>LFSN1800E2G</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>BRBSAFLNN7R1</t>
+          <t>BRABCBLFIM22</t>
         </is>
       </c>
       <c r="F71" t="inlineStr"/>
       <c r="G71" t="inlineStr">
         <is>
-          <t>2026-11-06 00:00:00</t>
+          <t>2025-09-29 00:00:00</t>
         </is>
       </c>
       <c r="H71" t="n">
-        <v>1.02462</v>
+        <v>0.00399851</v>
       </c>
       <c r="I71" t="inlineStr">
         <is>
@@ -3614,22 +3610,22 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>LFSN1900008</t>
+          <t>LFSN1800HXO</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>BRBSAFLFNBB5</t>
+          <t>BRBSAFLNN7R1</t>
         </is>
       </c>
       <c r="F72" t="inlineStr"/>
       <c r="G72" t="inlineStr">
         <is>
-          <t>2027-01-08 00:00:00</t>
+          <t>2026-11-06 00:00:00</t>
         </is>
       </c>
       <c r="H72" t="n">
-        <v>1.030045</v>
+        <v>1.021813</v>
       </c>
       <c r="I72" t="inlineStr">
         <is>
@@ -3648,36 +3644,36 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>BANCO BTG PACTUAL S.A.</t>
+          <t>BANCO SAFRA S.A.</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>CARMEL INFRA</t>
+          <t>FIRF GERAES</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>LFSN19001BC</t>
+          <t>LFSN1900008</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>BRBPACLFIVQ4</t>
+          <t>BRBSAFLFNBB5</t>
         </is>
       </c>
       <c r="F73" t="inlineStr"/>
       <c r="G73" t="inlineStr">
         <is>
-          <t>2027-04-09 00:00:00</t>
+          <t>2027-01-08 00:00:00</t>
         </is>
       </c>
       <c r="H73" t="n">
-        <v>1.045398856829075</v>
+        <v>1.027364</v>
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>MATRIZ</t>
+          <t>ISIN</t>
         </is>
       </c>
       <c r="J73" t="b">
@@ -3697,7 +3693,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>JERA2026</t>
+          <t>CARMEL INFRA</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -3710,22 +3706,18 @@
           <t>BRBPACLFIVQ4</t>
         </is>
       </c>
-      <c r="F74" t="inlineStr">
-        <is>
-          <t>353997-N L</t>
-        </is>
-      </c>
+      <c r="F74" t="inlineStr"/>
       <c r="G74" t="inlineStr">
         <is>
           <t>2027-04-09 00:00:00</t>
         </is>
       </c>
       <c r="H74" t="n">
-        <v>1.045398856829075</v>
+        <v>1.035107</v>
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>MATRIZ</t>
+          <t>ISIN</t>
         </is>
       </c>
       <c r="J74" t="b">
@@ -3745,12 +3737,12 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>BH INFRA</t>
+          <t>JERA2026</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>LFSN19001BH</t>
+          <t>LFSN19001BC</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
@@ -3758,14 +3750,18 @@
           <t>BRBPACLFIVQ4</t>
         </is>
       </c>
-      <c r="F75" t="inlineStr"/>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>353997-N L</t>
+        </is>
+      </c>
       <c r="G75" t="inlineStr">
         <is>
           <t>2027-04-09 00:00:00</t>
         </is>
       </c>
       <c r="H75" t="n">
-        <v>1.045398856829075</v>
+        <v>1.043402160663369</v>
       </c>
       <c r="I75" t="inlineStr">
         <is>
@@ -3789,7 +3785,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>FIRF GERAES</t>
+          <t>BH INFRA</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -3809,11 +3805,11 @@
         </is>
       </c>
       <c r="H76" t="n">
-        <v>1.036336</v>
+        <v>1.043402160663369</v>
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>ISIN</t>
+          <t>MATRIZ</t>
         </is>
       </c>
       <c r="J76" t="b">
@@ -3833,27 +3829,27 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>FIRF GERAES 30</t>
+          <t>FIRF GERAES</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>LFSN19006KM</t>
+          <t>LFSN19001BH</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>BRBPACLFIWC2</t>
+          <t>BRBPACLFIVQ4</t>
         </is>
       </c>
       <c r="F77" t="inlineStr"/>
       <c r="G77" t="inlineStr">
         <is>
-          <t>2028-05-31 00:00:00</t>
+          <t>2027-04-09 00:00:00</t>
         </is>
       </c>
       <c r="H77" t="n">
-        <v>1.050808</v>
+        <v>1.035107</v>
       </c>
       <c r="I77" t="inlineStr">
         <is>
@@ -3877,7 +3873,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>HORIZONTE FIM</t>
+          <t>FIRF GERAES 30</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -3897,7 +3893,7 @@
         </is>
       </c>
       <c r="H78" t="n">
-        <v>1.050808</v>
+        <v>1.049916</v>
       </c>
       <c r="I78" t="inlineStr">
         <is>
@@ -3921,7 +3917,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>MANACA INFRA</t>
+          <t>HORIZONTE FIM</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -3941,7 +3937,7 @@
         </is>
       </c>
       <c r="H79" t="n">
-        <v>1.050808</v>
+        <v>1.049916</v>
       </c>
       <c r="I79" t="inlineStr">
         <is>
@@ -3965,7 +3961,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>REAL FIM</t>
+          <t>MANACA INFRA</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -3978,22 +3974,18 @@
           <t>BRBPACLFIWC2</t>
         </is>
       </c>
-      <c r="F80" t="inlineStr">
-        <is>
-          <t>513453-LFS</t>
-        </is>
-      </c>
+      <c r="F80" t="inlineStr"/>
       <c r="G80" t="inlineStr">
         <is>
           <t>2028-05-31 00:00:00</t>
         </is>
       </c>
       <c r="H80" t="n">
-        <v>1.061626607216338</v>
+        <v>1.049916</v>
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>MATRIZ</t>
+          <t>ISIN</t>
         </is>
       </c>
       <c r="J80" t="b">
@@ -4013,12 +4005,12 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>FIRF GERAES</t>
+          <t>REAL FIM</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>LFSN19006KN</t>
+          <t>LFSN19006KM</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
@@ -4026,18 +4018,22 @@
           <t>BRBPACLFIWC2</t>
         </is>
       </c>
-      <c r="F81" t="inlineStr"/>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>513453-LFS</t>
+        </is>
+      </c>
       <c r="G81" t="inlineStr">
         <is>
           <t>2028-05-31 00:00:00</t>
         </is>
       </c>
       <c r="H81" t="n">
-        <v>1.050808</v>
+        <v>1.060074022977964</v>
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>ISIN</t>
+          <t>MATRIZ</t>
         </is>
       </c>
       <c r="J81" t="b">
@@ -4052,36 +4048,36 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>BANCO BMG S.A.</t>
+          <t>BANCO BTG PACTUAL S.A.</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>BH INFRA</t>
+          <t>FIRF GERAES</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>LFSN1900971</t>
+          <t>LFSN19006KN</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>BRBMGBLFI489</t>
+          <t>BRBPACLFIWC2</t>
         </is>
       </c>
       <c r="F82" t="inlineStr"/>
       <c r="G82" t="inlineStr">
         <is>
-          <t>2026-06-22 00:00:00</t>
+          <t>2028-05-31 00:00:00</t>
         </is>
       </c>
       <c r="H82" t="n">
-        <v>1.113579137078064</v>
+        <v>1.049916</v>
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>MATRIZ</t>
+          <t>ISIN</t>
         </is>
       </c>
       <c r="J82" t="b">
@@ -4101,7 +4097,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>BORDEAUX INFRA</t>
+          <t>BH INFRA</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -4121,11 +4117,11 @@
         </is>
       </c>
       <c r="H83" t="n">
-        <v>1.187403</v>
+        <v>1.07</v>
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t>ISIN</t>
+          <t>MATRIZ</t>
         </is>
       </c>
       <c r="J83" t="b">
@@ -4145,7 +4141,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>CARMEL INFRA</t>
+          <t>BORDEAUX INFRA</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -4153,7 +4149,11 @@
           <t>LFSN1900971</t>
         </is>
       </c>
-      <c r="E84" t="inlineStr"/>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>BRBMGBLFI489</t>
+        </is>
+      </c>
       <c r="F84" t="inlineStr"/>
       <c r="G84" t="inlineStr">
         <is>
@@ -4161,7 +4161,7 @@
         </is>
       </c>
       <c r="H84" t="n">
-        <v>1.113579137078064</v>
+        <v>1.07</v>
       </c>
       <c r="I84" t="inlineStr">
         <is>
@@ -4185,7 +4185,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>FIRF GERAES 30</t>
+          <t>CARMEL INFRA</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -4193,11 +4193,7 @@
           <t>LFSN1900971</t>
         </is>
       </c>
-      <c r="E85" t="inlineStr">
-        <is>
-          <t>BRBMGBLFI489</t>
-        </is>
-      </c>
+      <c r="E85" t="inlineStr"/>
       <c r="F85" t="inlineStr"/>
       <c r="G85" t="inlineStr">
         <is>
@@ -4205,11 +4201,11 @@
         </is>
       </c>
       <c r="H85" t="n">
-        <v>1.187403</v>
+        <v>1.07</v>
       </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t>ISIN</t>
+          <t>MATRIZ</t>
         </is>
       </c>
       <c r="J85" t="b">
@@ -4229,7 +4225,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>FIRF GERAES</t>
+          <t>FIRF GERAES 30</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -4249,11 +4245,11 @@
         </is>
       </c>
       <c r="H86" t="n">
-        <v>1.187403</v>
+        <v>1.07</v>
       </c>
       <c r="I86" t="inlineStr">
         <is>
-          <t>ISIN</t>
+          <t>MATRIZ</t>
         </is>
       </c>
       <c r="J86" t="b">
@@ -4273,27 +4269,27 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>BH INFRA</t>
+          <t>FIRF GERAES</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>LFSN19009YU</t>
+          <t>LFSN1900971</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>BRBMGBLFI6I3</t>
+          <t>BRBMGBLFI489</t>
         </is>
       </c>
       <c r="F87" t="inlineStr"/>
       <c r="G87" t="inlineStr">
         <is>
-          <t>2026-06-26 00:00:00</t>
+          <t>2026-06-22 00:00:00</t>
         </is>
       </c>
       <c r="H87" t="n">
-        <v>1.115289929595834</v>
+        <v>1.07</v>
       </c>
       <c r="I87" t="inlineStr">
         <is>
@@ -4317,7 +4313,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>CARMEL INFRA</t>
+          <t>BH INFRA</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -4337,7 +4333,7 @@
         </is>
       </c>
       <c r="H88" t="n">
-        <v>1.115289929595834</v>
+        <v>1.07</v>
       </c>
       <c r="I88" t="inlineStr">
         <is>
@@ -4361,7 +4357,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>FIRF GERAES</t>
+          <t>CARMEL INFRA</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -4381,11 +4377,11 @@
         </is>
       </c>
       <c r="H89" t="n">
-        <v>1.187403</v>
+        <v>1.07</v>
       </c>
       <c r="I89" t="inlineStr">
         <is>
-          <t>ISIN</t>
+          <t>MATRIZ</t>
         </is>
       </c>
       <c r="J89" t="b">
@@ -4400,36 +4396,36 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>BANCO SAFRA S.A.</t>
+          <t>BANCO BMG S.A.</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>FIRF GERAES 30</t>
+          <t>FIRF GERAES</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>LFSN1900CR5</t>
+          <t>LFSN19009YU</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>BRBSAFLFNG47</t>
+          <t>BRBMGBLFI6I3</t>
         </is>
       </c>
       <c r="F90" t="inlineStr"/>
       <c r="G90" t="inlineStr">
         <is>
-          <t>2029-08-13 00:00:00</t>
+          <t>2026-06-26 00:00:00</t>
         </is>
       </c>
       <c r="H90" t="n">
-        <v>1.088496</v>
+        <v>1.07</v>
       </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t>ISIN</t>
+          <t>MATRIZ</t>
         </is>
       </c>
       <c r="J90" t="b">
@@ -4439,45 +4435,41 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>CDB</t>
+          <t>LFSN</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>AGIBANK</t>
+          <t>BANCO SAFRA S.A.</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>BMG SEG</t>
+          <t>FIRF GERAES 30</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>CDB3251WXH0</t>
+          <t>LFSN1900CR5</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>BRAGBKC00M66</t>
-        </is>
-      </c>
-      <c r="F91" t="inlineStr">
-        <is>
-          <t>614522-CDB</t>
-        </is>
-      </c>
+          <t>BRBSAFLFNG47</t>
+        </is>
+      </c>
+      <c r="F91" t="inlineStr"/>
       <c r="G91" t="inlineStr">
         <is>
-          <t>2027-03-08 00:00:00</t>
+          <t>2029-08-13 00:00:00</t>
         </is>
       </c>
       <c r="H91" t="n">
-        <v>1.059782354033702</v>
+        <v>1.087205</v>
       </c>
       <c r="I91" t="inlineStr">
         <is>
-          <t>MATRIZ</t>
+          <t>ISIN</t>
         </is>
       </c>
       <c r="J91" t="b">
@@ -4497,7 +4489,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>JERA2026</t>
+          <t>BMG SEG</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -4512,7 +4504,7 @@
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>353997-N L</t>
+          <t>614522-CDB</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
@@ -4521,7 +4513,7 @@
         </is>
       </c>
       <c r="H92" t="n">
-        <v>1.059782354033702</v>
+        <v>1.058550815989044</v>
       </c>
       <c r="I92" t="inlineStr">
         <is>
@@ -4545,7 +4537,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>REAL FIM</t>
+          <t>JERA2026</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -4569,7 +4561,7 @@
         </is>
       </c>
       <c r="H93" t="n">
-        <v>1.059782354033702</v>
+        <v>1.058550815989044</v>
       </c>
       <c r="I93" t="inlineStr">
         <is>
@@ -4588,36 +4580,36 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>BANCO XP</t>
+          <t>AGIBANK</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>BMG SEG</t>
+          <t>REAL FIM</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>LF00240072E</t>
+          <t>CDB3251WXH0</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>BRBCXPLFIKS5</t>
+          <t>BRAGBKC00M66</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>614522-CDB</t>
+          <t>353997-N L</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>2026-03-02 00:00:00</t>
+          <t>2027-03-08 00:00:00</t>
         </is>
       </c>
       <c r="H94" t="n">
-        <v>1.0225</v>
+        <v>1.058550815989044</v>
       </c>
       <c r="I94" t="inlineStr">
         <is>
@@ -4641,7 +4633,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>JERA2026</t>
+          <t>BMG SEG</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -4656,7 +4648,7 @@
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>353997-N L</t>
+          <t>614522-CDB</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
@@ -4684,7 +4676,7 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>BANCO BMG S.A.</t>
+          <t>BANCO XP</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
@@ -4694,26 +4686,26 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>LFSC19002CD</t>
+          <t>LF00240072E</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>BRBMGBLFI7Q4</t>
+          <t>BRBCXPLFIKS5</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>609712-LFS</t>
+          <t>353997-N L</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>2029-04-09 00:00:00</t>
+          <t>2026-03-02 00:00:00</t>
         </is>
       </c>
       <c r="H96" t="n">
-        <v>1.139413068351466</v>
+        <v>1.0225</v>
       </c>
       <c r="I96" t="inlineStr">
         <is>
@@ -4742,17 +4734,17 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>LFSC19002CE</t>
+          <t>LFSC19002CD</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>BRBMGBLFI7P6</t>
+          <t>BRBMGBLFI7Q4</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>609711-LFS</t>
+          <t>609712-LFS</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
@@ -4761,7 +4753,7 @@
         </is>
       </c>
       <c r="H97" t="n">
-        <v>1.139413068351466</v>
+        <v>1.137748629076882</v>
       </c>
       <c r="I97" t="inlineStr">
         <is>
@@ -4790,33 +4782,81 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
+          <t>LFSC19002CE</t>
+        </is>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>BRBMGBLFI7P6</t>
+        </is>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>609711-LFS</t>
+        </is>
+      </c>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>2029-04-09 00:00:00</t>
+        </is>
+      </c>
+      <c r="H98" t="n">
+        <v>1.137748629076882</v>
+      </c>
+      <c r="I98" t="inlineStr">
+        <is>
+          <t>MATRIZ</t>
+        </is>
+      </c>
+      <c r="J98" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>CDB</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>BANCO BMG S.A.</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>JERA2026</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
           <t>LFSC19002HS</t>
         </is>
       </c>
-      <c r="E98" t="inlineStr">
+      <c r="E99" t="inlineStr">
         <is>
           <t>BRBMGBLFI7R2</t>
         </is>
       </c>
-      <c r="F98" t="inlineStr">
+      <c r="F99" t="inlineStr">
         <is>
           <t>609713-LFS</t>
         </is>
       </c>
-      <c r="G98" t="inlineStr">
+      <c r="G99" t="inlineStr">
         <is>
           <t>2029-04-09 00:00:00</t>
         </is>
       </c>
-      <c r="H98" t="n">
-        <v>1.139413068351466</v>
-      </c>
-      <c r="I98" t="inlineStr">
+      <c r="H99" t="n">
+        <v>1.137748629076882</v>
+      </c>
+      <c r="I99" t="inlineStr">
         <is>
           <t>MATRIZ</t>
         </is>
       </c>
-      <c r="J98" t="b">
+      <c r="J99" t="b">
         <v>0</v>
       </c>
     </row>

--- a/Dados/ativos_mapeados_com_taxa_efetiva.xlsx
+++ b/Dados/ativos_mapeados_com_taxa_efetiva.xlsx
@@ -513,7 +513,7 @@
         </is>
       </c>
       <c r="H2" t="n">
-        <v>1.016679840302595</v>
+        <v>1.016511732460023</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
@@ -557,7 +557,7 @@
         </is>
       </c>
       <c r="H3" t="n">
-        <v>1.016679840302595</v>
+        <v>1.016511732460023</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
@@ -597,7 +597,7 @@
         </is>
       </c>
       <c r="H4" t="n">
-        <v>1.016679840302595</v>
+        <v>1.016511732460023</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
@@ -641,7 +641,7 @@
         </is>
       </c>
       <c r="H5" t="n">
-        <v>1.058550815989044</v>
+        <v>1.035313360558953</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
@@ -685,7 +685,7 @@
         </is>
       </c>
       <c r="H6" t="n">
-        <v>1.058550815989044</v>
+        <v>1.035313360558953</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
@@ -861,11 +861,11 @@
         </is>
       </c>
       <c r="H10" t="n">
-        <v>1.04537937504615</v>
+        <v>1.035313360558953</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>ISIN</t>
+          <t>MATRIZ</t>
         </is>
       </c>
       <c r="J10" t="b">
@@ -905,7 +905,7 @@
         </is>
       </c>
       <c r="H11" t="n">
-        <v>1.032479330249586</v>
+        <v>1.032476523828006</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
@@ -949,7 +949,7 @@
         </is>
       </c>
       <c r="H12" t="n">
-        <v>1.032479330249586</v>
+        <v>1.032476523828006</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
@@ -993,7 +993,7 @@
         </is>
       </c>
       <c r="H13" t="n">
-        <v>1.032479330249586</v>
+        <v>1.032476523828006</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
@@ -1041,7 +1041,7 @@
         </is>
       </c>
       <c r="H14" t="n">
-        <v>1.032479330249586</v>
+        <v>1.032476523828006</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
@@ -1085,7 +1085,7 @@
         </is>
       </c>
       <c r="H15" t="n">
-        <v>1.032479330249586</v>
+        <v>1.032476523828006</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
@@ -1133,7 +1133,7 @@
         </is>
       </c>
       <c r="H16" t="n">
-        <v>1.032479330249586</v>
+        <v>1.032476523828006</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
@@ -1269,7 +1269,7 @@
         </is>
       </c>
       <c r="H19" t="n">
-        <v>1.027481208289491</v>
+        <v>1.0274786630262</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
@@ -1405,7 +1405,7 @@
         </is>
       </c>
       <c r="H22" t="n">
-        <v>1.027481208289491</v>
+        <v>1.0274786630262</v>
       </c>
       <c r="I22" t="inlineStr">
         <is>
@@ -1493,7 +1493,7 @@
         </is>
       </c>
       <c r="H24" t="n">
-        <v>1.312943</v>
+        <v>1.307094</v>
       </c>
       <c r="I24" t="inlineStr">
         <is>
@@ -1541,7 +1541,7 @@
         </is>
       </c>
       <c r="H25" t="n">
-        <v>1.312943</v>
+        <v>1.307094</v>
       </c>
       <c r="I25" t="inlineStr">
         <is>
@@ -1585,7 +1585,7 @@
         </is>
       </c>
       <c r="H26" t="n">
-        <v>1.031817</v>
+        <v>1.030641</v>
       </c>
       <c r="I26" t="inlineStr">
         <is>
@@ -1629,7 +1629,7 @@
         </is>
       </c>
       <c r="H27" t="n">
-        <v>1.031817</v>
+        <v>1.030641</v>
       </c>
       <c r="I27" t="inlineStr">
         <is>
@@ -1673,7 +1673,7 @@
         </is>
       </c>
       <c r="H28" t="n">
-        <v>1.031817</v>
+        <v>1.030641</v>
       </c>
       <c r="I28" t="inlineStr">
         <is>
@@ -1717,7 +1717,7 @@
         </is>
       </c>
       <c r="H29" t="n">
-        <v>1.031817</v>
+        <v>1.030641</v>
       </c>
       <c r="I29" t="inlineStr">
         <is>
@@ -1765,7 +1765,7 @@
         </is>
       </c>
       <c r="H30" t="n">
-        <v>1.031817</v>
+        <v>1.030641</v>
       </c>
       <c r="I30" t="inlineStr">
         <is>
@@ -2209,7 +2209,7 @@
         </is>
       </c>
       <c r="H40" t="n">
-        <v>1.052138784815274</v>
+        <v>1.046169955658442</v>
       </c>
       <c r="I40" t="inlineStr">
         <is>
@@ -2257,7 +2257,7 @@
         </is>
       </c>
       <c r="H41" t="n">
-        <v>1.052138784815274</v>
+        <v>1.046169955658442</v>
       </c>
       <c r="I41" t="inlineStr">
         <is>
@@ -2305,7 +2305,7 @@
         </is>
       </c>
       <c r="H42" t="n">
-        <v>1.052138784815274</v>
+        <v>1.046169955658442</v>
       </c>
       <c r="I42" t="inlineStr">
         <is>
@@ -2349,11 +2349,11 @@
         </is>
       </c>
       <c r="H43" t="n">
-        <v>1.02858992832202</v>
+        <v>1.046169955658442</v>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>ISIN</t>
+          <t>MATRIZ</t>
         </is>
       </c>
       <c r="J43" t="b">
@@ -3141,7 +3141,7 @@
         </is>
       </c>
       <c r="H61" t="n">
-        <v>1.016226620178901</v>
+        <v>1.016085755815899</v>
       </c>
       <c r="I61" t="inlineStr">
         <is>
@@ -3225,7 +3225,7 @@
         </is>
       </c>
       <c r="H63" t="n">
-        <v>1.016226620178901</v>
+        <v>1.016085755815899</v>
       </c>
       <c r="I63" t="inlineStr">
         <is>
@@ -3309,7 +3309,7 @@
         </is>
       </c>
       <c r="H65" t="n">
-        <v>1.020749</v>
+        <v>1.020018</v>
       </c>
       <c r="I65" t="inlineStr">
         <is>
@@ -3401,7 +3401,7 @@
         </is>
       </c>
       <c r="H67" t="n">
-        <v>1.020749</v>
+        <v>1.020018</v>
       </c>
       <c r="I67" t="inlineStr">
         <is>
@@ -3537,7 +3537,7 @@
         </is>
       </c>
       <c r="H70" t="n">
-        <v>1.016379649932376</v>
+        <v>1.016302694975625</v>
       </c>
       <c r="I70" t="inlineStr">
         <is>
@@ -3761,7 +3761,7 @@
         </is>
       </c>
       <c r="H75" t="n">
-        <v>1.043402160663369</v>
+        <v>1.04296980890625</v>
       </c>
       <c r="I75" t="inlineStr">
         <is>
@@ -3805,7 +3805,7 @@
         </is>
       </c>
       <c r="H76" t="n">
-        <v>1.043402160663369</v>
+        <v>1.04296980890625</v>
       </c>
       <c r="I76" t="inlineStr">
         <is>
@@ -4029,7 +4029,7 @@
         </is>
       </c>
       <c r="H81" t="n">
-        <v>1.060074022977964</v>
+        <v>1.059747868494567</v>
       </c>
       <c r="I81" t="inlineStr">
         <is>
@@ -4513,7 +4513,7 @@
         </is>
       </c>
       <c r="H92" t="n">
-        <v>1.058550815989044</v>
+        <v>1.035313360558953</v>
       </c>
       <c r="I92" t="inlineStr">
         <is>
@@ -4561,7 +4561,7 @@
         </is>
       </c>
       <c r="H93" t="n">
-        <v>1.058550815989044</v>
+        <v>1.035313360558953</v>
       </c>
       <c r="I93" t="inlineStr">
         <is>
@@ -4609,7 +4609,7 @@
         </is>
       </c>
       <c r="H94" t="n">
-        <v>1.058550815989044</v>
+        <v>1.035313360558953</v>
       </c>
       <c r="I94" t="inlineStr">
         <is>
@@ -4753,7 +4753,7 @@
         </is>
       </c>
       <c r="H97" t="n">
-        <v>1.137748629076882</v>
+        <v>1.07740539991251</v>
       </c>
       <c r="I97" t="inlineStr">
         <is>
@@ -4801,7 +4801,7 @@
         </is>
       </c>
       <c r="H98" t="n">
-        <v>1.137748629076882</v>
+        <v>1.07740539991251</v>
       </c>
       <c r="I98" t="inlineStr">
         <is>
@@ -4849,7 +4849,7 @@
         </is>
       </c>
       <c r="H99" t="n">
-        <v>1.137748629076882</v>
+        <v>1.07740539991251</v>
       </c>
       <c r="I99" t="inlineStr">
         <is>

--- a/Dados/ativos_mapeados_com_taxa_efetiva.xlsx
+++ b/Dados/ativos_mapeados_com_taxa_efetiva.xlsx
@@ -589,7 +589,11 @@
           <t>CDB3239C4TL</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr"/>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>BRBPACC0F3U7</t>
+        </is>
+      </c>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
@@ -597,11 +601,11 @@
         </is>
       </c>
       <c r="H4" t="n">
-        <v>1.016511732460023</v>
+        <v>1.0569</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>MATRIZ</t>
+          <t>ISIN</t>
         </is>
       </c>
       <c r="J4" t="b">

--- a/Dados/ativos_mapeados_com_taxa_efetiva.xlsx
+++ b/Dados/ativos_mapeados_com_taxa_efetiva.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J99"/>
+  <dimension ref="A1:J100"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -513,7 +513,7 @@
         </is>
       </c>
       <c r="H2" t="n">
-        <v>1.016511732460023</v>
+        <v>1.02</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
@@ -557,7 +557,7 @@
         </is>
       </c>
       <c r="H3" t="n">
-        <v>1.016511732460023</v>
+        <v>1.02</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
@@ -645,7 +645,7 @@
         </is>
       </c>
       <c r="H5" t="n">
-        <v>1.035313360558953</v>
+        <v>1.034885761650082</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
@@ -689,7 +689,7 @@
         </is>
       </c>
       <c r="H6" t="n">
-        <v>1.035313360558953</v>
+        <v>1.034885761650082</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
@@ -845,7 +845,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>TOPAZIO INFRA</t>
+          <t>REAL FIM</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -865,7 +865,7 @@
         </is>
       </c>
       <c r="H10" t="n">
-        <v>1.035313360558953</v>
+        <v>1.034885761650082</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
@@ -884,32 +884,32 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>PARANA BANCO S.A.</t>
+          <t>AGIBANK</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>BH INFRA</t>
+          <t>TOPAZIO INFRA</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>CDB3253PPYA</t>
+          <t>CDB3251WXH0</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>BRPRBCC059P8</t>
+          <t>BRAGBKC00M66</t>
         </is>
       </c>
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr">
         <is>
-          <t>2026-03-10 00:00:00</t>
+          <t>2027-03-08 00:00:00</t>
         </is>
       </c>
       <c r="H11" t="n">
-        <v>1.032476523828006</v>
+        <v>1.034885761650082</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
@@ -933,7 +933,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>FIRF GERAES 30</t>
+          <t>BH INFRA</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -953,7 +953,7 @@
         </is>
       </c>
       <c r="H12" t="n">
-        <v>1.032476523828006</v>
+        <v>1.032449941153846</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
@@ -977,7 +977,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>FIRF GERAES</t>
+          <t>FIRF GERAES 30</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -997,7 +997,7 @@
         </is>
       </c>
       <c r="H13" t="n">
-        <v>1.032476523828006</v>
+        <v>1.032449941153846</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
@@ -1021,7 +1021,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>JERA2026</t>
+          <t>FIRF GERAES</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -1034,18 +1034,14 @@
           <t>BRPRBCC059P8</t>
         </is>
       </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>606488-CDB</t>
-        </is>
-      </c>
+      <c r="F14" t="inlineStr"/>
       <c r="G14" t="inlineStr">
         <is>
           <t>2026-03-10 00:00:00</t>
         </is>
       </c>
       <c r="H14" t="n">
-        <v>1.032476523828006</v>
+        <v>1.032449941153846</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
@@ -1069,7 +1065,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>MANACA INFRA</t>
+          <t>JERA2026</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -1082,14 +1078,18 @@
           <t>BRPRBCC059P8</t>
         </is>
       </c>
-      <c r="F15" t="inlineStr"/>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>606488-CDB</t>
+        </is>
+      </c>
       <c r="G15" t="inlineStr">
         <is>
           <t>2026-03-10 00:00:00</t>
         </is>
       </c>
       <c r="H15" t="n">
-        <v>1.032476523828006</v>
+        <v>1.032449941153846</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
@@ -1113,7 +1113,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>REAL FIM</t>
+          <t>MANACA INFRA</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -1126,18 +1126,14 @@
           <t>BRPRBCC059P8</t>
         </is>
       </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>606488-CDB</t>
-        </is>
-      </c>
+      <c r="F16" t="inlineStr"/>
       <c r="G16" t="inlineStr">
         <is>
           <t>2026-03-10 00:00:00</t>
         </is>
       </c>
       <c r="H16" t="n">
-        <v>1.032476523828006</v>
+        <v>1.032449941153846</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
@@ -1156,32 +1152,36 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>BANCO VOLKSWAGEN S/A</t>
+          <t>PARANA BANCO S.A.</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>BBRASIL FIM CP RESP</t>
+          <t>REAL FIM</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>CDB424EERW3</t>
+          <t>CDB3253PPYA</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>BRBVKWC00WA0</t>
-        </is>
-      </c>
-      <c r="F17" t="inlineStr"/>
+          <t>BRPRBCC059P8</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>606488-CDB</t>
+        </is>
+      </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>2026-05-04 00:00:00</t>
+          <t>2026-03-10 00:00:00</t>
         </is>
       </c>
       <c r="H17" t="n">
-        <v>1.015</v>
+        <v>1.032449941153846</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
@@ -1205,7 +1205,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>BBRASIL FIM</t>
+          <t>BBRASIL FIM CP RESP</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -1225,7 +1225,7 @@
         </is>
       </c>
       <c r="H18" t="n">
-        <v>1.015</v>
+        <v>1.02</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
@@ -1244,36 +1244,32 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>BANCO INTER SA</t>
+          <t>BANCO VOLKSWAGEN S/A</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>REAL FIM</t>
+          <t>BBRASIL FIM</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>CDB7257QUDF</t>
+          <t>CDB424EERW3</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>BRBIDIC002H4</t>
-        </is>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>613312-CDB</t>
-        </is>
-      </c>
+          <t>BRBVKWC00WA0</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr"/>
       <c r="G19" t="inlineStr">
         <is>
-          <t>2026-07-10 00:00:00</t>
+          <t>2026-05-04 00:00:00</t>
         </is>
       </c>
       <c r="H19" t="n">
-        <v>1.0274786630262</v>
+        <v>1.02</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
@@ -1297,12 +1293,12 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>FIRF GERAES</t>
+          <t>REAL FIM</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>CDB7257QUDG</t>
+          <t>CDB7257QUDF</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -1310,18 +1306,22 @@
           <t>BRBIDIC002H4</t>
         </is>
       </c>
-      <c r="F20" t="inlineStr"/>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>613312-CDB</t>
+        </is>
+      </c>
       <c r="G20" t="inlineStr">
         <is>
           <t>2026-07-10 00:00:00</t>
         </is>
       </c>
       <c r="H20" t="n">
-        <v>1.06</v>
+        <v>1.027455331736998</v>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>ISIN</t>
+          <t>MATRIZ</t>
         </is>
       </c>
       <c r="J20" t="b">
@@ -1341,12 +1341,12 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>FIRF GERAES 30</t>
+          <t>FIRF GERAES</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>CDB7257QUDH</t>
+          <t>CDB7257QUDG</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -1385,12 +1385,12 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>BMG SEG</t>
+          <t>FIRF GERAES 30</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>CDB7257QUDI</t>
+          <t>CDB7257QUDH</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -1398,22 +1398,18 @@
           <t>BRBIDIC002H4</t>
         </is>
       </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>613315-CDB</t>
-        </is>
-      </c>
+      <c r="F22" t="inlineStr"/>
       <c r="G22" t="inlineStr">
         <is>
           <t>2026-07-10 00:00:00</t>
         </is>
       </c>
       <c r="H22" t="n">
-        <v>1.0274786630262</v>
+        <v>1.06</v>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>MATRIZ</t>
+          <t>ISIN</t>
         </is>
       </c>
       <c r="J22" t="b">
@@ -1428,32 +1424,36 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>BANCO VOLKSWAGEN S/A</t>
+          <t>BANCO INTER SA</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>BBRASIL FIM CP RESP</t>
+          <t>BMG SEG</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>CDB925CDN0L</t>
+          <t>CDB7257QUDI</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>BRBVKWC01543</t>
-        </is>
-      </c>
-      <c r="F23" t="inlineStr"/>
+          <t>BRBIDIC002H4</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>613315-CDB</t>
+        </is>
+      </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>2025-12-22 00:00:00</t>
+          <t>2026-07-10 00:00:00</t>
         </is>
       </c>
       <c r="H23" t="n">
-        <v>1.015</v>
+        <v>1.027455331736998</v>
       </c>
       <c r="I23" t="inlineStr">
         <is>
@@ -1467,41 +1467,41 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Debêntures</t>
+          <t>CDB</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>HAPVIDA PARTICIPACOES E INVESTIMENTOS S/A</t>
+          <t>BANCO VOLKSWAGEN S/A</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>FIRF GERAES</t>
+          <t>BBRASIL FIM CP RESP</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>HAPV21</t>
+          <t>CDB925CDN0L</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>BRHAPVDBS014</t>
+          <t>BRBVKWC01543</t>
         </is>
       </c>
       <c r="F24" t="inlineStr"/>
       <c r="G24" t="inlineStr">
         <is>
-          <t>2026-07-10 00:00:00</t>
+          <t>2025-12-22 00:00:00</t>
         </is>
       </c>
       <c r="H24" t="n">
-        <v>1.307094</v>
+        <v>1.02</v>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>ISIN</t>
+          <t>MATRIZ</t>
         </is>
       </c>
       <c r="J24" t="b">
@@ -1521,7 +1521,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>JERA2026</t>
+          <t>FIRF GERAES</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -1534,11 +1534,7 @@
           <t>BRHAPVDBS014</t>
         </is>
       </c>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>362409-HAP</t>
-        </is>
-      </c>
+      <c r="F25" t="inlineStr"/>
       <c r="G25" t="inlineStr">
         <is>
           <t>2026-07-10 00:00:00</t>
@@ -1549,11 +1545,11 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>ISIN</t>
         </is>
       </c>
       <c r="J25" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="26">
@@ -1564,32 +1560,36 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>KLABIN S/A</t>
+          <t>HAPVIDA PARTICIPACOES E INVESTIMENTOS S/A</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>BH INFRA</t>
+          <t>JERA2026</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>KLBNA2</t>
+          <t>HAPV21</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>BRKLBNDBS004</t>
-        </is>
-      </c>
-      <c r="F26" t="inlineStr"/>
+          <t>BRHAPVDBS014</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>362409-HAP</t>
+        </is>
+      </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>2029-03-19 00:00:00</t>
+          <t>2026-07-10 00:00:00</t>
         </is>
       </c>
       <c r="H26" t="n">
-        <v>1.030641</v>
+        <v>1.307094</v>
       </c>
       <c r="I26" t="inlineStr">
         <is>
@@ -1613,7 +1613,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>FIRF GERAES 30</t>
+          <t>BH INFRA</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -1637,11 +1637,11 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>ISIN</t>
+          <t>NA</t>
         </is>
       </c>
       <c r="J27" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="28">
@@ -1657,7 +1657,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>FIRF GERAES</t>
+          <t>FIRF GERAES 30</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -1701,7 +1701,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>HORIZONTE FIM</t>
+          <t>FIRF GERAES</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -1745,7 +1745,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>REAL FIM</t>
+          <t>HORIZONTE FIM</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -1758,11 +1758,7 @@
           <t>BRKLBNDBS004</t>
         </is>
       </c>
-      <c r="F30" t="inlineStr">
-        <is>
-          <t>353017-KLB</t>
-        </is>
-      </c>
+      <c r="F30" t="inlineStr"/>
       <c r="G30" t="inlineStr">
         <is>
           <t>2029-03-19 00:00:00</t>
@@ -1773,55 +1769,59 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>ISIN</t>
         </is>
       </c>
       <c r="J30" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Letra Financeira</t>
+          <t>Debêntures</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>BANCO XP</t>
+          <t>KLABIN S/A</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>BMG SEG</t>
+          <t>REAL FIM</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LF00240072E</t>
+          <t>KLBNA2</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>BRBCXPLFIKS5</t>
-        </is>
-      </c>
-      <c r="F31" t="inlineStr"/>
+          <t>BRKLBNDBS004</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>353017-KLB</t>
+        </is>
+      </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>2026-03-02 00:00:00</t>
+          <t>2029-03-19 00:00:00</t>
         </is>
       </c>
       <c r="H31" t="n">
-        <v>1.0225</v>
+        <v>1.030641</v>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>MATRIZ</t>
+          <t>NA</t>
         </is>
       </c>
       <c r="J31" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="32">
@@ -1837,23 +1837,23 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>FIRF GERAES</t>
+          <t>BMG SEG</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LF0024007Y4</t>
+          <t>LF00240072E</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>BRBCXPLFIO68</t>
+          <t>BRBCXPLFIKS5</t>
         </is>
       </c>
       <c r="F32" t="inlineStr"/>
       <c r="G32" t="inlineStr">
         <is>
-          <t>2026-03-16 00:00:00</t>
+          <t>2026-03-02 00:00:00</t>
         </is>
       </c>
       <c r="H32" t="n">
@@ -1871,7 +1871,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>CDB</t>
+          <t>Letra Financeira</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -1881,27 +1881,23 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>BMG SEG</t>
+          <t>FIRF GERAES</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LF0024008OB</t>
+          <t>LF0024007Y4</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>BRBCXPLFIO76</t>
-        </is>
-      </c>
-      <c r="F33" t="inlineStr">
-        <is>
-          <t>614522-CDB</t>
-        </is>
-      </c>
+          <t>BRBCXPLFIO68</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr"/>
       <c r="G33" t="inlineStr">
         <is>
-          <t>2026-03-23 00:00:00</t>
+          <t>2026-03-16 00:00:00</t>
         </is>
       </c>
       <c r="H33" t="n">
@@ -1919,7 +1915,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Letra Financeira</t>
+          <t>CDB</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -1929,7 +1925,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>FIRF GERAES</t>
+          <t>BMG SEG</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -1942,7 +1938,11 @@
           <t>BRBCXPLFIO76</t>
         </is>
       </c>
-      <c r="F34" t="inlineStr"/>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>614522-CDB</t>
+        </is>
+      </c>
       <c r="G34" t="inlineStr">
         <is>
           <t>2026-03-23 00:00:00</t>
@@ -1968,36 +1968,36 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>BANCO MERCANTIL DO BRASIL S.A.</t>
+          <t>BANCO XP</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>FIRF GERAES 30</t>
+          <t>FIRF GERAES</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LF002400KBT</t>
+          <t>LF0024008OB</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>BRBMEBLFI8V4</t>
+          <t>BRBCXPLFIO76</t>
         </is>
       </c>
       <c r="F35" t="inlineStr"/>
       <c r="G35" t="inlineStr">
         <is>
-          <t>2026-07-31 00:00:00</t>
+          <t>2026-03-23 00:00:00</t>
         </is>
       </c>
       <c r="H35" t="n">
-        <v>1.02858992832202</v>
+        <v>1.0225</v>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>ISIN</t>
+          <t>MATRIZ</t>
         </is>
       </c>
       <c r="J35" t="b">
@@ -2017,12 +2017,12 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>FIRF GERAES</t>
+          <t>FIRF GERAES 30</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LF002400KBU</t>
+          <t>LF002400KBT</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
@@ -2066,7 +2066,7 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>LF002400KBW</t>
+          <t>LF002400KBU</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
@@ -2105,12 +2105,12 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>MANACA INFRA</t>
+          <t>FIRF GERAES</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>LF002400KBX</t>
+          <t>LF002400KBW</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
@@ -2149,12 +2149,12 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>FIRF GERAES 30</t>
+          <t>MANACA INFRA</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>LF002400KBY</t>
+          <t>LF002400KBX</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
@@ -2193,12 +2193,12 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>BMG SEG</t>
+          <t>FIRF GERAES 30</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>LF002400KC0</t>
+          <t>LF002400KBY</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
@@ -2213,11 +2213,11 @@
         </is>
       </c>
       <c r="H40" t="n">
-        <v>1.046169955658442</v>
+        <v>1.02858992832202</v>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>MATRIZ</t>
+          <t>ISIN</t>
         </is>
       </c>
       <c r="J40" t="b">
@@ -2237,7 +2237,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>JERA2026</t>
+          <t>BMG SEG</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -2250,18 +2250,14 @@
           <t>BRBMEBLFI8V4</t>
         </is>
       </c>
-      <c r="F41" t="inlineStr">
-        <is>
-          <t>567797-LF0</t>
-        </is>
-      </c>
+      <c r="F41" t="inlineStr"/>
       <c r="G41" t="inlineStr">
         <is>
           <t>2026-07-31 00:00:00</t>
         </is>
       </c>
       <c r="H41" t="n">
-        <v>1.046169955658442</v>
+        <v>1.035</v>
       </c>
       <c r="I41" t="inlineStr">
         <is>
@@ -2285,12 +2281,12 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>REAL FIM</t>
+          <t>JERA2026</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>LF002400KC1</t>
+          <t>LF002400KC0</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
@@ -2300,7 +2296,7 @@
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>567798-LF0</t>
+          <t>567797-LF0</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
@@ -2309,7 +2305,7 @@
         </is>
       </c>
       <c r="H42" t="n">
-        <v>1.046169955658442</v>
+        <v>1.035</v>
       </c>
       <c r="I42" t="inlineStr">
         <is>
@@ -2333,12 +2329,12 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>TOPAZIO INFRA</t>
+          <t>REAL FIM</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>LF002400KC2</t>
+          <t>LF002400KC1</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
@@ -2346,14 +2342,18 @@
           <t>BRBMEBLFI8V4</t>
         </is>
       </c>
-      <c r="F43" t="inlineStr"/>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>567798-LF0</t>
+        </is>
+      </c>
       <c r="G43" t="inlineStr">
         <is>
           <t>2026-07-31 00:00:00</t>
         </is>
       </c>
       <c r="H43" t="n">
-        <v>1.046169955658442</v>
+        <v>1.035</v>
       </c>
       <c r="I43" t="inlineStr">
         <is>
@@ -2367,41 +2367,41 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>LFSC</t>
+          <t>Letra Financeira</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>BANCO ABC BRASIL S.A.</t>
+          <t>BANCO MERCANTIL DO BRASIL S.A.</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>FIRF GERAES</t>
+          <t>TOPAZIO INFRA</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>LFSC19003FD</t>
+          <t>LF002400KC2</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>BRABCBLFN7I2</t>
+          <t>BRBMEBLFI8V4</t>
         </is>
       </c>
       <c r="F44" t="inlineStr"/>
       <c r="G44" t="inlineStr">
         <is>
-          <t>2024-10-17 00:00:00</t>
+          <t>2026-07-31 00:00:00</t>
         </is>
       </c>
       <c r="H44" t="n">
-        <v>0.009000000000000001</v>
+        <v>1.035</v>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>ISIN</t>
+          <t>MATRIZ</t>
         </is>
       </c>
       <c r="J44" t="b">
@@ -2421,12 +2421,12 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>HORIZONTE FIM</t>
+          <t>FIRF GERAES</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>LFSC19003W3</t>
+          <t>LFSC19003FD</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
@@ -2465,12 +2465,12 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>FIRF GERAES 30</t>
+          <t>HORIZONTE FIM</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>LFSC19003W4</t>
+          <t>LFSC19003W3</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
@@ -2504,32 +2504,32 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>BANCO DO NORDESTE DO BRASIL S.A.</t>
+          <t>BANCO ABC BRASIL S.A.</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>HORIZONTE FIM</t>
+          <t>FIRF GERAES 30</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>LFSC190054C</t>
+          <t>LFSC19003W4</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>BRBNBRLFI013</t>
+          <t>BRABCBLFN7I2</t>
         </is>
       </c>
       <c r="F47" t="inlineStr"/>
       <c r="G47" t="inlineStr">
         <is>
-          <t>2024-06-11 00:00:00</t>
+          <t>2024-10-17 00:00:00</t>
         </is>
       </c>
       <c r="H47" t="n">
-        <v>1.18113603052</v>
+        <v>0.009000000000000001</v>
       </c>
       <c r="I47" t="inlineStr">
         <is>
@@ -2553,17 +2553,17 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>BH INFRA</t>
+          <t>HORIZONTE FIM</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>LFSC190054D</t>
+          <t>LFSC190054C</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>BRBNBRLFI021</t>
+          <t>BRBNBRLFI013</t>
         </is>
       </c>
       <c r="F48" t="inlineStr"/>
@@ -2597,7 +2597,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>FIRF GERAES</t>
+          <t>BH INFRA</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -2641,7 +2641,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>HORIZONTE FIM</t>
+          <t>FIRF GERAES</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -2685,7 +2685,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>MANACA INFRA</t>
+          <t>HORIZONTE FIM</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -2729,23 +2729,23 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>FIRF GERAES 30</t>
+          <t>MANACA INFRA</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>LFSC190054I</t>
+          <t>LFSC190054D</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>BRBNBRLFI039</t>
+          <t>BRBNBRLFI021</t>
         </is>
       </c>
       <c r="F52" t="inlineStr"/>
       <c r="G52" t="inlineStr">
         <is>
-          <t>2024-06-12 00:00:00</t>
+          <t>2024-06-11 00:00:00</t>
         </is>
       </c>
       <c r="H52" t="n">
@@ -2773,7 +2773,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>HORIZONTE FIM</t>
+          <t>FIRF GERAES 30</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -2822,12 +2822,12 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>LFSC190059S</t>
+          <t>LFSC190054I</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>BRBNBRLFI062</t>
+          <t>BRBNBRLFI039</t>
         </is>
       </c>
       <c r="F54" t="inlineStr"/>
@@ -2861,23 +2861,23 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>FIRF GERAES 30</t>
+          <t>HORIZONTE FIM</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>LFSC19005FF</t>
+          <t>LFSC190059S</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>BRBNBRLFI0C5</t>
+          <t>BRBNBRLFI062</t>
         </is>
       </c>
       <c r="F55" t="inlineStr"/>
       <c r="G55" t="inlineStr">
         <is>
-          <t>2024-06-18 00:00:00</t>
+          <t>2024-06-12 00:00:00</t>
         </is>
       </c>
       <c r="H55" t="n">
@@ -2905,7 +2905,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>HORIZONTE FIM</t>
+          <t>FIRF GERAES 30</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -2954,18 +2954,18 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>LFSC19005L1</t>
+          <t>LFSC19005FF</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>BRBNBRLFI0F8</t>
+          <t>BRBNBRLFI0C5</t>
         </is>
       </c>
       <c r="F57" t="inlineStr"/>
       <c r="G57" t="inlineStr">
         <is>
-          <t>2024-06-19 00:00:00</t>
+          <t>2024-06-18 00:00:00</t>
         </is>
       </c>
       <c r="H57" t="n">
@@ -2993,23 +2993,23 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>BH INFRA</t>
+          <t>HORIZONTE FIM</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>LFSC19005L3</t>
+          <t>LFSC19005L1</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>BRBNBRLFI0G6</t>
+          <t>BRBNBRLFI0F8</t>
         </is>
       </c>
       <c r="F58" t="inlineStr"/>
       <c r="G58" t="inlineStr">
         <is>
-          <t>2024-06-21 00:00:00</t>
+          <t>2024-06-19 00:00:00</t>
         </is>
       </c>
       <c r="H58" t="n">
@@ -3037,7 +3037,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>FIRF GERAES 30</t>
+          <t>BH INFRA</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -3076,7 +3076,7 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>BANCO ABC BRASIL S.A.</t>
+          <t>BANCO DO NORDESTE DO BRASIL S.A.</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -3086,22 +3086,22 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>LFSC19007G2</t>
+          <t>LFSC19005L3</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>BRABCBLFIM30</t>
+          <t>BRBNBRLFI0G6</t>
         </is>
       </c>
       <c r="F60" t="inlineStr"/>
       <c r="G60" t="inlineStr">
         <is>
-          <t>2024-10-17 00:00:00</t>
+          <t>2024-06-21 00:00:00</t>
         </is>
       </c>
       <c r="H60" t="n">
-        <v>0.00399851</v>
+        <v>1.18113603052</v>
       </c>
       <c r="I60" t="inlineStr">
         <is>
@@ -3115,41 +3115,41 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>LFSN</t>
+          <t>LFSC</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>BANCO SAFRA S.A.</t>
+          <t>BANCO ABC BRASIL S.A.</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>BH INFRA</t>
+          <t>FIRF GERAES 30</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>LFSN1800D4W</t>
+          <t>LFSC19007G2</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>BRBSAFLNND73</t>
+          <t>BRABCBLFIM30</t>
         </is>
       </c>
       <c r="F61" t="inlineStr"/>
       <c r="G61" t="inlineStr">
         <is>
-          <t>2026-06-08 00:00:00</t>
+          <t>2024-10-17 00:00:00</t>
         </is>
       </c>
       <c r="H61" t="n">
-        <v>1.016085755815899</v>
+        <v>0.00399851</v>
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>MATRIZ</t>
+          <t>ISIN</t>
         </is>
       </c>
       <c r="J61" t="b">
@@ -3185,7 +3185,7 @@
       <c r="F62" t="inlineStr"/>
       <c r="G62" t="inlineStr">
         <is>
-          <t>2026-08-06 00:00:00</t>
+          <t>2026-06-08 00:00:00</t>
         </is>
       </c>
       <c r="H62" t="n">
@@ -3213,7 +3213,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>CARMEL INFRA</t>
+          <t>BH INFRA</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -3221,15 +3221,19 @@
           <t>LFSN1800D4W</t>
         </is>
       </c>
-      <c r="E63" t="inlineStr"/>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>BRBSAFLNND73</t>
+        </is>
+      </c>
       <c r="F63" t="inlineStr"/>
       <c r="G63" t="inlineStr">
         <is>
-          <t>2026-06-08 00:00:00</t>
+          <t>2026-08-06 00:00:00</t>
         </is>
       </c>
       <c r="H63" t="n">
-        <v>1.016085755815899</v>
+        <v>1.003</v>
       </c>
       <c r="I63" t="inlineStr">
         <is>
@@ -3265,7 +3269,7 @@
       <c r="F64" t="inlineStr"/>
       <c r="G64" t="inlineStr">
         <is>
-          <t>2026-08-06 00:00:00</t>
+          <t>2026-06-08 00:00:00</t>
         </is>
       </c>
       <c r="H64" t="n">
@@ -3288,7 +3292,7 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>BANCO BRADESCO S.A.</t>
+          <t>BANCO SAFRA S.A.</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
@@ -3298,26 +3302,22 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>LFSN1800DG1</t>
-        </is>
-      </c>
-      <c r="E65" t="inlineStr">
-        <is>
-          <t>BRBBDCLTR2X9</t>
-        </is>
-      </c>
+          <t>LFSN1800D4W</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr"/>
       <c r="F65" t="inlineStr"/>
       <c r="G65" t="inlineStr">
         <is>
-          <t>2026-08-03 00:00:00</t>
+          <t>2026-08-06 00:00:00</t>
         </is>
       </c>
       <c r="H65" t="n">
-        <v>1.020018</v>
+        <v>1.003</v>
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>ISIN</t>
+          <t>MATRIZ</t>
         </is>
       </c>
       <c r="J65" t="b">
@@ -3337,7 +3337,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>JERA2026</t>
+          <t>CARMEL INFRA</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -3350,22 +3350,18 @@
           <t>BRBBDCLTR2X9</t>
         </is>
       </c>
-      <c r="F66" t="inlineStr">
-        <is>
-          <t>407137-LFS</t>
-        </is>
-      </c>
+      <c r="F66" t="inlineStr"/>
       <c r="G66" t="inlineStr">
         <is>
           <t>2026-08-03 00:00:00</t>
         </is>
       </c>
       <c r="H66" t="n">
-        <v>1.003</v>
+        <v>1.020018</v>
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>MATRIZ</t>
+          <t>ISIN</t>
         </is>
       </c>
       <c r="J66" t="b">
@@ -3385,31 +3381,35 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>FIRF GERAES</t>
+          <t>JERA2026</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>LFSN1800DIG</t>
+          <t>LFSN1800DG1</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>BRBBDCLTROH4</t>
-        </is>
-      </c>
-      <c r="F67" t="inlineStr"/>
+          <t>BRBBDCLTR2X9</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>407137-LFS</t>
+        </is>
+      </c>
       <c r="G67" t="inlineStr">
         <is>
           <t>2026-08-03 00:00:00</t>
         </is>
       </c>
       <c r="H67" t="n">
-        <v>1.020018</v>
+        <v>1.003</v>
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>ISIN</t>
+          <t>MATRIZ</t>
         </is>
       </c>
       <c r="J67" t="b">
@@ -3424,32 +3424,32 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>BANCO SAFRA S.A.</t>
+          <t>BANCO BRADESCO S.A.</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>BORDEAUX INFRA</t>
+          <t>FIRF GERAES</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>LFSN1800DS5</t>
+          <t>LFSN1800DIG</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>BRBSAFLNN8B3</t>
+          <t>BRBBDCLTROH4</t>
         </is>
       </c>
       <c r="F68" t="inlineStr"/>
       <c r="G68" t="inlineStr">
         <is>
-          <t>2026-08-17 00:00:00</t>
+          <t>2026-08-03 00:00:00</t>
         </is>
       </c>
       <c r="H68" t="n">
-        <v>1.012998</v>
+        <v>1.020018</v>
       </c>
       <c r="I68" t="inlineStr">
         <is>
@@ -3473,7 +3473,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>CARMEL INFRA</t>
+          <t>BORDEAUX INFRA</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -3517,7 +3517,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>JERA2026</t>
+          <t>CARMEL INFRA</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -3530,22 +3530,18 @@
           <t>BRBSAFLNN8B3</t>
         </is>
       </c>
-      <c r="F70" t="inlineStr">
-        <is>
-          <t>335769-LFS</t>
-        </is>
-      </c>
+      <c r="F70" t="inlineStr"/>
       <c r="G70" t="inlineStr">
         <is>
           <t>2026-08-17 00:00:00</t>
         </is>
       </c>
       <c r="H70" t="n">
-        <v>1.016302694975625</v>
+        <v>1.012998</v>
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>MATRIZ</t>
+          <t>ISIN</t>
         </is>
       </c>
       <c r="J70" t="b">
@@ -3560,36 +3556,40 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>BANCO ABC BRASIL S.A.</t>
+          <t>BANCO SAFRA S.A.</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>FIRF GERAES</t>
+          <t>JERA2026</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>LFSN1800E2G</t>
+          <t>LFSN1800DS5</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>BRABCBLFIM22</t>
-        </is>
-      </c>
-      <c r="F71" t="inlineStr"/>
+          <t>BRBSAFLNN8B3</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>335769-LFS</t>
+        </is>
+      </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>2025-09-29 00:00:00</t>
+          <t>2026-08-17 00:00:00</t>
         </is>
       </c>
       <c r="H71" t="n">
-        <v>0.00399851</v>
+        <v>1.012219553815679</v>
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>ISIN</t>
+          <t>MATRIZ</t>
         </is>
       </c>
       <c r="J71" t="b">
@@ -3604,7 +3604,7 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>BANCO SAFRA S.A.</t>
+          <t>BANCO ABC BRASIL S.A.</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
@@ -3614,22 +3614,22 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>LFSN1800HXO</t>
+          <t>LFSN1800E2G</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>BRBSAFLNN7R1</t>
+          <t>BRABCBLFIM22</t>
         </is>
       </c>
       <c r="F72" t="inlineStr"/>
       <c r="G72" t="inlineStr">
         <is>
-          <t>2026-11-06 00:00:00</t>
+          <t>2025-09-29 00:00:00</t>
         </is>
       </c>
       <c r="H72" t="n">
-        <v>1.021813</v>
+        <v>0.00399851</v>
       </c>
       <c r="I72" t="inlineStr">
         <is>
@@ -3658,22 +3658,22 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>LFSN1900008</t>
+          <t>LFSN1800HXO</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>BRBSAFLFNBB5</t>
+          <t>BRBSAFLNN7R1</t>
         </is>
       </c>
       <c r="F73" t="inlineStr"/>
       <c r="G73" t="inlineStr">
         <is>
-          <t>2027-01-08 00:00:00</t>
+          <t>2026-11-06 00:00:00</t>
         </is>
       </c>
       <c r="H73" t="n">
-        <v>1.027364</v>
+        <v>1.021813</v>
       </c>
       <c r="I73" t="inlineStr">
         <is>
@@ -3692,32 +3692,32 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>BANCO BTG PACTUAL S.A.</t>
+          <t>BANCO SAFRA S.A.</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>CARMEL INFRA</t>
+          <t>FIRF GERAES</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>LFSN19001BC</t>
+          <t>LFSN1900008</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>BRBPACLFIVQ4</t>
+          <t>BRBSAFLFNBB5</t>
         </is>
       </c>
       <c r="F74" t="inlineStr"/>
       <c r="G74" t="inlineStr">
         <is>
-          <t>2027-04-09 00:00:00</t>
+          <t>2027-01-08 00:00:00</t>
         </is>
       </c>
       <c r="H74" t="n">
-        <v>1.035107</v>
+        <v>1.027364</v>
       </c>
       <c r="I74" t="inlineStr">
         <is>
@@ -3741,7 +3741,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>JERA2026</t>
+          <t>CARMEL INFRA</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -3754,22 +3754,18 @@
           <t>BRBPACLFIVQ4</t>
         </is>
       </c>
-      <c r="F75" t="inlineStr">
-        <is>
-          <t>353997-N L</t>
-        </is>
-      </c>
+      <c r="F75" t="inlineStr"/>
       <c r="G75" t="inlineStr">
         <is>
           <t>2027-04-09 00:00:00</t>
         </is>
       </c>
       <c r="H75" t="n">
-        <v>1.04296980890625</v>
+        <v>1.035107</v>
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>MATRIZ</t>
+          <t>ISIN</t>
         </is>
       </c>
       <c r="J75" t="b">
@@ -3789,12 +3785,12 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>BH INFRA</t>
+          <t>JERA2026</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>LFSN19001BH</t>
+          <t>LFSN19001BC</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
@@ -3802,14 +3798,18 @@
           <t>BRBPACLFIVQ4</t>
         </is>
       </c>
-      <c r="F76" t="inlineStr"/>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>353997-N L</t>
+        </is>
+      </c>
       <c r="G76" t="inlineStr">
         <is>
           <t>2027-04-09 00:00:00</t>
         </is>
       </c>
       <c r="H76" t="n">
-        <v>1.04296980890625</v>
+        <v>1.044027056767213</v>
       </c>
       <c r="I76" t="inlineStr">
         <is>
@@ -3833,7 +3833,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>FIRF GERAES</t>
+          <t>BH INFRA</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -3853,11 +3853,11 @@
         </is>
       </c>
       <c r="H77" t="n">
-        <v>1.035107</v>
+        <v>1.044027056767213</v>
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>ISIN</t>
+          <t>MATRIZ</t>
         </is>
       </c>
       <c r="J77" t="b">
@@ -3877,27 +3877,27 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>FIRF GERAES 30</t>
+          <t>FIRF GERAES</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>LFSN19006KM</t>
+          <t>LFSN19001BH</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>BRBPACLFIWC2</t>
+          <t>BRBPACLFIVQ4</t>
         </is>
       </c>
       <c r="F78" t="inlineStr"/>
       <c r="G78" t="inlineStr">
         <is>
-          <t>2028-05-31 00:00:00</t>
+          <t>2027-04-09 00:00:00</t>
         </is>
       </c>
       <c r="H78" t="n">
-        <v>1.049916</v>
+        <v>1.035107</v>
       </c>
       <c r="I78" t="inlineStr">
         <is>
@@ -3921,7 +3921,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>HORIZONTE FIM</t>
+          <t>FIRF GERAES 30</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -3965,7 +3965,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>MANACA INFRA</t>
+          <t>HORIZONTE FIM</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -4009,7 +4009,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>REAL FIM</t>
+          <t>MANACA INFRA</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -4022,22 +4022,18 @@
           <t>BRBPACLFIWC2</t>
         </is>
       </c>
-      <c r="F81" t="inlineStr">
-        <is>
-          <t>513453-LFS</t>
-        </is>
-      </c>
+      <c r="F81" t="inlineStr"/>
       <c r="G81" t="inlineStr">
         <is>
           <t>2028-05-31 00:00:00</t>
         </is>
       </c>
       <c r="H81" t="n">
-        <v>1.059747868494567</v>
+        <v>1.049916</v>
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>MATRIZ</t>
+          <t>ISIN</t>
         </is>
       </c>
       <c r="J81" t="b">
@@ -4057,12 +4053,12 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>FIRF GERAES</t>
+          <t>REAL FIM</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>LFSN19006KN</t>
+          <t>LFSN19006KM</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
@@ -4070,18 +4066,22 @@
           <t>BRBPACLFIWC2</t>
         </is>
       </c>
-      <c r="F82" t="inlineStr"/>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>513453-LFS</t>
+        </is>
+      </c>
       <c r="G82" t="inlineStr">
         <is>
           <t>2028-05-31 00:00:00</t>
         </is>
       </c>
       <c r="H82" t="n">
-        <v>1.049916</v>
+        <v>1.060596901321775</v>
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>ISIN</t>
+          <t>MATRIZ</t>
         </is>
       </c>
       <c r="J82" t="b">
@@ -4096,36 +4096,36 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>BANCO BMG S.A.</t>
+          <t>BANCO BTG PACTUAL S.A.</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>BH INFRA</t>
+          <t>FIRF GERAES</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>LFSN1900971</t>
+          <t>LFSN19006KN</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>BRBMGBLFI489</t>
+          <t>BRBPACLFIWC2</t>
         </is>
       </c>
       <c r="F83" t="inlineStr"/>
       <c r="G83" t="inlineStr">
         <is>
-          <t>2026-06-22 00:00:00</t>
+          <t>2028-05-31 00:00:00</t>
         </is>
       </c>
       <c r="H83" t="n">
-        <v>1.07</v>
+        <v>1.049916</v>
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t>MATRIZ</t>
+          <t>ISIN</t>
         </is>
       </c>
       <c r="J83" t="b">
@@ -4145,7 +4145,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>BORDEAUX INFRA</t>
+          <t>BH INFRA</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -4165,7 +4165,7 @@
         </is>
       </c>
       <c r="H84" t="n">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="I84" t="inlineStr">
         <is>
@@ -4189,7 +4189,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>CARMEL INFRA</t>
+          <t>BORDEAUX INFRA</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -4197,7 +4197,11 @@
           <t>LFSN1900971</t>
         </is>
       </c>
-      <c r="E85" t="inlineStr"/>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>BRBMGBLFI489</t>
+        </is>
+      </c>
       <c r="F85" t="inlineStr"/>
       <c r="G85" t="inlineStr">
         <is>
@@ -4205,7 +4209,7 @@
         </is>
       </c>
       <c r="H85" t="n">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="I85" t="inlineStr">
         <is>
@@ -4229,7 +4233,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>FIRF GERAES 30</t>
+          <t>CARMEL INFRA</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -4237,11 +4241,7 @@
           <t>LFSN1900971</t>
         </is>
       </c>
-      <c r="E86" t="inlineStr">
-        <is>
-          <t>BRBMGBLFI489</t>
-        </is>
-      </c>
+      <c r="E86" t="inlineStr"/>
       <c r="F86" t="inlineStr"/>
       <c r="G86" t="inlineStr">
         <is>
@@ -4249,7 +4249,7 @@
         </is>
       </c>
       <c r="H86" t="n">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="I86" t="inlineStr">
         <is>
@@ -4273,7 +4273,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>FIRF GERAES</t>
+          <t>FIRF GERAES 30</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -4293,7 +4293,7 @@
         </is>
       </c>
       <c r="H87" t="n">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="I87" t="inlineStr">
         <is>
@@ -4317,27 +4317,27 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>BH INFRA</t>
+          <t>FIRF GERAES</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>LFSN19009YU</t>
+          <t>LFSN1900971</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>BRBMGBLFI6I3</t>
+          <t>BRBMGBLFI489</t>
         </is>
       </c>
       <c r="F88" t="inlineStr"/>
       <c r="G88" t="inlineStr">
         <is>
-          <t>2026-06-26 00:00:00</t>
+          <t>2026-06-22 00:00:00</t>
         </is>
       </c>
       <c r="H88" t="n">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="I88" t="inlineStr">
         <is>
@@ -4361,7 +4361,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>CARMEL INFRA</t>
+          <t>BH INFRA</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -4381,7 +4381,7 @@
         </is>
       </c>
       <c r="H89" t="n">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="I89" t="inlineStr">
         <is>
@@ -4405,7 +4405,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>FIRF GERAES</t>
+          <t>CARMEL INFRA</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -4425,7 +4425,7 @@
         </is>
       </c>
       <c r="H90" t="n">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="I90" t="inlineStr">
         <is>
@@ -4444,36 +4444,36 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>BANCO SAFRA S.A.</t>
+          <t>BANCO BMG S.A.</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>FIRF GERAES 30</t>
+          <t>FIRF GERAES</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>LFSN1900CR5</t>
+          <t>LFSN19009YU</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>BRBSAFLFNG47</t>
+          <t>BRBMGBLFI6I3</t>
         </is>
       </c>
       <c r="F91" t="inlineStr"/>
       <c r="G91" t="inlineStr">
         <is>
-          <t>2029-08-13 00:00:00</t>
+          <t>2026-06-26 00:00:00</t>
         </is>
       </c>
       <c r="H91" t="n">
-        <v>1.087205</v>
+        <v>1.05</v>
       </c>
       <c r="I91" t="inlineStr">
         <is>
-          <t>ISIN</t>
+          <t>MATRIZ</t>
         </is>
       </c>
       <c r="J91" t="b">
@@ -4483,45 +4483,41 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>CDB</t>
+          <t>LFSN</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>AGIBANK</t>
+          <t>BANCO SAFRA S.A.</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>BMG SEG</t>
+          <t>FIRF GERAES 30</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>CDB3251WXH0</t>
+          <t>LFSN1900CR5</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>BRAGBKC00M66</t>
-        </is>
-      </c>
-      <c r="F92" t="inlineStr">
-        <is>
-          <t>614522-CDB</t>
-        </is>
-      </c>
+          <t>BRBSAFLFNG47</t>
+        </is>
+      </c>
+      <c r="F92" t="inlineStr"/>
       <c r="G92" t="inlineStr">
         <is>
-          <t>2027-03-08 00:00:00</t>
+          <t>2029-08-13 00:00:00</t>
         </is>
       </c>
       <c r="H92" t="n">
-        <v>1.035313360558953</v>
+        <v>1.087205</v>
       </c>
       <c r="I92" t="inlineStr">
         <is>
-          <t>MATRIZ</t>
+          <t>ISIN</t>
         </is>
       </c>
       <c r="J92" t="b">
@@ -4541,7 +4537,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>JERA2026</t>
+          <t>BMG SEG</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -4556,7 +4552,7 @@
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>353997-N L</t>
+          <t>614522-CDB</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
@@ -4565,7 +4561,7 @@
         </is>
       </c>
       <c r="H93" t="n">
-        <v>1.035313360558953</v>
+        <v>1.034885761650082</v>
       </c>
       <c r="I93" t="inlineStr">
         <is>
@@ -4589,7 +4585,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>REAL FIM</t>
+          <t>JERA2026</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -4613,7 +4609,7 @@
         </is>
       </c>
       <c r="H94" t="n">
-        <v>1.035313360558953</v>
+        <v>1.034885761650082</v>
       </c>
       <c r="I94" t="inlineStr">
         <is>
@@ -4632,36 +4628,36 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>BANCO XP</t>
+          <t>AGIBANK</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>BMG SEG</t>
+          <t>REAL FIM</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>LF00240072E</t>
+          <t>CDB3251WXH0</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>BRBCXPLFIKS5</t>
+          <t>BRAGBKC00M66</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>614522-CDB</t>
+          <t>353997-N L</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>2026-03-02 00:00:00</t>
+          <t>2027-03-08 00:00:00</t>
         </is>
       </c>
       <c r="H95" t="n">
-        <v>1.0225</v>
+        <v>1.034885761650082</v>
       </c>
       <c r="I95" t="inlineStr">
         <is>
@@ -4685,7 +4681,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>JERA2026</t>
+          <t>BMG SEG</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -4700,7 +4696,7 @@
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>353997-N L</t>
+          <t>614522-CDB</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
@@ -4728,7 +4724,7 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>BANCO BMG S.A.</t>
+          <t>BANCO XP</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
@@ -4738,26 +4734,26 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>LFSC19002CD</t>
+          <t>LF00240072E</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>BRBMGBLFI7Q4</t>
+          <t>BRBCXPLFIKS5</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>609712-LFS</t>
+          <t>353997-N L</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>2029-04-09 00:00:00</t>
+          <t>2026-03-02 00:00:00</t>
         </is>
       </c>
       <c r="H97" t="n">
-        <v>1.07740539991251</v>
+        <v>1.0225</v>
       </c>
       <c r="I97" t="inlineStr">
         <is>
@@ -4786,17 +4782,17 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>LFSC19002CE</t>
+          <t>LFSC19002CD</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>BRBMGBLFI7P6</t>
+          <t>BRBMGBLFI7Q4</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>609711-LFS</t>
+          <t>609712-LFS</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
@@ -4805,7 +4801,7 @@
         </is>
       </c>
       <c r="H98" t="n">
-        <v>1.07740539991251</v>
+        <v>1.07045790198874</v>
       </c>
       <c r="I98" t="inlineStr">
         <is>
@@ -4834,33 +4830,81 @@
       </c>
       <c r="D99" t="inlineStr">
         <is>
+          <t>LFSC19002CE</t>
+        </is>
+      </c>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>BRBMGBLFI7P6</t>
+        </is>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>609711-LFS</t>
+        </is>
+      </c>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>2029-04-09 00:00:00</t>
+        </is>
+      </c>
+      <c r="H99" t="n">
+        <v>1.07045790198874</v>
+      </c>
+      <c r="I99" t="inlineStr">
+        <is>
+          <t>MATRIZ</t>
+        </is>
+      </c>
+      <c r="J99" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>CDB</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>BANCO BMG S.A.</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>JERA2026</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
           <t>LFSC19002HS</t>
         </is>
       </c>
-      <c r="E99" t="inlineStr">
+      <c r="E100" t="inlineStr">
         <is>
           <t>BRBMGBLFI7R2</t>
         </is>
       </c>
-      <c r="F99" t="inlineStr">
+      <c r="F100" t="inlineStr">
         <is>
           <t>609713-LFS</t>
         </is>
       </c>
-      <c r="G99" t="inlineStr">
+      <c r="G100" t="inlineStr">
         <is>
           <t>2029-04-09 00:00:00</t>
         </is>
       </c>
-      <c r="H99" t="n">
-        <v>1.07740539991251</v>
-      </c>
-      <c r="I99" t="inlineStr">
+      <c r="H100" t="n">
+        <v>1.07045790198874</v>
+      </c>
+      <c r="I100" t="inlineStr">
         <is>
           <t>MATRIZ</t>
         </is>
       </c>
-      <c r="J99" t="b">
+      <c r="J100" t="b">
         <v>0</v>
       </c>
     </row>

--- a/Dados/ativos_mapeados_com_taxa_efetiva.xlsx
+++ b/Dados/ativos_mapeados_com_taxa_efetiva.xlsx
@@ -601,11 +601,11 @@
         </is>
       </c>
       <c r="H4" t="n">
-        <v>1.0569</v>
+        <v>1.02</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>ISIN</t>
+          <t>MATRIZ</t>
         </is>
       </c>
       <c r="J4" t="b">
@@ -645,7 +645,7 @@
         </is>
       </c>
       <c r="H5" t="n">
-        <v>1.034885761650082</v>
+        <v>1.034712084469143</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
@@ -689,7 +689,7 @@
         </is>
       </c>
       <c r="H6" t="n">
-        <v>1.034885761650082</v>
+        <v>1.034712084469143</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
@@ -733,7 +733,7 @@
         </is>
       </c>
       <c r="H7" t="n">
-        <v>1.04537937504615</v>
+        <v>1.0252348601965</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
@@ -777,7 +777,7 @@
         </is>
       </c>
       <c r="H8" t="n">
-        <v>1.04537937504615</v>
+        <v>1.0252348601965</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
@@ -821,7 +821,7 @@
         </is>
       </c>
       <c r="H9" t="n">
-        <v>1.04537937504615</v>
+        <v>1.0252348601965</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
@@ -865,7 +865,7 @@
         </is>
       </c>
       <c r="H10" t="n">
-        <v>1.034885761650082</v>
+        <v>1.034712084469143</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
@@ -909,7 +909,7 @@
         </is>
       </c>
       <c r="H11" t="n">
-        <v>1.034885761650082</v>
+        <v>1.034712084469143</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
@@ -953,7 +953,7 @@
         </is>
       </c>
       <c r="H12" t="n">
-        <v>1.032449941153846</v>
+        <v>1.03239988471142</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
@@ -997,7 +997,7 @@
         </is>
       </c>
       <c r="H13" t="n">
-        <v>1.032449941153846</v>
+        <v>1.03239988471142</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
@@ -1041,7 +1041,7 @@
         </is>
       </c>
       <c r="H14" t="n">
-        <v>1.032449941153846</v>
+        <v>1.03239988471142</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
@@ -1089,7 +1089,7 @@
         </is>
       </c>
       <c r="H15" t="n">
-        <v>1.032449941153846</v>
+        <v>1.03239988471142</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
@@ -1133,7 +1133,7 @@
         </is>
       </c>
       <c r="H16" t="n">
-        <v>1.032449941153846</v>
+        <v>1.03239988471142</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
@@ -1181,7 +1181,7 @@
         </is>
       </c>
       <c r="H17" t="n">
-        <v>1.032449941153846</v>
+        <v>1.03239988471142</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
@@ -1317,7 +1317,7 @@
         </is>
       </c>
       <c r="H20" t="n">
-        <v>1.027455331736998</v>
+        <v>1.027414900915792</v>
       </c>
       <c r="I20" t="inlineStr">
         <is>
@@ -1361,11 +1361,11 @@
         </is>
       </c>
       <c r="H21" t="n">
-        <v>1.06</v>
+        <v>1.027414900915792</v>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>ISIN</t>
+          <t>MATRIZ</t>
         </is>
       </c>
       <c r="J21" t="b">
@@ -1405,11 +1405,11 @@
         </is>
       </c>
       <c r="H22" t="n">
-        <v>1.06</v>
+        <v>1.027414900915792</v>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>ISIN</t>
+          <t>MATRIZ</t>
         </is>
       </c>
       <c r="J22" t="b">
@@ -1453,7 +1453,7 @@
         </is>
       </c>
       <c r="H23" t="n">
-        <v>1.027455331736998</v>
+        <v>1.027414900915792</v>
       </c>
       <c r="I23" t="inlineStr">
         <is>
@@ -1540,12 +1540,10 @@
           <t>2026-07-10 00:00:00</t>
         </is>
       </c>
-      <c r="H25" t="n">
-        <v>1.307094</v>
-      </c>
+      <c r="H25" t="inlineStr"/>
       <c r="I25" t="inlineStr">
         <is>
-          <t>ISIN</t>
+          <t>NA</t>
         </is>
       </c>
       <c r="J25" t="b">
@@ -1588,16 +1586,14 @@
           <t>2026-07-10 00:00:00</t>
         </is>
       </c>
-      <c r="H26" t="n">
-        <v>1.307094</v>
-      </c>
+      <c r="H26" t="inlineStr"/>
       <c r="I26" t="inlineStr">
         <is>
           <t>NA</t>
         </is>
       </c>
       <c r="J26" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="27">
@@ -1633,7 +1629,7 @@
         </is>
       </c>
       <c r="H27" t="n">
-        <v>1.030641</v>
+        <v>1.028614</v>
       </c>
       <c r="I27" t="inlineStr">
         <is>
@@ -1677,7 +1673,7 @@
         </is>
       </c>
       <c r="H28" t="n">
-        <v>1.030641</v>
+        <v>1.028614</v>
       </c>
       <c r="I28" t="inlineStr">
         <is>
@@ -1721,7 +1717,7 @@
         </is>
       </c>
       <c r="H29" t="n">
-        <v>1.030641</v>
+        <v>1.028614</v>
       </c>
       <c r="I29" t="inlineStr">
         <is>
@@ -1765,7 +1761,7 @@
         </is>
       </c>
       <c r="H30" t="n">
-        <v>1.030641</v>
+        <v>1.029422</v>
       </c>
       <c r="I30" t="inlineStr">
         <is>
@@ -1813,7 +1809,7 @@
         </is>
       </c>
       <c r="H31" t="n">
-        <v>1.030641</v>
+        <v>1.028614</v>
       </c>
       <c r="I31" t="inlineStr">
         <is>
@@ -2037,11 +2033,11 @@
         </is>
       </c>
       <c r="H36" t="n">
-        <v>1.02858992832202</v>
+        <v>1.035</v>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>ISIN</t>
+          <t>MATRIZ</t>
         </is>
       </c>
       <c r="J36" t="b">
@@ -2081,11 +2077,11 @@
         </is>
       </c>
       <c r="H37" t="n">
-        <v>1.02858992832202</v>
+        <v>1.035</v>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>ISIN</t>
+          <t>MATRIZ</t>
         </is>
       </c>
       <c r="J37" t="b">
@@ -2125,11 +2121,11 @@
         </is>
       </c>
       <c r="H38" t="n">
-        <v>1.02858992832202</v>
+        <v>1.035</v>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>ISIN</t>
+          <t>MATRIZ</t>
         </is>
       </c>
       <c r="J38" t="b">
@@ -2169,11 +2165,11 @@
         </is>
       </c>
       <c r="H39" t="n">
-        <v>1.02858992832202</v>
+        <v>1.035</v>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>ISIN</t>
+          <t>MATRIZ</t>
         </is>
       </c>
       <c r="J39" t="b">
@@ -2213,11 +2209,11 @@
         </is>
       </c>
       <c r="H40" t="n">
-        <v>1.02858992832202</v>
+        <v>1.035</v>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>ISIN</t>
+          <t>MATRIZ</t>
         </is>
       </c>
       <c r="J40" t="b">
@@ -2441,7 +2437,7 @@
         </is>
       </c>
       <c r="H45" t="n">
-        <v>0.009000000000000001</v>
+        <v>0.008500000000000001</v>
       </c>
       <c r="I45" t="inlineStr">
         <is>
@@ -2529,7 +2525,7 @@
         </is>
       </c>
       <c r="H47" t="n">
-        <v>0.009000000000000001</v>
+        <v>0.008500000000000001</v>
       </c>
       <c r="I47" t="inlineStr">
         <is>
@@ -3145,7 +3141,7 @@
         </is>
       </c>
       <c r="H61" t="n">
-        <v>0.00399851</v>
+        <v>0.00373305</v>
       </c>
       <c r="I61" t="inlineStr">
         <is>
@@ -3357,11 +3353,11 @@
         </is>
       </c>
       <c r="H66" t="n">
-        <v>1.020018</v>
+        <v>1.003</v>
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>ISIN</t>
+          <t>MATRIZ</t>
         </is>
       </c>
       <c r="J66" t="b">
@@ -3449,11 +3445,11 @@
         </is>
       </c>
       <c r="H68" t="n">
-        <v>1.020018</v>
+        <v>1.003</v>
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>ISIN</t>
+          <t>MATRIZ</t>
         </is>
       </c>
       <c r="J68" t="b">
@@ -3493,11 +3489,11 @@
         </is>
       </c>
       <c r="H69" t="n">
-        <v>1.012998</v>
+        <v>1.003</v>
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>ISIN</t>
+          <t>MATRIZ</t>
         </is>
       </c>
       <c r="J69" t="b">
@@ -3537,11 +3533,11 @@
         </is>
       </c>
       <c r="H70" t="n">
-        <v>1.012998</v>
+        <v>1.003</v>
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>ISIN</t>
+          <t>MATRIZ</t>
         </is>
       </c>
       <c r="J70" t="b">
@@ -3585,7 +3581,7 @@
         </is>
       </c>
       <c r="H71" t="n">
-        <v>1.012219553815679</v>
+        <v>1.003</v>
       </c>
       <c r="I71" t="inlineStr">
         <is>
@@ -3629,7 +3625,7 @@
         </is>
       </c>
       <c r="H72" t="n">
-        <v>0.00399851</v>
+        <v>0.00373305</v>
       </c>
       <c r="I72" t="inlineStr">
         <is>
@@ -3673,7 +3669,7 @@
         </is>
       </c>
       <c r="H73" t="n">
-        <v>1.021813</v>
+        <v>1.016004</v>
       </c>
       <c r="I73" t="inlineStr">
         <is>
@@ -3717,7 +3713,7 @@
         </is>
       </c>
       <c r="H74" t="n">
-        <v>1.027364</v>
+        <v>1.021813</v>
       </c>
       <c r="I74" t="inlineStr">
         <is>
@@ -3761,7 +3757,7 @@
         </is>
       </c>
       <c r="H75" t="n">
-        <v>1.035107</v>
+        <v>1.032555</v>
       </c>
       <c r="I75" t="inlineStr">
         <is>
@@ -3809,7 +3805,7 @@
         </is>
       </c>
       <c r="H76" t="n">
-        <v>1.044027056767213</v>
+        <v>1.04236373705509</v>
       </c>
       <c r="I76" t="inlineStr">
         <is>
@@ -3853,7 +3849,7 @@
         </is>
       </c>
       <c r="H77" t="n">
-        <v>1.044027056767213</v>
+        <v>1.04236373705509</v>
       </c>
       <c r="I77" t="inlineStr">
         <is>
@@ -3897,7 +3893,7 @@
         </is>
       </c>
       <c r="H78" t="n">
-        <v>1.035107</v>
+        <v>1.032555</v>
       </c>
       <c r="I78" t="inlineStr">
         <is>
@@ -3941,7 +3937,7 @@
         </is>
       </c>
       <c r="H79" t="n">
-        <v>1.049916</v>
+        <v>1.048077</v>
       </c>
       <c r="I79" t="inlineStr">
         <is>
@@ -3985,7 +3981,7 @@
         </is>
       </c>
       <c r="H80" t="n">
-        <v>1.049916</v>
+        <v>1.049006</v>
       </c>
       <c r="I80" t="inlineStr">
         <is>
@@ -4029,7 +4025,7 @@
         </is>
       </c>
       <c r="H81" t="n">
-        <v>1.049916</v>
+        <v>1.048077</v>
       </c>
       <c r="I81" t="inlineStr">
         <is>
@@ -4077,7 +4073,7 @@
         </is>
       </c>
       <c r="H82" t="n">
-        <v>1.060596901321775</v>
+        <v>1.059268852932506</v>
       </c>
       <c r="I82" t="inlineStr">
         <is>
@@ -4121,7 +4117,7 @@
         </is>
       </c>
       <c r="H83" t="n">
-        <v>1.049916</v>
+        <v>1.048077</v>
       </c>
       <c r="I83" t="inlineStr">
         <is>
@@ -4513,7 +4509,7 @@
         </is>
       </c>
       <c r="H92" t="n">
-        <v>1.087205</v>
+        <v>1.08453</v>
       </c>
       <c r="I92" t="inlineStr">
         <is>
@@ -4561,7 +4557,7 @@
         </is>
       </c>
       <c r="H93" t="n">
-        <v>1.034885761650082</v>
+        <v>1.034712084469143</v>
       </c>
       <c r="I93" t="inlineStr">
         <is>
@@ -4609,7 +4605,7 @@
         </is>
       </c>
       <c r="H94" t="n">
-        <v>1.034885761650082</v>
+        <v>1.034712084469143</v>
       </c>
       <c r="I94" t="inlineStr">
         <is>
@@ -4657,7 +4653,7 @@
         </is>
       </c>
       <c r="H95" t="n">
-        <v>1.034885761650082</v>
+        <v>1.034712084469143</v>
       </c>
       <c r="I95" t="inlineStr">
         <is>
@@ -4801,7 +4797,7 @@
         </is>
       </c>
       <c r="H98" t="n">
-        <v>1.07045790198874</v>
+        <v>1.069664153441496</v>
       </c>
       <c r="I98" t="inlineStr">
         <is>
@@ -4849,7 +4845,7 @@
         </is>
       </c>
       <c r="H99" t="n">
-        <v>1.07045790198874</v>
+        <v>1.069664153441496</v>
       </c>
       <c r="I99" t="inlineStr">
         <is>
@@ -4897,7 +4893,7 @@
         </is>
       </c>
       <c r="H100" t="n">
-        <v>1.07045790198874</v>
+        <v>1.069664153441496</v>
       </c>
       <c r="I100" t="inlineStr">
         <is>
